--- a/data/historico_comisiones.xlsx
+++ b/data/historico_comisiones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L85"/>
+  <dimension ref="A1:L121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1401,19 +1401,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LÃ­der Sandra Arbelaez</t>
+          <t>Eduar Alonso Olaya Estrada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>GIRARDOTA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1436,12 +1436,16 @@
           <t>Sin pago (0%)</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Mes de gracia</t>
+        </is>
+      </c>
       <c r="K20" t="n">
         <v>100</v>
       </c>
       <c r="L20" t="n">
-        <v>15.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="21">
@@ -1451,7 +1455,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -1463,7 +1467,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>LÃ­der Sandra Arbelaez</t>
+          <t>Eduar Alonso Olaya Estrada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1473,7 +1477,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>GIRARDOTA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1491,7 +1495,7 @@
         <v>100</v>
       </c>
       <c r="L21" t="n">
-        <v>15.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="22">
@@ -1501,19 +1505,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>LÃ­der Sandra Arbelaez</t>
+          <t>Eduar Alonso Olaya Estrada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1523,7 +1527,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>GIRARDOTA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1541,7 +1545,7 @@
         <v>100</v>
       </c>
       <c r="L22" t="n">
-        <v>15.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="23">
@@ -1551,10 +1555,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C23" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1563,7 +1567,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>LÃ­der Sandra Arbelaez</t>
+          <t>Eduar Alonso Olaya Estrada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1573,7 +1577,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>GIRARDOTA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1591,7 +1595,7 @@
         <v>100</v>
       </c>
       <c r="L23" t="n">
-        <v>15.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="24">
@@ -1601,7 +1605,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>375</v>
+        <v>480</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -1613,7 +1617,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>LÃ­der Sandra Arbelaez</t>
+          <t>Eduar Alonso Olaya Estrada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1623,7 +1627,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>GIRARDOTA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1641,7 +1645,7 @@
         <v>100</v>
       </c>
       <c r="L24" t="n">
-        <v>15.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="25">
@@ -1651,19 +1655,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1000000</v>
+        <v>2200000</v>
       </c>
       <c r="C25" t="n">
-        <v>110000</v>
+        <v>0</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>LÃ­der Sandra Arbelaez</t>
+          <t>Eduar Alonso Olaya Estrada</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1673,7 +1677,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>GIRARDOTA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1691,7 +1695,7 @@
         <v>100</v>
       </c>
       <c r="L25" t="n">
-        <v>15.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="26">
@@ -1701,19 +1705,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>48%</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Andrea  Arenas Hurtado</t>
+          <t>Narelig Alejandra GarcÃ­a Ramirez</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1723,7 +1727,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>GIRARDOTA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1736,16 +1740,12 @@
           <t>Sin pago (0%)</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Vacaciones hasta el 2 de septiembre</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="n">
         <v>100</v>
       </c>
       <c r="L26" t="n">
-        <v>25.5</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="27">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Andrea  Arenas Hurtado</t>
+          <t>Narelig Alejandra GarcÃ­a Ramirez</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>GIRARDOTA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1795,7 +1795,7 @@
         <v>100</v>
       </c>
       <c r="L27" t="n">
-        <v>25.5</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="28">
@@ -1805,19 +1805,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Andrea  Arenas Hurtado</t>
+          <t>Narelig Alejandra GarcÃ­a Ramirez</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>GIRARDOTA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1845,7 +1845,7 @@
         <v>100</v>
       </c>
       <c r="L28" t="n">
-        <v>25.5</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="29">
@@ -1855,10 +1855,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Andrea  Arenas Hurtado</t>
+          <t>Narelig Alejandra GarcÃ­a Ramirez</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>GIRARDOTA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1895,7 +1895,7 @@
         <v>100</v>
       </c>
       <c r="L29" t="n">
-        <v>25.5</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="30">
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>563</v>
+        <v>720</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Andrea  Arenas Hurtado</t>
+          <t>Narelig Alejandra GarcÃ­a Ramirez</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>GIRARDOTA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1945,7 +1945,7 @@
         <v>100</v>
       </c>
       <c r="L30" t="n">
-        <v>25.5</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="31">
@@ -1955,19 +1955,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1500000</v>
+        <v>3300000</v>
       </c>
       <c r="C31" t="n">
-        <v>175000</v>
+        <v>613000</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Andrea  Arenas Hurtado</t>
+          <t>Narelig Alejandra GarcÃ­a Ramirez</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>GIRARDOTA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1995,7 +1995,7 @@
         <v>100</v>
       </c>
       <c r="L31" t="n">
-        <v>25.5</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="32">
@@ -2005,29 +2005,29 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Luz Enith Sanchez Galeano</t>
+          <t>Lider Leider  Alexander Calderon</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2040,12 +2040,16 @@
           <t>Sin pago (0%)</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Vacaciones del 1 al  17  de septiembre</t>
+        </is>
+      </c>
       <c r="K32" t="n">
         <v>100</v>
       </c>
       <c r="L32" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2055,7 +2059,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -2067,17 +2071,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Luz Enith Sanchez Galeano</t>
+          <t>Lider Leider  Alexander Calderon</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2095,7 +2099,7 @@
         <v>100</v>
       </c>
       <c r="L33" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2105,7 +2109,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -2117,17 +2121,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Luz Enith Sanchez Galeano</t>
+          <t>Lider Leider  Alexander Calderon</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2145,7 +2149,7 @@
         <v>100</v>
       </c>
       <c r="L34" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2155,10 +2159,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="C35" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2167,17 +2171,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Luz Enith Sanchez Galeano</t>
+          <t>Lider Leider  Alexander Calderon</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2195,7 +2199,7 @@
         <v>100</v>
       </c>
       <c r="L35" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2205,7 +2209,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>563</v>
+        <v>127</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -2217,17 +2221,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Luz Enith Sanchez Galeano</t>
+          <t>Lider Leider  Alexander Calderon</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2245,7 +2249,7 @@
         <v>100</v>
       </c>
       <c r="L36" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2255,29 +2259,29 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1500000</v>
+        <v>592015</v>
       </c>
       <c r="C37" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Luz Enith Sanchez Galeano</t>
+          <t>Lider Leider  Alexander Calderon</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2295,7 +2299,7 @@
         <v>100</v>
       </c>
       <c r="L37" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2305,29 +2309,29 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Eduar Alonso Olaya Estrada</t>
+          <t>Jessica Catherine Gutierrez Garcia</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>GIRARDOTA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2340,16 +2344,12 @@
           <t>Sin pago (0%)</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Mes de gracia</t>
-        </is>
-      </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="n">
         <v>100</v>
       </c>
       <c r="L38" t="n">
-        <v>0.9</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="39">
@@ -2359,29 +2359,29 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Eduar Alonso Olaya Estrada</t>
+          <t>Jessica Catherine Gutierrez Garcia</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>GIRARDOTA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2399,7 +2399,7 @@
         <v>100</v>
       </c>
       <c r="L39" t="n">
-        <v>0.9</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="40">
@@ -2409,29 +2409,29 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Eduar Alonso Olaya Estrada</t>
+          <t>Jessica Catherine Gutierrez Garcia</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>GIRARDOTA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2449,7 +2449,7 @@
         <v>100</v>
       </c>
       <c r="L40" t="n">
-        <v>0.9</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="41">
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>52</v>
+        <v>133</v>
       </c>
       <c r="C41" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2471,17 +2471,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Eduar Alonso Olaya Estrada</t>
+          <t>Jessica Catherine Gutierrez Garcia</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>GIRARDOTA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2499,7 +2499,7 @@
         <v>100</v>
       </c>
       <c r="L41" t="n">
-        <v>0.9</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="42">
@@ -2509,7 +2509,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>480</v>
+        <v>400</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -2521,17 +2521,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Eduar Alonso Olaya Estrada</t>
+          <t>Jessica Catherine Gutierrez Garcia</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>GIRARDOTA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2549,7 +2549,7 @@
         <v>100</v>
       </c>
       <c r="L42" t="n">
-        <v>0.9</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="43">
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2200000</v>
+        <v>1866632</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -2571,17 +2571,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Eduar Alonso Olaya Estrada</t>
+          <t>Jessica Catherine Gutierrez Garcia</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>GIRARDOTA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2599,7 +2599,7 @@
         <v>100</v>
       </c>
       <c r="L43" t="n">
-        <v>0.9</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="44">
@@ -2609,19 +2609,19 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C44" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Narelig Alejandra GarcÃ­a Ramirez</t>
+          <t>Julieth Acevedo Gutierrez</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>GIRARDOTA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2649,7 +2649,7 @@
         <v>100</v>
       </c>
       <c r="L44" t="n">
-        <v>25.2</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="45">
@@ -2659,19 +2659,19 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Narelig Alejandra GarcÃ­a Ramirez</t>
+          <t>Julieth Acevedo Gutierrez</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>GIRARDOTA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2699,7 +2699,7 @@
         <v>100</v>
       </c>
       <c r="L45" t="n">
-        <v>25.2</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="46">
@@ -2709,19 +2709,19 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C46" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Narelig Alejandra GarcÃ­a Ramirez</t>
+          <t>Julieth Acevedo Gutierrez</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>GIRARDOTA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2749,7 +2749,7 @@
         <v>100</v>
       </c>
       <c r="L46" t="n">
-        <v>25.2</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="47">
@@ -2759,10 +2759,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="C47" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Narelig Alejandra GarcÃ­a Ramirez</t>
+          <t>Julieth Acevedo Gutierrez</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>GIRARDOTA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2799,7 +2799,7 @@
         <v>100</v>
       </c>
       <c r="L47" t="n">
-        <v>25.2</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="48">
@@ -2809,7 +2809,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>720</v>
+        <v>173</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Narelig Alejandra GarcÃ­a Ramirez</t>
+          <t>Julieth Acevedo Gutierrez</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>GIRARDOTA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2849,7 +2849,7 @@
         <v>100</v>
       </c>
       <c r="L48" t="n">
-        <v>25.2</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="49">
@@ -2859,19 +2859,19 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3300000</v>
+        <v>808088</v>
       </c>
       <c r="C49" t="n">
-        <v>613000</v>
+        <v>20000</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>19%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Narelig Alejandra GarcÃ­a Ramirez</t>
+          <t>Julieth Acevedo Gutierrez</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>GIRARDOTA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2899,7 +2899,7 @@
         <v>100</v>
       </c>
       <c r="L49" t="n">
-        <v>25.2</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="50">
@@ -2909,24 +2909,24 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>49%</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Lider Leider  Alexander Calderon</t>
+          <t>Nasly Johanna Martinez Ocampo</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2944,16 +2944,12 @@
           <t>Sin pago (0%)</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Vacaciones del 1 al  17  de septiembre</t>
-        </is>
-      </c>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="n">
         <v>100</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="51">
@@ -2963,24 +2959,24 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Lider Leider  Alexander Calderon</t>
+          <t>Nasly Johanna Martinez Ocampo</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3003,7 +2999,7 @@
         <v>100</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="52">
@@ -3013,24 +3009,24 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Lider Leider  Alexander Calderon</t>
+          <t>Nasly Johanna Martinez Ocampo</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3053,7 +3049,7 @@
         <v>100</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="53">
@@ -3063,10 +3059,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>42</v>
+        <v>133</v>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3075,12 +3071,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Lider Leider  Alexander Calderon</t>
+          <t>Nasly Johanna Martinez Ocampo</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3103,7 +3099,7 @@
         <v>100</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="54">
@@ -3113,7 +3109,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>127</v>
+        <v>400</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
@@ -3125,12 +3121,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Lider Leider  Alexander Calderon</t>
+          <t>Nasly Johanna Martinez Ocampo</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3153,7 +3149,7 @@
         <v>100</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="55">
@@ -3163,24 +3159,24 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>592015</v>
+        <v>1866632</v>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>160000</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Lider Leider  Alexander Calderon</t>
+          <t>Nasly Johanna Martinez Ocampo</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3203,7 +3199,7 @@
         <v>100</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="56">
@@ -3216,16 +3212,16 @@
         <v>37</v>
       </c>
       <c r="C56" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Jessica Catherine Gutierrez Garcia</t>
+          <t>Sandra Milena Carmona Galeano</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3253,7 +3249,7 @@
         <v>100</v>
       </c>
       <c r="L56" t="n">
-        <v>27.9</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="57">
@@ -3266,16 +3262,16 @@
         <v>4</v>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Jessica Catherine Gutierrez Garcia</t>
+          <t>Sandra Milena Carmona Galeano</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3303,7 +3299,7 @@
         <v>100</v>
       </c>
       <c r="L57" t="n">
-        <v>27.9</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="58">
@@ -3316,16 +3312,16 @@
         <v>59</v>
       </c>
       <c r="C58" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Jessica Catherine Gutierrez Garcia</t>
+          <t>Sandra Milena Carmona Galeano</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3353,7 +3349,7 @@
         <v>100</v>
       </c>
       <c r="L58" t="n">
-        <v>27.9</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="59">
@@ -3366,7 +3362,7 @@
         <v>133</v>
       </c>
       <c r="C59" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -3375,7 +3371,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Jessica Catherine Gutierrez Garcia</t>
+          <t>Sandra Milena Carmona Galeano</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3403,7 +3399,7 @@
         <v>100</v>
       </c>
       <c r="L59" t="n">
-        <v>27.9</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="60">
@@ -3425,7 +3421,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Jessica Catherine Gutierrez Garcia</t>
+          <t>Sandra Milena Carmona Galeano</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3453,7 +3449,7 @@
         <v>100</v>
       </c>
       <c r="L60" t="n">
-        <v>27.9</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="61">
@@ -3466,16 +3462,16 @@
         <v>1866632</v>
       </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>260000</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Jessica Catherine Gutierrez Garcia</t>
+          <t>Sandra Milena Carmona Galeano</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3503,7 +3499,7 @@
         <v>100</v>
       </c>
       <c r="L61" t="n">
-        <v>27.9</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="62">
@@ -3513,24 +3509,24 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C62" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Julieth Acevedo Gutierrez</t>
+          <t>Kelly Yuliana Ospina Saldarriaga</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>SUPERNUMERARIO</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3553,7 +3549,7 @@
         <v>100</v>
       </c>
       <c r="L62" t="n">
-        <v>13.5</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="63">
@@ -3563,7 +3559,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C63" t="n">
         <v>0</v>
@@ -3575,12 +3571,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Julieth Acevedo Gutierrez</t>
+          <t>Kelly Yuliana Ospina Saldarriaga</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>SUPERNUMERARIO</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3603,7 +3599,7 @@
         <v>100</v>
       </c>
       <c r="L63" t="n">
-        <v>13.5</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="64">
@@ -3613,24 +3609,24 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Julieth Acevedo Gutierrez</t>
+          <t>Kelly Yuliana Ospina Saldarriaga</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>SUPERNUMERARIO</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3653,7 +3649,7 @@
         <v>100</v>
       </c>
       <c r="L64" t="n">
-        <v>13.5</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="65">
@@ -3663,10 +3659,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="C65" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -3675,12 +3671,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Julieth Acevedo Gutierrez</t>
+          <t>Kelly Yuliana Ospina Saldarriaga</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>SUPERNUMERARIO</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3703,7 +3699,7 @@
         <v>100</v>
       </c>
       <c r="L65" t="n">
-        <v>13.5</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="66">
@@ -3713,7 +3709,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>173</v>
+        <v>399</v>
       </c>
       <c r="C66" t="n">
         <v>0</v>
@@ -3725,12 +3721,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Julieth Acevedo Gutierrez</t>
+          <t>Kelly Yuliana Ospina Saldarriaga</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>SUPERNUMERARIO</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3753,7 +3749,7 @@
         <v>100</v>
       </c>
       <c r="L66" t="n">
-        <v>13.5</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="67">
@@ -3763,24 +3759,24 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>808088</v>
+        <v>1862000</v>
       </c>
       <c r="C67" t="n">
-        <v>20000</v>
+        <v>95000</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Julieth Acevedo Gutierrez</t>
+          <t>Kelly Yuliana Ospina Saldarriaga</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>SUPERNUMERARIO</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3803,7 +3799,7 @@
         <v>100</v>
       </c>
       <c r="L67" t="n">
-        <v>13.5</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="68">
@@ -3813,29 +3809,29 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C68" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>49%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Nasly Johanna Martinez Ocampo</t>
+          <t>LÃ­der Sandra Arbelaez</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3853,7 +3849,7 @@
         <v>100</v>
       </c>
       <c r="L68" t="n">
-        <v>36.9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69">
@@ -3863,29 +3859,29 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C69" t="n">
         <v>2</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Nasly Johanna Martinez Ocampo</t>
+          <t>LÃ­der Sandra Arbelaez</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3903,7 +3899,7 @@
         <v>100</v>
       </c>
       <c r="L69" t="n">
-        <v>36.9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70">
@@ -3913,29 +3909,29 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="C70" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Nasly Johanna Martinez Ocampo</t>
+          <t>LÃ­der Sandra Arbelaez</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3953,7 +3949,7 @@
         <v>100</v>
       </c>
       <c r="L70" t="n">
-        <v>36.9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71">
@@ -3963,10 +3959,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>133</v>
+        <v>84</v>
       </c>
       <c r="C71" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -3975,17 +3971,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Nasly Johanna Martinez Ocampo</t>
+          <t>LÃ­der Sandra Arbelaez</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4003,7 +3999,7 @@
         <v>100</v>
       </c>
       <c r="L71" t="n">
-        <v>36.9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="72">
@@ -4013,7 +4009,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
@@ -4025,17 +4021,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Nasly Johanna Martinez Ocampo</t>
+          <t>LÃ­der Sandra Arbelaez</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4053,7 +4049,7 @@
         <v>100</v>
       </c>
       <c r="L72" t="n">
-        <v>36.9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="73">
@@ -4063,29 +4059,29 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1866632</v>
+        <v>1600000</v>
       </c>
       <c r="C73" t="n">
-        <v>160000</v>
+        <v>110000</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Nasly Johanna Martinez Ocampo</t>
+          <t>LÃ­der Sandra Arbelaez</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4103,7 +4099,7 @@
         <v>100</v>
       </c>
       <c r="L73" t="n">
-        <v>36.9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74">
@@ -4113,10 +4109,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C74" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -4125,7 +4121,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sandra Milena Carmona Galeano</t>
+          <t>Andrea  Arenas Hurtado</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4135,7 +4131,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4148,12 +4144,16 @@
           <t>Sin pago (0%)</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Vacaciones hasta el 2 de septiembre - inicia labores el 3</t>
+        </is>
+      </c>
       <c r="K74" t="n">
         <v>100</v>
       </c>
       <c r="L74" t="n">
-        <v>19.5</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="75">
@@ -4163,19 +4163,19 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sandra Milena Carmona Galeano</t>
+          <t>Andrea  Arenas Hurtado</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -4203,7 +4203,7 @@
         <v>100</v>
       </c>
       <c r="L75" t="n">
-        <v>19.5</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="76">
@@ -4213,19 +4213,19 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="C76" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sandra Milena Carmona Galeano</t>
+          <t>Andrea  Arenas Hurtado</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4253,7 +4253,7 @@
         <v>100</v>
       </c>
       <c r="L76" t="n">
-        <v>19.5</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="77">
@@ -4263,10 +4263,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="C77" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sandra Milena Carmona Galeano</t>
+          <t>Andrea  Arenas Hurtado</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4303,7 +4303,7 @@
         <v>100</v>
       </c>
       <c r="L77" t="n">
-        <v>19.5</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="78">
@@ -4313,7 +4313,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>400</v>
+        <v>831</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sandra Milena Carmona Galeano</t>
+          <t>Andrea  Arenas Hurtado</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4353,7 +4353,7 @@
         <v>100</v>
       </c>
       <c r="L78" t="n">
-        <v>19.5</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="79">
@@ -4363,19 +4363,19 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1866632</v>
+        <v>2215385</v>
       </c>
       <c r="C79" t="n">
-        <v>260000</v>
+        <v>175000</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sandra Milena Carmona Galeano</t>
+          <t>Andrea  Arenas Hurtado</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4403,7 +4403,7 @@
         <v>100</v>
       </c>
       <c r="L79" t="n">
-        <v>19.5</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="80">
@@ -4413,29 +4413,29 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="C80" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Kelly Yuliana Ospina Saldarriaga</t>
+          <t>Luz Enith Sanchez Galeano</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SUPERNUMERARIO</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4448,12 +4448,16 @@
           <t>Sin pago (0%)</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Cubre 2 días Andrea</t>
+        </is>
+      </c>
       <c r="K80" t="n">
         <v>100</v>
       </c>
       <c r="L80" t="n">
-        <v>4.4</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="81">
@@ -4463,7 +4467,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
@@ -4475,17 +4479,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Kelly Yuliana Ospina Saldarriaga</t>
+          <t>Luz Enith Sanchez Galeano</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>SUPERNUMERARIO</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4503,7 +4507,7 @@
         <v>100</v>
       </c>
       <c r="L81" t="n">
-        <v>4.4</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="82">
@@ -4513,29 +4517,29 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="C82" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Kelly Yuliana Ospina Saldarriaga</t>
+          <t>Luz Enith Sanchez Galeano</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SUPERNUMERARIO</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4553,7 +4557,7 @@
         <v>100</v>
       </c>
       <c r="L82" t="n">
-        <v>4.4</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="83">
@@ -4563,10 +4567,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>133</v>
+        <v>10</v>
       </c>
       <c r="C83" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -4575,17 +4579,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Kelly Yuliana Ospina Saldarriaga</t>
+          <t>Luz Enith Sanchez Galeano</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>SUPERNUMERARIO</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4603,7 +4607,7 @@
         <v>100</v>
       </c>
       <c r="L83" t="n">
-        <v>4.4</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="84">
@@ -4613,7 +4617,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>399</v>
+        <v>69</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
@@ -4625,17 +4629,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kelly Yuliana Ospina Saldarriaga</t>
+          <t>Luz Enith Sanchez Galeano</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>SUPERNUMERARIO</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4653,7 +4657,7 @@
         <v>100</v>
       </c>
       <c r="L84" t="n">
-        <v>4.4</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="85">
@@ -4663,29 +4667,29 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1862000</v>
+        <v>184615</v>
       </c>
       <c r="C85" t="n">
-        <v>95000</v>
+        <v>0</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Kelly Yuliana Ospina Saldarriaga</t>
+          <t>Luz Enith Sanchez Galeano</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>SUPERNUMERARIO</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4703,7 +4707,1819 @@
         <v>100</v>
       </c>
       <c r="L85" t="n">
-        <v>4.4</v>
+        <v>43.1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>POSTPAGO</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>21</v>
+      </c>
+      <c r="C86" t="n">
+        <v>15</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Lider Paola Andrea Clavijo</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>ENVIGADO</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="n">
+        <v>100</v>
+      </c>
+      <c r="L86" t="n">
+        <v>50.1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>HOGAR</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>5</v>
+      </c>
+      <c r="C87" t="n">
+        <v>9</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>180%</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Lider Paola Andrea Clavijo</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>ENVIGADO</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="n">
+        <v>100</v>
+      </c>
+      <c r="L87" t="n">
+        <v>50.1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>TERMINALES</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>24</v>
+      </c>
+      <c r="C88" t="n">
+        <v>4</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Lider Paola Andrea Clavijo</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>ENVIGADO</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="n">
+        <v>100</v>
+      </c>
+      <c r="L88" t="n">
+        <v>50.1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>50</v>
+      </c>
+      <c r="C89" t="n">
+        <v>17</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Pendiente 4 porta pre</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Lider Paola Andrea Clavijo</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>ENVIGADO</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="n">
+        <v>100</v>
+      </c>
+      <c r="L89" t="n">
+        <v>50.1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>CVS PLUS</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>392</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Lider Paola Andrea Clavijo</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>ENVIGADO</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="n">
+        <v>100</v>
+      </c>
+      <c r="L90" t="n">
+        <v>50.1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>ACCESORIOS</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>1177071</v>
+      </c>
+      <c r="C91" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Lider Paola Andrea Clavijo</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>ENVIGADO</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="n">
+        <v>100</v>
+      </c>
+      <c r="L91" t="n">
+        <v>50.1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>POSTPAGO</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>28</v>
+      </c>
+      <c r="C92" t="n">
+        <v>11</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Luz Enith Sanchez Galeano</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>ENVIGADO</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Cubrio 2 días a la asesora Andrea Arenas en el CVS de Sabaneta por ende se promedia la meta</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>100</v>
+      </c>
+      <c r="L92" t="n">
+        <v>36.8</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>HOGAR</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>7</v>
+      </c>
+      <c r="C93" t="n">
+        <v>4</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Luz Enith Sanchez Galeano</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>ENVIGADO</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="n">
+        <v>100</v>
+      </c>
+      <c r="L93" t="n">
+        <v>36.8</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>TERMINALES</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>31</v>
+      </c>
+      <c r="C94" t="n">
+        <v>12</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Luz Enith Sanchez Galeano</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>ENVIGADO</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="n">
+        <v>100</v>
+      </c>
+      <c r="L94" t="n">
+        <v>36.8</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>66</v>
+      </c>
+      <c r="C95" t="n">
+        <v>19</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Pendiente 4 porta pre</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Luz Enith Sanchez Galeano</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>ENVIGADO</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="n">
+        <v>100</v>
+      </c>
+      <c r="L95" t="n">
+        <v>36.8</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>CVS PLUS</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>519</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Luz Enith Sanchez Galeano</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>ENVIGADO</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="n">
+        <v>100</v>
+      </c>
+      <c r="L96" t="n">
+        <v>36.8</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>ACCESORIOS</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>1557643</v>
+      </c>
+      <c r="C97" t="n">
+        <v>250000</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Luz Enith Sanchez Galeano</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>ENVIGADO</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="n">
+        <v>100</v>
+      </c>
+      <c r="L97" t="n">
+        <v>36.8</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>POSTPAGO</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>31</v>
+      </c>
+      <c r="C98" t="n">
+        <v>14</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Yessica  Restrepo Caicedo</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>ENVIGADO</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="n">
+        <v>100</v>
+      </c>
+      <c r="L98" t="n">
+        <v>34.3</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>HOGAR</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>8</v>
+      </c>
+      <c r="C99" t="n">
+        <v>4</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Yessica  Restrepo Caicedo</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>ENVIGADO</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="n">
+        <v>100</v>
+      </c>
+      <c r="L99" t="n">
+        <v>34.3</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>TERMINALES</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>35</v>
+      </c>
+      <c r="C100" t="n">
+        <v>11</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Yessica  Restrepo Caicedo</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>ENVIGADO</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="n">
+        <v>100</v>
+      </c>
+      <c r="L100" t="n">
+        <v>34.3</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>75</v>
+      </c>
+      <c r="C101" t="n">
+        <v>19</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Pendiente 4 porta pre</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Yessica  Restrepo Caicedo</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>ENVIGADO</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="n">
+        <v>100</v>
+      </c>
+      <c r="L101" t="n">
+        <v>34.3</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>CVS PLUS</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>588</v>
+      </c>
+      <c r="C102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Yessica  Restrepo Caicedo</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>ENVIGADO</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="n">
+        <v>100</v>
+      </c>
+      <c r="L102" t="n">
+        <v>34.3</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>ACCESORIOS</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>1765286</v>
+      </c>
+      <c r="C103" t="n">
+        <v>424000</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Yessica  Restrepo Caicedo</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>ENVIGADO</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="n">
+        <v>100</v>
+      </c>
+      <c r="L103" t="n">
+        <v>34.3</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>POSTPAGO</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>12</v>
+      </c>
+      <c r="C104" t="n">
+        <v>1</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Lider Sara Julieth Acevedo Gutierrez</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>METRO EST. SAN ANTONIO</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="n">
+        <v>100</v>
+      </c>
+      <c r="L104" t="n">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>HOGAR</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>3</v>
+      </c>
+      <c r="C105" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Lider Sara Julieth Acevedo Gutierrez</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>METRO EST. SAN ANTONIO</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="n">
+        <v>100</v>
+      </c>
+      <c r="L105" t="n">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>TERMINALES</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>23</v>
+      </c>
+      <c r="C106" t="n">
+        <v>5</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Lider Sara Julieth Acevedo Gutierrez</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>METRO EST. SAN ANTONIO</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="n">
+        <v>100</v>
+      </c>
+      <c r="L106" t="n">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>54</v>
+      </c>
+      <c r="C107" t="n">
+        <v>5</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Pendiente 4 porta pre</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Lider Sara Julieth Acevedo Gutierrez</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>METRO EST. SAN ANTONIO</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="n">
+        <v>100</v>
+      </c>
+      <c r="L107" t="n">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>CVS PLUS</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Lider Sara Julieth Acevedo Gutierrez</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>METRO EST. SAN ANTONIO</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="n">
+        <v>100</v>
+      </c>
+      <c r="L108" t="n">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>ACCESORIOS</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>1540000</v>
+      </c>
+      <c r="C109" t="n">
+        <v>160000</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Lider Sara Julieth Acevedo Gutierrez</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>METRO EST. SAN ANTONIO</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="n">
+        <v>100</v>
+      </c>
+      <c r="L109" t="n">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>POSTPAGO</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>1</v>
+      </c>
+      <c r="C110" t="n">
+        <v>3</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>300%</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Daniel Alberto Orozco Orozco</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>METRO EST. SAN ANTONIO</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>El 8 inician capacitación de CVS PLUS</t>
+        </is>
+      </c>
+      <c r="K110" t="n">
+        <v>100</v>
+      </c>
+      <c r="L110" t="n">
+        <v>114.2</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>HOGAR</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Daniel Alberto Orozco Orozco</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>METRO EST. SAN ANTONIO</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="n">
+        <v>100</v>
+      </c>
+      <c r="L111" t="n">
+        <v>114.2</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>TERMINALES</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>3</v>
+      </c>
+      <c r="C112" t="n">
+        <v>3</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Daniel Alberto Orozco Orozco</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>METRO EST. SAN ANTONIO</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="n">
+        <v>100</v>
+      </c>
+      <c r="L112" t="n">
+        <v>114.2</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>6</v>
+      </c>
+      <c r="C113" t="n">
+        <v>6</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Pendiente 4 porta pre</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Daniel Alberto Orozco Orozco</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>METRO EST. SAN ANTONIO</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="n">
+        <v>100</v>
+      </c>
+      <c r="L113" t="n">
+        <v>114.2</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>CVS PLUS</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Daniel Alberto Orozco Orozco</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>METRO EST. SAN ANTONIO</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="n">
+        <v>100</v>
+      </c>
+      <c r="L114" t="n">
+        <v>114.2</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>ACCESORIOS</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>184000</v>
+      </c>
+      <c r="C115" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Daniel Alberto Orozco Orozco</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>METRO EST. SAN ANTONIO</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="n">
+        <v>100</v>
+      </c>
+      <c r="L115" t="n">
+        <v>114.2</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>POSTPAGO</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>6</v>
+      </c>
+      <c r="C116" t="n">
+        <v>3</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Luz Aida Quirama Corrales</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>METRO EST. SAN ANTONIO</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>El 8 inician capacitación de CVS PLUS</t>
+        </is>
+      </c>
+      <c r="K116" t="n">
+        <v>100</v>
+      </c>
+      <c r="L116" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>HOGAR</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>2</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Luz Aida Quirama Corrales</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>METRO EST. SAN ANTONIO</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="n">
+        <v>100</v>
+      </c>
+      <c r="L117" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>TERMINALES</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>11</v>
+      </c>
+      <c r="C118" t="n">
+        <v>2</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Luz Aida Quirama Corrales</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>METRO EST. SAN ANTONIO</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="n">
+        <v>100</v>
+      </c>
+      <c r="L118" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>26</v>
+      </c>
+      <c r="C119" t="n">
+        <v>11</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Pendiente 4 porta pre</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Luz Aida Quirama Corrales</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>METRO EST. SAN ANTONIO</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="n">
+        <v>100</v>
+      </c>
+      <c r="L119" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>CVS PLUS</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Luz Aida Quirama Corrales</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>METRO EST. SAN ANTONIO</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="n">
+        <v>100</v>
+      </c>
+      <c r="L120" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>ACCESORIOS</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>750000</v>
+      </c>
+      <c r="C121" t="n">
+        <v>135000</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Luz Aida Quirama Corrales</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>METRO EST. SAN ANTONIO</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="n">
+        <v>100</v>
+      </c>
+      <c r="L121" t="n">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/data/historico_comisiones.xlsx
+++ b/data/historico_comisiones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L121"/>
+  <dimension ref="A1:L175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3809,19 +3809,19 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C68" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>LÃ­der Sandra Arbelaez</t>
+          <t>Lider Paola Andrea Clavijo</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>ENVIGADO</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3849,7 +3849,7 @@
         <v>100</v>
       </c>
       <c r="L68" t="n">
-        <v>19</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="69">
@@ -3859,19 +3859,19 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>180%</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>LÃ­der Sandra Arbelaez</t>
+          <t>Lider Paola Andrea Clavijo</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>ENVIGADO</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3899,7 +3899,7 @@
         <v>100</v>
       </c>
       <c r="L69" t="n">
-        <v>19</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="70">
@@ -3912,16 +3912,16 @@
         <v>24</v>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>LÃ­der Sandra Arbelaez</t>
+          <t>Lider Paola Andrea Clavijo</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>ENVIGADO</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3949,7 +3949,7 @@
         <v>100</v>
       </c>
       <c r="L70" t="n">
-        <v>19</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="71">
@@ -3959,10 +3959,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C71" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>LÃ­der Sandra Arbelaez</t>
+          <t>Lider Paola Andrea Clavijo</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>ENVIGADO</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3999,7 +3999,7 @@
         <v>100</v>
       </c>
       <c r="L71" t="n">
-        <v>19</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="72">
@@ -4009,7 +4009,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>600</v>
+        <v>392</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>LÃ­der Sandra Arbelaez</t>
+          <t>Lider Paola Andrea Clavijo</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>ENVIGADO</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4049,7 +4049,7 @@
         <v>100</v>
       </c>
       <c r="L72" t="n">
-        <v>19</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="73">
@@ -4059,19 +4059,19 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1600000</v>
+        <v>1177071</v>
       </c>
       <c r="C73" t="n">
-        <v>110000</v>
+        <v>100000</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>LÃ­der Sandra Arbelaez</t>
+          <t>Lider Paola Andrea Clavijo</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>ENVIGADO</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4099,7 +4099,7 @@
         <v>100</v>
       </c>
       <c r="L73" t="n">
-        <v>19</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="74">
@@ -4109,19 +4109,19 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C74" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Andrea  Arenas Hurtado</t>
+          <t>Luz Enith Sanchez Galeano</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>ENVIGADO</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4146,14 +4146,14 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Vacaciones hasta el 2 de septiembre - inicia labores el 3</t>
+          <t>Cubrio 2 días a la asesora Andrea Arenas en el CVS de Sabaneta por ende se promedia la meta</t>
         </is>
       </c>
       <c r="K74" t="n">
         <v>100</v>
       </c>
       <c r="L74" t="n">
-        <v>27.3</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="75">
@@ -4163,19 +4163,19 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Andrea  Arenas Hurtado</t>
+          <t>Luz Enith Sanchez Galeano</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>ENVIGADO</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -4203,7 +4203,7 @@
         <v>100</v>
       </c>
       <c r="L75" t="n">
-        <v>27.3</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="76">
@@ -4213,10 +4213,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C76" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Andrea  Arenas Hurtado</t>
+          <t>Luz Enith Sanchez Galeano</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>ENVIGADO</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4253,7 +4253,7 @@
         <v>100</v>
       </c>
       <c r="L76" t="n">
-        <v>27.3</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="77">
@@ -4263,10 +4263,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>116</v>
+        <v>66</v>
       </c>
       <c r="C77" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Andrea  Arenas Hurtado</t>
+          <t>Luz Enith Sanchez Galeano</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>ENVIGADO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4303,7 +4303,7 @@
         <v>100</v>
       </c>
       <c r="L77" t="n">
-        <v>27.3</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="78">
@@ -4313,7 +4313,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>831</v>
+        <v>519</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Andrea  Arenas Hurtado</t>
+          <t>Luz Enith Sanchez Galeano</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>ENVIGADO</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4353,7 +4353,7 @@
         <v>100</v>
       </c>
       <c r="L78" t="n">
-        <v>27.3</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="79">
@@ -4363,19 +4363,19 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2215385</v>
+        <v>1557643</v>
       </c>
       <c r="C79" t="n">
-        <v>175000</v>
+        <v>250000</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Andrea  Arenas Hurtado</t>
+          <t>Luz Enith Sanchez Galeano</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>ENVIGADO</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4403,7 +4403,7 @@
         <v>100</v>
       </c>
       <c r="L79" t="n">
-        <v>27.3</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="80">
@@ -4413,19 +4413,19 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="C80" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Luz Enith Sanchez Galeano</t>
+          <t>Yessica  Restrepo Caicedo</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>ENVIGADO</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4448,16 +4448,12 @@
           <t>Sin pago (0%)</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>Cubre 2 días Andrea</t>
-        </is>
-      </c>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="n">
         <v>100</v>
       </c>
       <c r="L80" t="n">
-        <v>43.1</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="81">
@@ -4467,19 +4463,19 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C81" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Luz Enith Sanchez Galeano</t>
+          <t>Yessica  Restrepo Caicedo</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4489,7 +4485,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>ENVIGADO</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4507,7 +4503,7 @@
         <v>100</v>
       </c>
       <c r="L81" t="n">
-        <v>43.1</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="82">
@@ -4517,19 +4513,19 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="C82" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Luz Enith Sanchez Galeano</t>
+          <t>Yessica  Restrepo Caicedo</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4539,7 +4535,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>ENVIGADO</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4557,7 +4553,7 @@
         <v>100</v>
       </c>
       <c r="L82" t="n">
-        <v>43.1</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="83">
@@ -4567,10 +4563,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="C83" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -4579,7 +4575,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Luz Enith Sanchez Galeano</t>
+          <t>Yessica  Restrepo Caicedo</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4589,7 +4585,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>ENVIGADO</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4607,7 +4603,7 @@
         <v>100</v>
       </c>
       <c r="L83" t="n">
-        <v>43.1</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="84">
@@ -4617,7 +4613,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>69</v>
+        <v>588</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
@@ -4629,7 +4625,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Luz Enith Sanchez Galeano</t>
+          <t>Yessica  Restrepo Caicedo</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4639,7 +4635,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>ENVIGADO</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4657,7 +4653,7 @@
         <v>100</v>
       </c>
       <c r="L84" t="n">
-        <v>43.1</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="85">
@@ -4667,19 +4663,19 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>184615</v>
+        <v>1765286</v>
       </c>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>424000</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Luz Enith Sanchez Galeano</t>
+          <t>Yessica  Restrepo Caicedo</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4689,7 +4685,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>ENVIGADO</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4707,7 +4703,7 @@
         <v>100</v>
       </c>
       <c r="L85" t="n">
-        <v>43.1</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="86">
@@ -4717,19 +4713,19 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C86" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Lider Paola Andrea Clavijo</t>
+          <t>Lider Sara Julieth Acevedo Gutierrez</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4739,7 +4735,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>ENVIGADO</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4757,7 +4753,7 @@
         <v>100</v>
       </c>
       <c r="L86" t="n">
-        <v>50.1</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="87">
@@ -4767,19 +4763,19 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C87" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>180%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Lider Paola Andrea Clavijo</t>
+          <t>Lider Sara Julieth Acevedo Gutierrez</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4789,7 +4785,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>ENVIGADO</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4807,7 +4803,7 @@
         <v>100</v>
       </c>
       <c r="L87" t="n">
-        <v>50.1</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="88">
@@ -4817,19 +4813,19 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C88" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Lider Paola Andrea Clavijo</t>
+          <t>Lider Sara Julieth Acevedo Gutierrez</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4839,7 +4835,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>ENVIGADO</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4857,7 +4853,7 @@
         <v>100</v>
       </c>
       <c r="L88" t="n">
-        <v>50.1</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="89">
@@ -4867,10 +4863,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C89" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -4879,7 +4875,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Lider Paola Andrea Clavijo</t>
+          <t>Lider Sara Julieth Acevedo Gutierrez</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4889,7 +4885,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>ENVIGADO</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4907,7 +4903,7 @@
         <v>100</v>
       </c>
       <c r="L89" t="n">
-        <v>50.1</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="90">
@@ -4917,7 +4913,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
@@ -4929,7 +4925,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Lider Paola Andrea Clavijo</t>
+          <t>Lider Sara Julieth Acevedo Gutierrez</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4939,7 +4935,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>ENVIGADO</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4957,7 +4953,7 @@
         <v>100</v>
       </c>
       <c r="L90" t="n">
-        <v>50.1</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="91">
@@ -4967,19 +4963,19 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1177071</v>
+        <v>1540000</v>
       </c>
       <c r="C91" t="n">
-        <v>100000</v>
+        <v>160000</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Lider Paola Andrea Clavijo</t>
+          <t>Lider Sara Julieth Acevedo Gutierrez</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4989,7 +4985,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>ENVIGADO</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5007,7 +5003,7 @@
         <v>100</v>
       </c>
       <c r="L91" t="n">
-        <v>50.1</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="92">
@@ -5017,19 +5013,19 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="C92" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>300%</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Luz Enith Sanchez Galeano</t>
+          <t>Daniel Alberto Orozco Orozco</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -5039,7 +5035,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>ENVIGADO</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -5054,14 +5050,14 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Cubrio 2 días a la asesora Andrea Arenas en el CVS de Sabaneta por ende se promedia la meta</t>
+          <t>El 8 inician capacitación de CVS PLUS</t>
         </is>
       </c>
       <c r="K92" t="n">
         <v>100</v>
       </c>
       <c r="L92" t="n">
-        <v>36.8</v>
+        <v>114.2</v>
       </c>
     </row>
     <row r="93">
@@ -5071,19 +5067,19 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C93" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Luz Enith Sanchez Galeano</t>
+          <t>Daniel Alberto Orozco Orozco</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -5093,7 +5089,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>ENVIGADO</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -5111,7 +5107,7 @@
         <v>100</v>
       </c>
       <c r="L93" t="n">
-        <v>36.8</v>
+        <v>114.2</v>
       </c>
     </row>
     <row r="94">
@@ -5121,19 +5117,19 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="C94" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Luz Enith Sanchez Galeano</t>
+          <t>Daniel Alberto Orozco Orozco</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -5143,7 +5139,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>ENVIGADO</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -5161,7 +5157,7 @@
         <v>100</v>
       </c>
       <c r="L94" t="n">
-        <v>36.8</v>
+        <v>114.2</v>
       </c>
     </row>
     <row r="95">
@@ -5171,10 +5167,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>66</v>
+        <v>6</v>
       </c>
       <c r="C95" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -5183,7 +5179,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Luz Enith Sanchez Galeano</t>
+          <t>Daniel Alberto Orozco Orozco</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -5193,7 +5189,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>ENVIGADO</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -5211,7 +5207,7 @@
         <v>100</v>
       </c>
       <c r="L95" t="n">
-        <v>36.8</v>
+        <v>114.2</v>
       </c>
     </row>
     <row r="96">
@@ -5221,7 +5217,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>519</v>
+        <v>0</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
@@ -5233,7 +5229,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Luz Enith Sanchez Galeano</t>
+          <t>Daniel Alberto Orozco Orozco</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5243,7 +5239,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>ENVIGADO</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -5261,7 +5257,7 @@
         <v>100</v>
       </c>
       <c r="L96" t="n">
-        <v>36.8</v>
+        <v>114.2</v>
       </c>
     </row>
     <row r="97">
@@ -5271,19 +5267,19 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1557643</v>
+        <v>184000</v>
       </c>
       <c r="C97" t="n">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Luz Enith Sanchez Galeano</t>
+          <t>Daniel Alberto Orozco Orozco</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -5293,7 +5289,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>ENVIGADO</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -5311,7 +5307,7 @@
         <v>100</v>
       </c>
       <c r="L97" t="n">
-        <v>36.8</v>
+        <v>114.2</v>
       </c>
     </row>
     <row r="98">
@@ -5321,19 +5317,19 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="C98" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Yessica  Restrepo Caicedo</t>
+          <t>Luz Aida Quirama Corrales</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -5343,7 +5339,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>ENVIGADO</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -5356,12 +5352,16 @@
           <t>Sin pago (0%)</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr"/>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>El 8 inician capacitación de CVS PLUS</t>
+        </is>
+      </c>
       <c r="K98" t="n">
         <v>100</v>
       </c>
       <c r="L98" t="n">
-        <v>34.3</v>
+        <v>37</v>
       </c>
     </row>
     <row r="99">
@@ -5371,10 +5371,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C99" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Yessica  Restrepo Caicedo</t>
+          <t>Luz Aida Quirama Corrales</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>ENVIGADO</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -5411,7 +5411,7 @@
         <v>100</v>
       </c>
       <c r="L99" t="n">
-        <v>34.3</v>
+        <v>37</v>
       </c>
     </row>
     <row r="100">
@@ -5421,19 +5421,19 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="C100" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Yessica  Restrepo Caicedo</t>
+          <t>Luz Aida Quirama Corrales</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>ENVIGADO</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -5461,7 +5461,7 @@
         <v>100</v>
       </c>
       <c r="L100" t="n">
-        <v>34.3</v>
+        <v>37</v>
       </c>
     </row>
     <row r="101">
@@ -5471,10 +5471,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="C101" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Yessica  Restrepo Caicedo</t>
+          <t>Luz Aida Quirama Corrales</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>ENVIGADO</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -5511,7 +5511,7 @@
         <v>100</v>
       </c>
       <c r="L101" t="n">
-        <v>34.3</v>
+        <v>37</v>
       </c>
     </row>
     <row r="102">
@@ -5521,7 +5521,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>588</v>
+        <v>0</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
@@ -5533,7 +5533,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Yessica  Restrepo Caicedo</t>
+          <t>Luz Aida Quirama Corrales</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>ENVIGADO</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -5561,7 +5561,7 @@
         <v>100</v>
       </c>
       <c r="L102" t="n">
-        <v>34.3</v>
+        <v>37</v>
       </c>
     </row>
     <row r="103">
@@ -5571,19 +5571,19 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1765286</v>
+        <v>750000</v>
       </c>
       <c r="C103" t="n">
-        <v>424000</v>
+        <v>135000</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Yessica  Restrepo Caicedo</t>
+          <t>Luz Aida Quirama Corrales</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>ENVIGADO</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -5611,7 +5611,7 @@
         <v>100</v>
       </c>
       <c r="L103" t="n">
-        <v>34.3</v>
+        <v>37</v>
       </c>
     </row>
     <row r="104">
@@ -5621,19 +5621,19 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Lider Sara Julieth Acevedo Gutierrez</t>
+          <t>Lider Maribel Cortes Pineda</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -5661,7 +5661,7 @@
         <v>100</v>
       </c>
       <c r="L104" t="n">
-        <v>17.7</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="105">
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
@@ -5683,7 +5683,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Lider Sara Julieth Acevedo Gutierrez</t>
+          <t>Lider Maribel Cortes Pineda</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5693,7 +5693,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -5711,7 +5711,7 @@
         <v>100</v>
       </c>
       <c r="L105" t="n">
-        <v>17.7</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="106">
@@ -5721,19 +5721,19 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C106" t="n">
         <v>5</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Lider Sara Julieth Acevedo Gutierrez</t>
+          <t>Lider Maribel Cortes Pineda</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -5761,7 +5761,7 @@
         <v>100</v>
       </c>
       <c r="L106" t="n">
-        <v>17.7</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="107">
@@ -5771,10 +5771,10 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="C107" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Lider Sara Julieth Acevedo Gutierrez</t>
+          <t>Lider Maribel Cortes Pineda</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -5811,7 +5811,7 @@
         <v>100</v>
       </c>
       <c r="L107" t="n">
-        <v>17.7</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="108">
@@ -5821,7 +5821,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0</v>
+        <v>375</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Lider Sara Julieth Acevedo Gutierrez</t>
+          <t>Lider Maribel Cortes Pineda</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -5861,7 +5861,7 @@
         <v>100</v>
       </c>
       <c r="L108" t="n">
-        <v>17.7</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="109">
@@ -5871,10 +5871,10 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>1540000</v>
+        <v>1000702</v>
       </c>
       <c r="C109" t="n">
-        <v>160000</v>
+        <v>105000</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Lider Sara Julieth Acevedo Gutierrez</t>
+          <t>Lider Maribel Cortes Pineda</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -5911,7 +5911,7 @@
         <v>100</v>
       </c>
       <c r="L109" t="n">
-        <v>17.7</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="110">
@@ -5921,19 +5921,19 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C110" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>300%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Daniel Alberto Orozco Orozco</t>
+          <t>Cristian Camilo Torres Toro</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5956,16 +5956,12 @@
           <t>Sin pago (0%)</t>
         </is>
       </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>El 8 inician capacitación de CVS PLUS</t>
-        </is>
-      </c>
+      <c r="J110" t="inlineStr"/>
       <c r="K110" t="n">
         <v>100</v>
       </c>
       <c r="L110" t="n">
-        <v>114.2</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="111">
@@ -5975,19 +5971,19 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C111" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Daniel Alberto Orozco Orozco</t>
+          <t>Cristian Camilo Torres Toro</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5997,7 +5993,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -6015,7 +6011,7 @@
         <v>100</v>
       </c>
       <c r="L111" t="n">
-        <v>114.2</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="112">
@@ -6025,19 +6021,19 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C112" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Daniel Alberto Orozco Orozco</t>
+          <t>Cristian Camilo Torres Toro</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -6047,7 +6043,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -6065,7 +6061,7 @@
         <v>100</v>
       </c>
       <c r="L112" t="n">
-        <v>114.2</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="113">
@@ -6075,19 +6071,19 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="C113" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Pendiente 4 porta pre</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Daniel Alberto Orozco Orozco</t>
+          <t>Cristian Camilo Torres Toro</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -6097,7 +6093,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -6115,7 +6111,7 @@
         <v>100</v>
       </c>
       <c r="L113" t="n">
-        <v>114.2</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="114">
@@ -6125,7 +6121,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0</v>
+        <v>563</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
@@ -6137,7 +6133,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Daniel Alberto Orozco Orozco</t>
+          <t>Cristian Camilo Torres Toro</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -6147,7 +6143,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -6165,7 +6161,7 @@
         <v>100</v>
       </c>
       <c r="L114" t="n">
-        <v>114.2</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="115">
@@ -6175,19 +6171,19 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>184000</v>
+        <v>1500351</v>
       </c>
       <c r="C115" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Daniel Alberto Orozco Orozco</t>
+          <t>Cristian Camilo Torres Toro</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -6197,7 +6193,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -6215,7 +6211,7 @@
         <v>100</v>
       </c>
       <c r="L115" t="n">
-        <v>114.2</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="116">
@@ -6225,19 +6221,19 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C116" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Luz Aida Quirama Corrales</t>
+          <t>Diana Marcela Taborda Ruiz</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -6247,7 +6243,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -6262,14 +6258,14 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>El 8 inician capacitación de CVS PLUS</t>
+          <t>Inicia el 12 como reemplazó de Elizabeth</t>
         </is>
       </c>
       <c r="K116" t="n">
         <v>100</v>
       </c>
       <c r="L116" t="n">
-        <v>37</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="117">
@@ -6279,19 +6275,19 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Luz Aida Quirama Corrales</t>
+          <t>Diana Marcela Taborda Ruiz</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -6301,7 +6297,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -6319,7 +6315,7 @@
         <v>100</v>
       </c>
       <c r="L117" t="n">
-        <v>37</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="118">
@@ -6329,19 +6325,19 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C118" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Luz Aida Quirama Corrales</t>
+          <t>Diana Marcela Taborda Ruiz</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -6351,7 +6347,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -6369,7 +6365,7 @@
         <v>100</v>
       </c>
       <c r="L118" t="n">
-        <v>37</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="119">
@@ -6379,10 +6375,10 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C119" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -6391,7 +6387,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Luz Aida Quirama Corrales</t>
+          <t>Diana Marcela Taborda Ruiz</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -6401,7 +6397,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -6419,7 +6415,7 @@
         <v>100</v>
       </c>
       <c r="L119" t="n">
-        <v>37</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="120">
@@ -6429,7 +6425,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="C120" t="n">
         <v>0</v>
@@ -6441,7 +6437,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Luz Aida Quirama Corrales</t>
+          <t>Diana Marcela Taborda Ruiz</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -6451,7 +6447,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -6469,7 +6465,7 @@
         <v>100</v>
       </c>
       <c r="L120" t="n">
-        <v>37</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="121">
@@ -6479,19 +6475,19 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>750000</v>
+        <v>923509</v>
       </c>
       <c r="C121" t="n">
-        <v>135000</v>
+        <v>0</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Luz Aida Quirama Corrales</t>
+          <t>Diana Marcela Taborda Ruiz</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -6501,7 +6497,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -6519,7 +6515,2731 @@
         <v>100</v>
       </c>
       <c r="L121" t="n">
-        <v>37</v>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>POSTPAGO</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>8</v>
+      </c>
+      <c r="C122" t="n">
+        <v>9</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>112%</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Elizabeth  Quintero Mejia</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>BELLO</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Pasa a Sabaneta como reemplazó de Andrea</t>
+        </is>
+      </c>
+      <c r="K122" t="n">
+        <v>100</v>
+      </c>
+      <c r="L122" t="n">
+        <v>101.5</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>HOGAR</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>2</v>
+      </c>
+      <c r="C123" t="n">
+        <v>5</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>250%</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Elizabeth  Quintero Mejia</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>BELLO</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="n">
+        <v>100</v>
+      </c>
+      <c r="L123" t="n">
+        <v>101.5</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>TERMINALES</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>12</v>
+      </c>
+      <c r="C124" t="n">
+        <v>9</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Elizabeth  Quintero Mejia</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>BELLO</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="n">
+        <v>100</v>
+      </c>
+      <c r="L124" t="n">
+        <v>101.5</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>22</v>
+      </c>
+      <c r="C125" t="n">
+        <v>24</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Pendiente 4 porta pre</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Elizabeth  Quintero Mejia</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>BELLO</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="n">
+        <v>100</v>
+      </c>
+      <c r="L125" t="n">
+        <v>101.5</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>CVS PLUS</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>216</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Elizabeth  Quintero Mejia</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>BELLO</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="n">
+        <v>100</v>
+      </c>
+      <c r="L126" t="n">
+        <v>101.5</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>ACCESORIOS</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>576842</v>
+      </c>
+      <c r="C127" t="n">
+        <v>720000</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>125%</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Elizabeth  Quintero Mejia</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>BELLO</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="n">
+        <v>100</v>
+      </c>
+      <c r="L127" t="n">
+        <v>101.5</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>POSTPAGO</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>25</v>
+      </c>
+      <c r="C128" t="n">
+        <v>10</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>LÃ­der Sandra Arbelaez</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>SABANETA</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="n">
+        <v>100</v>
+      </c>
+      <c r="L128" t="n">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>HOGAR</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>6</v>
+      </c>
+      <c r="C129" t="n">
+        <v>3</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>LÃ­der Sandra Arbelaez</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>SABANETA</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="n">
+        <v>100</v>
+      </c>
+      <c r="L129" t="n">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>TERMINALES</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>24</v>
+      </c>
+      <c r="C130" t="n">
+        <v>1</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>LÃ­der Sandra Arbelaez</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>SABANETA</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="n">
+        <v>100</v>
+      </c>
+      <c r="L130" t="n">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>84</v>
+      </c>
+      <c r="C131" t="n">
+        <v>30</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Pendiente 4 porta pre</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>LÃ­der Sandra Arbelaez</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>SABANETA</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="n">
+        <v>100</v>
+      </c>
+      <c r="L131" t="n">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>CVS PLUS</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>600</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>LÃ­der Sandra Arbelaez</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>SABANETA</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="n">
+        <v>100</v>
+      </c>
+      <c r="L132" t="n">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>ACCESORIOS</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="C133" t="n">
+        <v>110000</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>LÃ­der Sandra Arbelaez</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>SABANETA</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="n">
+        <v>100</v>
+      </c>
+      <c r="L133" t="n">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>POSTPAGO</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>11</v>
+      </c>
+      <c r="C134" t="n">
+        <v>13</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>118%</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Andrea  Arenas Hurtado</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>SABANETA</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Vacaciones hasta el 2 de septiembre - inicia labores el 3 - pasa el 12 a Itagui</t>
+        </is>
+      </c>
+      <c r="K134" t="n">
+        <v>100</v>
+      </c>
+      <c r="L134" t="n">
+        <v>96.59999999999999</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>HOGAR</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>3</v>
+      </c>
+      <c r="C135" t="n">
+        <v>2</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Andrea  Arenas Hurtado</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>SABANETA</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="n">
+        <v>100</v>
+      </c>
+      <c r="L135" t="n">
+        <v>96.59999999999999</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>TERMINALES</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>11</v>
+      </c>
+      <c r="C136" t="n">
+        <v>13</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>118%</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Andrea  Arenas Hurtado</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>SABANETA</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="n">
+        <v>100</v>
+      </c>
+      <c r="L136" t="n">
+        <v>96.59999999999999</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>39</v>
+      </c>
+      <c r="C137" t="n">
+        <v>33</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Pendiente 4 porta pre</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Andrea  Arenas Hurtado</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>SABANETA</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="n">
+        <v>100</v>
+      </c>
+      <c r="L137" t="n">
+        <v>96.59999999999999</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>CVS PLUS</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>277</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Andrea  Arenas Hurtado</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>SABANETA</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="n">
+        <v>100</v>
+      </c>
+      <c r="L138" t="n">
+        <v>96.59999999999999</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>ACCESORIOS</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>738462</v>
+      </c>
+      <c r="C139" t="n">
+        <v>175000</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Andrea  Arenas Hurtado</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>SABANETA</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="n">
+        <v>100</v>
+      </c>
+      <c r="L139" t="n">
+        <v>96.59999999999999</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>POSTPAGO</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>23</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Elizabeth  Quintero Mejia</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>SABANETA</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Reemplaza Andrea</t>
+        </is>
+      </c>
+      <c r="K140" t="n">
+        <v>100</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>HOGAR</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>5</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Elizabeth  Quintero Mejia</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>SABANETA</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="n">
+        <v>100</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>TERMINALES</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>22</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Elizabeth  Quintero Mejia</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>SABANETA</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="n">
+        <v>100</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>78</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Pendiente 4 porta pre</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Elizabeth  Quintero Mejia</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>SABANETA</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="n">
+        <v>100</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>CVS PLUS</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>554</v>
+      </c>
+      <c r="C144" t="n">
+        <v>0</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Elizabeth  Quintero Mejia</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>SABANETA</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="n">
+        <v>100</v>
+      </c>
+      <c r="L144" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>ACCESORIOS</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>1476923</v>
+      </c>
+      <c r="C145" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Elizabeth  Quintero Mejia</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>SABANETA</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="n">
+        <v>100</v>
+      </c>
+      <c r="L145" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>POSTPAGO</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>3</v>
+      </c>
+      <c r="C146" t="n">
+        <v>3</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Luz Enith Sanchez Galeano</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>SABANETA</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Cubre 2 días Andrea</t>
+        </is>
+      </c>
+      <c r="K146" t="n">
+        <v>100</v>
+      </c>
+      <c r="L146" t="n">
+        <v>43.1</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>HOGAR</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>1</v>
+      </c>
+      <c r="C147" t="n">
+        <v>0</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Luz Enith Sanchez Galeano</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>SABANETA</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="n">
+        <v>100</v>
+      </c>
+      <c r="L147" t="n">
+        <v>43.1</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>TERMINALES</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>3</v>
+      </c>
+      <c r="C148" t="n">
+        <v>0</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Luz Enith Sanchez Galeano</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>SABANETA</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="n">
+        <v>100</v>
+      </c>
+      <c r="L148" t="n">
+        <v>43.1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>10</v>
+      </c>
+      <c r="C149" t="n">
+        <v>8</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Pendiente 4 porta pre</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Luz Enith Sanchez Galeano</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>SABANETA</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="n">
+        <v>100</v>
+      </c>
+      <c r="L149" t="n">
+        <v>43.1</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>CVS PLUS</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>69</v>
+      </c>
+      <c r="C150" t="n">
+        <v>0</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Luz Enith Sanchez Galeano</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>SABANETA</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="n">
+        <v>100</v>
+      </c>
+      <c r="L150" t="n">
+        <v>43.1</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>ACCESORIOS</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>184615</v>
+      </c>
+      <c r="C151" t="n">
+        <v>0</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Luz Enith Sanchez Galeano</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>SABANETA</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="n">
+        <v>100</v>
+      </c>
+      <c r="L151" t="n">
+        <v>43.1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>POSTPAGO</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>13</v>
+      </c>
+      <c r="C152" t="n">
+        <v>7</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Lider Marcela Valencia Tabares</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>ITAGUI</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="n">
+        <v>100</v>
+      </c>
+      <c r="L152" t="n">
+        <v>39.8</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>HOGAR</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>3</v>
+      </c>
+      <c r="C153" t="n">
+        <v>3</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Lider Marcela Valencia Tabares</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>ITAGUI</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="n">
+        <v>100</v>
+      </c>
+      <c r="L153" t="n">
+        <v>39.8</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>TERMINALES</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>19</v>
+      </c>
+      <c r="C154" t="n">
+        <v>3</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Lider Marcela Valencia Tabares</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>ITAGUI</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="n">
+        <v>100</v>
+      </c>
+      <c r="L154" t="n">
+        <v>39.8</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>45</v>
+      </c>
+      <c r="C155" t="n">
+        <v>30</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Pendiente 4 porta pre</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Lider Marcela Valencia Tabares</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>ITAGUI</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="n">
+        <v>100</v>
+      </c>
+      <c r="L155" t="n">
+        <v>39.8</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>CVS PLUS</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>375</v>
+      </c>
+      <c r="C156" t="n">
+        <v>0</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Lider Marcela Valencia Tabares</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>ITAGUI</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="n">
+        <v>100</v>
+      </c>
+      <c r="L156" t="n">
+        <v>39.8</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>ACCESORIOS</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>0</v>
+      </c>
+      <c r="C157" t="n">
+        <v>0</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Lider Marcela Valencia Tabares</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>ITAGUI</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="n">
+        <v>100</v>
+      </c>
+      <c r="L157" t="n">
+        <v>39.8</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>POSTPAGO</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>12</v>
+      </c>
+      <c r="C158" t="n">
+        <v>1</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Andrea  Arenas Hurtado</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>ITAGUI</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>Inicia el 12 como remplazó de Diana</t>
+        </is>
+      </c>
+      <c r="K158" t="n">
+        <v>100</v>
+      </c>
+      <c r="L158" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>HOGAR</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>3</v>
+      </c>
+      <c r="C159" t="n">
+        <v>0</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Andrea  Arenas Hurtado</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>ITAGUI</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="n">
+        <v>100</v>
+      </c>
+      <c r="L159" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>TERMINALES</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>17</v>
+      </c>
+      <c r="C160" t="n">
+        <v>2</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Andrea  Arenas Hurtado</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>ITAGUI</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="n">
+        <v>100</v>
+      </c>
+      <c r="L160" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>42</v>
+      </c>
+      <c r="C161" t="n">
+        <v>2</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Pendiente 4 porta pre</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Andrea  Arenas Hurtado</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>ITAGUI</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="n">
+        <v>100</v>
+      </c>
+      <c r="L161" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>CVS PLUS</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>346</v>
+      </c>
+      <c r="C162" t="n">
+        <v>0</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Andrea  Arenas Hurtado</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>ITAGUI</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="n">
+        <v>100</v>
+      </c>
+      <c r="L162" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>ACCESORIOS</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>0</v>
+      </c>
+      <c r="C163" t="n">
+        <v>0</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Andrea  Arenas Hurtado</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>ITAGUI</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="n">
+        <v>100</v>
+      </c>
+      <c r="L163" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>POSTPAGO</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>19</v>
+      </c>
+      <c r="C164" t="n">
+        <v>7</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Dailyn Del Valle Alvarez Rueda</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>ITAGUI</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="n">
+        <v>100</v>
+      </c>
+      <c r="L164" t="n">
+        <v>44.4</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>HOGAR</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>5</v>
+      </c>
+      <c r="C165" t="n">
+        <v>3</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Dailyn Del Valle Alvarez Rueda</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>ITAGUI</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="n">
+        <v>100</v>
+      </c>
+      <c r="L165" t="n">
+        <v>44.4</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>TERMINALES</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>28</v>
+      </c>
+      <c r="C166" t="n">
+        <v>9</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Dailyn Del Valle Alvarez Rueda</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>ITAGUI</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="n">
+        <v>100</v>
+      </c>
+      <c r="L166" t="n">
+        <v>44.4</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>68</v>
+      </c>
+      <c r="C167" t="n">
+        <v>27</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Pendiente 4 porta pre</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Dailyn Del Valle Alvarez Rueda</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>ITAGUI</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="n">
+        <v>100</v>
+      </c>
+      <c r="L167" t="n">
+        <v>44.4</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>CVS PLUS</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>563</v>
+      </c>
+      <c r="C168" t="n">
+        <v>0</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Dailyn Del Valle Alvarez Rueda</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>ITAGUI</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="n">
+        <v>100</v>
+      </c>
+      <c r="L168" t="n">
+        <v>44.4</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>ACCESORIOS</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>0</v>
+      </c>
+      <c r="C169" t="n">
+        <v>0</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Dailyn Del Valle Alvarez Rueda</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>ITAGUI</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="n">
+        <v>100</v>
+      </c>
+      <c r="L169" t="n">
+        <v>44.4</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>POSTPAGO</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>7</v>
+      </c>
+      <c r="C170" t="n">
+        <v>14</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>200%</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Diana Marcela Taborda Ruiz</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>ITAGUI</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El 12 pasa a Bello </t>
+        </is>
+      </c>
+      <c r="K170" t="n">
+        <v>100</v>
+      </c>
+      <c r="L170" t="n">
+        <v>114.1</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>HOGAR</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>2</v>
+      </c>
+      <c r="C171" t="n">
+        <v>4</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>200%</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Diana Marcela Taborda Ruiz</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>ITAGUI</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="n">
+        <v>100</v>
+      </c>
+      <c r="L171" t="n">
+        <v>114.1</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>TERMINALES</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>11</v>
+      </c>
+      <c r="C172" t="n">
+        <v>8</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Diana Marcela Taborda Ruiz</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>ITAGUI</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="n">
+        <v>100</v>
+      </c>
+      <c r="L172" t="n">
+        <v>114.1</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>26</v>
+      </c>
+      <c r="C173" t="n">
+        <v>18</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Pendiente 4 porta pre</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Diana Marcela Taborda Ruiz</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>ITAGUI</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="n">
+        <v>100</v>
+      </c>
+      <c r="L173" t="n">
+        <v>114.1</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>CVS PLUS</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>217</v>
+      </c>
+      <c r="C174" t="n">
+        <v>0</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Diana Marcela Taborda Ruiz</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>ITAGUI</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="n">
+        <v>100</v>
+      </c>
+      <c r="L174" t="n">
+        <v>114.1</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>ACCESORIOS</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>0</v>
+      </c>
+      <c r="C175" t="n">
+        <v>0</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Diana Marcela Taborda Ruiz</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>ITAGUI</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="n">
+        <v>100</v>
+      </c>
+      <c r="L175" t="n">
+        <v>114.1</v>
       </c>
     </row>
   </sheetData>

--- a/data/historico_comisiones.xlsx
+++ b/data/historico_comisiones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L175"/>
+  <dimension ref="A1:L223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,19 +497,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Dayanis  Celsa Gamarra</t>
+          <t>Eduar Alonso Olaya Estrada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -519,7 +519,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>EL BAGRE</t>
+          <t>GIRARDOTA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -532,12 +532,16 @@
           <t>Sin pago (0%)</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Mes de gracia</t>
+        </is>
+      </c>
       <c r="K2" t="n">
         <v>100</v>
       </c>
       <c r="L2" t="n">
-        <v>21.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="3">
@@ -547,7 +551,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -559,7 +563,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dayanis  Celsa Gamarra</t>
+          <t>Eduar Alonso Olaya Estrada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -569,7 +573,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>EL BAGRE</t>
+          <t>GIRARDOTA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -587,7 +591,7 @@
         <v>100</v>
       </c>
       <c r="L3" t="n">
-        <v>21.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="4">
@@ -597,19 +601,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dayanis  Celsa Gamarra</t>
+          <t>Eduar Alonso Olaya Estrada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -619,7 +623,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>EL BAGRE</t>
+          <t>GIRARDOTA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -637,7 +641,7 @@
         <v>100</v>
       </c>
       <c r="L4" t="n">
-        <v>21.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="5">
@@ -647,10 +651,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C5" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -659,7 +663,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dayanis  Celsa Gamarra</t>
+          <t>Eduar Alonso Olaya Estrada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -669,7 +673,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>EL BAGRE</t>
+          <t>GIRARDOTA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,7 +691,7 @@
         <v>100</v>
       </c>
       <c r="L5" t="n">
-        <v>21.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="6">
@@ -697,7 +701,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>401</v>
+        <v>480</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -709,7 +713,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dayanis  Celsa Gamarra</t>
+          <t>Eduar Alonso Olaya Estrada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -719,7 +723,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>EL BAGRE</t>
+          <t>GIRARDOTA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -737,7 +741,7 @@
         <v>100</v>
       </c>
       <c r="L6" t="n">
-        <v>21.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="7">
@@ -747,19 +751,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2005714</v>
+        <v>2200000</v>
       </c>
       <c r="C7" t="n">
-        <v>403000</v>
+        <v>0</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dayanis  Celsa Gamarra</t>
+          <t>Eduar Alonso Olaya Estrada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -769,7 +773,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>EL BAGRE</t>
+          <t>GIRARDOTA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -787,7 +791,7 @@
         <v>100</v>
       </c>
       <c r="L7" t="n">
-        <v>21.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="8">
@@ -797,19 +801,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>48%</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Darly Esther Sola Tarriba</t>
+          <t>Narelig Alejandra GarcÃ­a Ramirez</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -819,7 +823,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>EL BAGRE</t>
+          <t>GIRARDOTA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -832,16 +836,12 @@
           <t>Sin pago (0%)</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Vacaciones hasta el 3 de septiembre</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
         <v>100</v>
       </c>
       <c r="L8" t="n">
-        <v>10</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="9">
@@ -851,19 +851,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Darly Esther Sola Tarriba</t>
+          <t>Narelig Alejandra GarcÃ­a Ramirez</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>EL BAGRE</t>
+          <t>GIRARDOTA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -891,7 +891,7 @@
         <v>100</v>
       </c>
       <c r="L9" t="n">
-        <v>10</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="10">
@@ -901,19 +901,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Darly Esther Sola Tarriba</t>
+          <t>Narelig Alejandra GarcÃ­a Ramirez</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>EL BAGRE</t>
+          <t>GIRARDOTA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -941,7 +941,7 @@
         <v>100</v>
       </c>
       <c r="L10" t="n">
-        <v>10</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="11">
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Darly Esther Sola Tarriba</t>
+          <t>Narelig Alejandra GarcÃ­a Ramirez</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>EL BAGRE</t>
+          <t>GIRARDOTA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -991,7 +991,7 @@
         <v>100</v>
       </c>
       <c r="L11" t="n">
-        <v>10</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="12">
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>498</v>
+        <v>720</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Darly Esther Sola Tarriba</t>
+          <t>Narelig Alejandra GarcÃ­a Ramirez</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>EL BAGRE</t>
+          <t>GIRARDOTA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1041,7 +1041,7 @@
         <v>100</v>
       </c>
       <c r="L12" t="n">
-        <v>10</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="13">
@@ -1051,19 +1051,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2487857</v>
+        <v>3300000</v>
       </c>
       <c r="C13" t="n">
-        <v>189900</v>
+        <v>613000</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Darly Esther Sola Tarriba</t>
+          <t>Narelig Alejandra GarcÃ­a Ramirez</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>EL BAGRE</t>
+          <t>GIRARDOTA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1091,7 +1091,7 @@
         <v>100</v>
       </c>
       <c r="L13" t="n">
-        <v>10</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="14">
@@ -1101,29 +1101,29 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jeider Alberto Moreno Solano</t>
+          <t>Lider Paola Andrea Clavijo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>EL BAGRE</t>
+          <t>ENVIGADO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1141,7 +1141,7 @@
         <v>100</v>
       </c>
       <c r="L14" t="n">
-        <v>15.6</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="15">
@@ -1151,29 +1151,29 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>180%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jeider Alberto Moreno Solano</t>
+          <t>Lider Paola Andrea Clavijo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>EL BAGRE</t>
+          <t>ENVIGADO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1191,7 +1191,7 @@
         <v>100</v>
       </c>
       <c r="L15" t="n">
-        <v>15.6</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="16">
@@ -1201,29 +1201,29 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jeider Alberto Moreno Solano</t>
+          <t>Lider Paola Andrea Clavijo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>EL BAGRE</t>
+          <t>ENVIGADO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1241,7 +1241,7 @@
         <v>100</v>
       </c>
       <c r="L16" t="n">
-        <v>15.6</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="17">
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="C17" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1263,17 +1263,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jeider Alberto Moreno Solano</t>
+          <t>Lider Paola Andrea Clavijo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>EL BAGRE</t>
+          <t>ENVIGADO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1291,7 +1291,7 @@
         <v>100</v>
       </c>
       <c r="L17" t="n">
-        <v>15.6</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="18">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>601</v>
+        <v>392</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -1313,17 +1313,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Jeider Alberto Moreno Solano</t>
+          <t>Lider Paola Andrea Clavijo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>EL BAGRE</t>
+          <t>ENVIGADO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1341,7 +1341,7 @@
         <v>100</v>
       </c>
       <c r="L18" t="n">
-        <v>15.6</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="19">
@@ -1351,29 +1351,29 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3006429</v>
+        <v>1177071</v>
       </c>
       <c r="C19" t="n">
-        <v>1183000</v>
+        <v>100000</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jeider Alberto Moreno Solano</t>
+          <t>Lider Paola Andrea Clavijo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>EL BAGRE</t>
+          <t>ENVIGADO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1391,7 +1391,7 @@
         <v>100</v>
       </c>
       <c r="L19" t="n">
-        <v>15.6</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="20">
@@ -1401,29 +1401,29 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Eduar Alonso Olaya Estrada</t>
+          <t>Luz Enith Sanchez Galeano</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>GIRARDOTA</t>
+          <t>ENVIGADO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1438,14 +1438,14 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Mes de gracia</t>
+          <t>Cubrio 2 días a la asesora Andrea Arenas en el CVS de Sabaneta por ende se promedia la meta</t>
         </is>
       </c>
       <c r="K20" t="n">
         <v>100</v>
       </c>
       <c r="L20" t="n">
-        <v>0.9</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="21">
@@ -1455,29 +1455,29 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Eduar Alonso Olaya Estrada</t>
+          <t>Luz Enith Sanchez Galeano</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>GIRARDOTA</t>
+          <t>ENVIGADO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1495,7 +1495,7 @@
         <v>100</v>
       </c>
       <c r="L21" t="n">
-        <v>0.9</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="22">
@@ -1505,29 +1505,29 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Eduar Alonso Olaya Estrada</t>
+          <t>Luz Enith Sanchez Galeano</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>GIRARDOTA</t>
+          <t>ENVIGADO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1545,7 +1545,7 @@
         <v>100</v>
       </c>
       <c r="L22" t="n">
-        <v>0.9</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="23">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1567,17 +1567,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Eduar Alonso Olaya Estrada</t>
+          <t>Luz Enith Sanchez Galeano</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>GIRARDOTA</t>
+          <t>ENVIGADO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1595,7 +1595,7 @@
         <v>100</v>
       </c>
       <c r="L23" t="n">
-        <v>0.9</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="24">
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>480</v>
+        <v>519</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -1617,17 +1617,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Eduar Alonso Olaya Estrada</t>
+          <t>Luz Enith Sanchez Galeano</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>GIRARDOTA</t>
+          <t>ENVIGADO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1645,7 +1645,7 @@
         <v>100</v>
       </c>
       <c r="L24" t="n">
-        <v>0.9</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="25">
@@ -1655,29 +1655,29 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2200000</v>
+        <v>1557643</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Eduar Alonso Olaya Estrada</t>
+          <t>Luz Enith Sanchez Galeano</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>GIRARDOTA</t>
+          <t>ENVIGADO</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1695,7 +1695,7 @@
         <v>100</v>
       </c>
       <c r="L25" t="n">
-        <v>0.9</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="26">
@@ -1705,19 +1705,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C26" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Narelig Alejandra GarcÃ­a Ramirez</t>
+          <t>Yessica  Restrepo Caicedo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>GIRARDOTA</t>
+          <t>ENVIGADO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1745,7 +1745,7 @@
         <v>100</v>
       </c>
       <c r="L26" t="n">
-        <v>25.2</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="27">
@@ -1755,19 +1755,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Narelig Alejandra GarcÃ­a Ramirez</t>
+          <t>Yessica  Restrepo Caicedo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>GIRARDOTA</t>
+          <t>ENVIGADO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1795,7 +1795,7 @@
         <v>100</v>
       </c>
       <c r="L27" t="n">
-        <v>25.2</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="28">
@@ -1805,19 +1805,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Narelig Alejandra GarcÃ­a Ramirez</t>
+          <t>Yessica  Restrepo Caicedo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>GIRARDOTA</t>
+          <t>ENVIGADO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1845,7 +1845,7 @@
         <v>100</v>
       </c>
       <c r="L28" t="n">
-        <v>25.2</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="29">
@@ -1855,10 +1855,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C29" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Narelig Alejandra GarcÃ­a Ramirez</t>
+          <t>Yessica  Restrepo Caicedo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>GIRARDOTA</t>
+          <t>ENVIGADO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1895,7 +1895,7 @@
         <v>100</v>
       </c>
       <c r="L29" t="n">
-        <v>25.2</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="30">
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>720</v>
+        <v>588</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Narelig Alejandra GarcÃ­a Ramirez</t>
+          <t>Yessica  Restrepo Caicedo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>GIRARDOTA</t>
+          <t>ENVIGADO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1945,7 +1945,7 @@
         <v>100</v>
       </c>
       <c r="L30" t="n">
-        <v>25.2</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="31">
@@ -1955,19 +1955,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3300000</v>
+        <v>1765286</v>
       </c>
       <c r="C31" t="n">
-        <v>613000</v>
+        <v>424000</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>19%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Narelig Alejandra GarcÃ­a Ramirez</t>
+          <t>Yessica  Restrepo Caicedo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>GIRARDOTA</t>
+          <t>ENVIGADO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1995,7 +1995,7 @@
         <v>100</v>
       </c>
       <c r="L31" t="n">
-        <v>25.2</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="32">
@@ -2008,16 +2008,16 @@
         <v>12</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lider Leider  Alexander Calderon</t>
+          <t>Lider Sara Julieth Acevedo Gutierrez</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2040,16 +2040,12 @@
           <t>Sin pago (0%)</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Vacaciones del 1 al  17  de septiembre</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="n">
         <v>100</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="33">
@@ -2059,7 +2055,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -2071,7 +2067,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lider Leider  Alexander Calderon</t>
+          <t>Lider Sara Julieth Acevedo Gutierrez</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2081,7 +2077,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2099,7 +2095,7 @@
         <v>100</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="34">
@@ -2109,19 +2105,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lider Leider  Alexander Calderon</t>
+          <t>Lider Sara Julieth Acevedo Gutierrez</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2131,7 +2127,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2149,7 +2145,7 @@
         <v>100</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="35">
@@ -2159,10 +2155,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2171,7 +2167,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lider Leider  Alexander Calderon</t>
+          <t>Lider Sara Julieth Acevedo Gutierrez</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2181,7 +2177,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2199,7 +2195,7 @@
         <v>100</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="36">
@@ -2209,7 +2205,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -2221,7 +2217,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lider Leider  Alexander Calderon</t>
+          <t>Lider Sara Julieth Acevedo Gutierrez</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2231,7 +2227,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2249,7 +2245,7 @@
         <v>100</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="37">
@@ -2259,19 +2255,19 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>592015</v>
+        <v>1540000</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>160000</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lider Leider  Alexander Calderon</t>
+          <t>Lider Sara Julieth Acevedo Gutierrez</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2281,7 +2277,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2299,7 +2295,7 @@
         <v>100</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="38">
@@ -2309,19 +2305,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>300%</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Jessica Catherine Gutierrez Garcia</t>
+          <t>Daniel Alberto Orozco Orozco</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2331,7 +2327,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2344,12 +2340,16 @@
           <t>Sin pago (0%)</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>El 8 inician capacitación de CVS PLUS</t>
+        </is>
+      </c>
       <c r="K38" t="n">
         <v>100</v>
       </c>
       <c r="L38" t="n">
-        <v>27.9</v>
+        <v>114.2</v>
       </c>
     </row>
     <row r="39">
@@ -2359,19 +2359,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Jessica Catherine Gutierrez Garcia</t>
+          <t>Daniel Alberto Orozco Orozco</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2399,7 +2399,7 @@
         <v>100</v>
       </c>
       <c r="L39" t="n">
-        <v>27.9</v>
+        <v>114.2</v>
       </c>
     </row>
     <row r="40">
@@ -2409,19 +2409,19 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="C40" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Jessica Catherine Gutierrez Garcia</t>
+          <t>Daniel Alberto Orozco Orozco</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2449,7 +2449,7 @@
         <v>100</v>
       </c>
       <c r="L40" t="n">
-        <v>27.9</v>
+        <v>114.2</v>
       </c>
     </row>
     <row r="41">
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>133</v>
+        <v>6</v>
       </c>
       <c r="C41" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Jessica Catherine Gutierrez Garcia</t>
+          <t>Daniel Alberto Orozco Orozco</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2499,7 +2499,7 @@
         <v>100</v>
       </c>
       <c r="L41" t="n">
-        <v>27.9</v>
+        <v>114.2</v>
       </c>
     </row>
     <row r="42">
@@ -2509,7 +2509,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Jessica Catherine Gutierrez Garcia</t>
+          <t>Daniel Alberto Orozco Orozco</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2549,7 +2549,7 @@
         <v>100</v>
       </c>
       <c r="L42" t="n">
-        <v>27.9</v>
+        <v>114.2</v>
       </c>
     </row>
     <row r="43">
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1866632</v>
+        <v>184000</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Jessica Catherine Gutierrez Garcia</t>
+          <t>Daniel Alberto Orozco Orozco</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2599,7 +2599,7 @@
         <v>100</v>
       </c>
       <c r="L43" t="n">
-        <v>27.9</v>
+        <v>114.2</v>
       </c>
     </row>
     <row r="44">
@@ -2609,19 +2609,19 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C44" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Julieth Acevedo Gutierrez</t>
+          <t>Luz Aida Quirama Corrales</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2644,12 +2644,16 @@
           <t>Sin pago (0%)</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>El 8 inician capacitación de CVS PLUS</t>
+        </is>
+      </c>
       <c r="K44" t="n">
         <v>100</v>
       </c>
       <c r="L44" t="n">
-        <v>13.5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="45">
@@ -2662,16 +2666,16 @@
         <v>2</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Julieth Acevedo Gutierrez</t>
+          <t>Luz Aida Quirama Corrales</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2681,7 +2685,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2699,7 +2703,7 @@
         <v>100</v>
       </c>
       <c r="L45" t="n">
-        <v>13.5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="46">
@@ -2709,19 +2713,19 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C46" t="n">
         <v>2</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Julieth Acevedo Gutierrez</t>
+          <t>Luz Aida Quirama Corrales</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2731,7 +2735,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2749,7 +2753,7 @@
         <v>100</v>
       </c>
       <c r="L46" t="n">
-        <v>13.5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="47">
@@ -2759,7 +2763,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="C47" t="n">
         <v>11</v>
@@ -2771,7 +2775,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Julieth Acevedo Gutierrez</t>
+          <t>Luz Aida Quirama Corrales</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2781,7 +2785,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2799,7 +2803,7 @@
         <v>100</v>
       </c>
       <c r="L47" t="n">
-        <v>13.5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="48">
@@ -2809,7 +2813,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -2821,7 +2825,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Julieth Acevedo Gutierrez</t>
+          <t>Luz Aida Quirama Corrales</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2831,7 +2835,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2849,7 +2853,7 @@
         <v>100</v>
       </c>
       <c r="L48" t="n">
-        <v>13.5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="49">
@@ -2859,19 +2863,19 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>808088</v>
+        <v>750000</v>
       </c>
       <c r="C49" t="n">
-        <v>20000</v>
+        <v>135000</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Julieth Acevedo Gutierrez</t>
+          <t>Luz Aida Quirama Corrales</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2881,7 +2885,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2899,7 +2903,7 @@
         <v>100</v>
       </c>
       <c r="L49" t="n">
-        <v>13.5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="50">
@@ -2909,29 +2913,29 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="C50" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>49%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Nasly Johanna Martinez Ocampo</t>
+          <t>Lider Maribel Cortes Pineda</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2949,7 +2953,7 @@
         <v>100</v>
       </c>
       <c r="L50" t="n">
-        <v>36.9</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="51">
@@ -2962,26 +2966,26 @@
         <v>4</v>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Nasly Johanna Martinez Ocampo</t>
+          <t>Lider Maribel Cortes Pineda</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2999,7 +3003,7 @@
         <v>100</v>
       </c>
       <c r="L51" t="n">
-        <v>36.9</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="52">
@@ -3009,29 +3013,29 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="C52" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Nasly Johanna Martinez Ocampo</t>
+          <t>Lider Maribel Cortes Pineda</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3049,7 +3053,7 @@
         <v>100</v>
       </c>
       <c r="L52" t="n">
-        <v>36.9</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="53">
@@ -3059,10 +3063,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>133</v>
+        <v>38</v>
       </c>
       <c r="C53" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3071,17 +3075,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Nasly Johanna Martinez Ocampo</t>
+          <t>Lider Maribel Cortes Pineda</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3099,7 +3103,7 @@
         <v>100</v>
       </c>
       <c r="L53" t="n">
-        <v>36.9</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="54">
@@ -3109,7 +3113,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>400</v>
+        <v>375</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
@@ -3121,17 +3125,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Nasly Johanna Martinez Ocampo</t>
+          <t>Lider Maribel Cortes Pineda</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3149,7 +3153,7 @@
         <v>100</v>
       </c>
       <c r="L54" t="n">
-        <v>36.9</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="55">
@@ -3159,29 +3163,29 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1866632</v>
+        <v>1000702</v>
       </c>
       <c r="C55" t="n">
-        <v>160000</v>
+        <v>105000</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Nasly Johanna Martinez Ocampo</t>
+          <t>Lider Maribel Cortes Pineda</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3199,7 +3203,7 @@
         <v>100</v>
       </c>
       <c r="L55" t="n">
-        <v>36.9</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="56">
@@ -3209,19 +3213,19 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="C56" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sandra Milena Carmona Galeano</t>
+          <t>Cristian Camilo Torres Toro</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3231,7 +3235,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3249,7 +3253,7 @@
         <v>100</v>
       </c>
       <c r="L56" t="n">
-        <v>19.5</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="57">
@@ -3259,19 +3263,19 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sandra Milena Carmona Galeano</t>
+          <t>Cristian Camilo Torres Toro</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3281,7 +3285,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3299,7 +3303,7 @@
         <v>100</v>
       </c>
       <c r="L57" t="n">
-        <v>19.5</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="58">
@@ -3309,19 +3313,19 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="C58" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sandra Milena Carmona Galeano</t>
+          <t>Cristian Camilo Torres Toro</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3331,7 +3335,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3349,7 +3353,7 @@
         <v>100</v>
       </c>
       <c r="L58" t="n">
-        <v>19.5</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="59">
@@ -3359,19 +3363,19 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>133</v>
+        <v>56</v>
       </c>
       <c r="C59" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Pendiente 4 porta pre</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sandra Milena Carmona Galeano</t>
+          <t>Cristian Camilo Torres Toro</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3381,7 +3385,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3399,7 +3403,7 @@
         <v>100</v>
       </c>
       <c r="L59" t="n">
-        <v>19.5</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="60">
@@ -3409,7 +3413,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>400</v>
+        <v>563</v>
       </c>
       <c r="C60" t="n">
         <v>0</v>
@@ -3421,7 +3425,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sandra Milena Carmona Galeano</t>
+          <t>Cristian Camilo Torres Toro</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3431,7 +3435,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3449,7 +3453,7 @@
         <v>100</v>
       </c>
       <c r="L60" t="n">
-        <v>19.5</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="61">
@@ -3459,19 +3463,19 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1866632</v>
+        <v>1500351</v>
       </c>
       <c r="C61" t="n">
-        <v>260000</v>
+        <v>20000</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sandra Milena Carmona Galeano</t>
+          <t>Cristian Camilo Torres Toro</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3481,7 +3485,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3499,7 +3503,7 @@
         <v>100</v>
       </c>
       <c r="L61" t="n">
-        <v>19.5</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="62">
@@ -3509,7 +3513,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="C62" t="n">
         <v>0</v>
@@ -3521,17 +3525,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kelly Yuliana Ospina Saldarriaga</t>
+          <t>Diana Marcela Taborda Ruiz</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SUPERNUMERARIO</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3544,12 +3548,16 @@
           <t>Sin pago (0%)</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Inicia el 12 como reemplazó de Elizabeth</t>
+        </is>
+      </c>
       <c r="K62" t="n">
         <v>100</v>
       </c>
       <c r="L62" t="n">
-        <v>4.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="63">
@@ -3559,7 +3567,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C63" t="n">
         <v>0</v>
@@ -3571,17 +3579,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Kelly Yuliana Ospina Saldarriaga</t>
+          <t>Diana Marcela Taborda Ruiz</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>SUPERNUMERARIO</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3599,7 +3607,7 @@
         <v>100</v>
       </c>
       <c r="L63" t="n">
-        <v>4.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="64">
@@ -3609,29 +3617,29 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kelly Yuliana Ospina Saldarriaga</t>
+          <t>Diana Marcela Taborda Ruiz</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>SUPERNUMERARIO</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3649,7 +3657,7 @@
         <v>100</v>
       </c>
       <c r="L64" t="n">
-        <v>4.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="65">
@@ -3659,10 +3667,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>133</v>
+        <v>35</v>
       </c>
       <c r="C65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -3671,17 +3679,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Kelly Yuliana Ospina Saldarriaga</t>
+          <t>Diana Marcela Taborda Ruiz</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SUPERNUMERARIO</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3699,7 +3707,7 @@
         <v>100</v>
       </c>
       <c r="L65" t="n">
-        <v>4.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="66">
@@ -3709,7 +3717,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>399</v>
+        <v>346</v>
       </c>
       <c r="C66" t="n">
         <v>0</v>
@@ -3721,17 +3729,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kelly Yuliana Ospina Saldarriaga</t>
+          <t>Diana Marcela Taborda Ruiz</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SUPERNUMERARIO</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3749,7 +3757,7 @@
         <v>100</v>
       </c>
       <c r="L66" t="n">
-        <v>4.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="67">
@@ -3759,29 +3767,29 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1862000</v>
+        <v>923509</v>
       </c>
       <c r="C67" t="n">
-        <v>95000</v>
+        <v>0</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kelly Yuliana Ospina Saldarriaga</t>
+          <t>Diana Marcela Taborda Ruiz</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SUPERNUMERARIO</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3799,7 +3807,7 @@
         <v>100</v>
       </c>
       <c r="L67" t="n">
-        <v>4.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="68">
@@ -3809,29 +3817,29 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="C68" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>112%</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Lider Paola Andrea Clavijo</t>
+          <t>Elizabeth  Quintero Mejia</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>ENVIGADO</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3844,12 +3852,16 @@
           <t>Sin pago (0%)</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Pasa a Sabaneta como reemplazó de Andrea</t>
+        </is>
+      </c>
       <c r="K68" t="n">
         <v>100</v>
       </c>
       <c r="L68" t="n">
-        <v>50.1</v>
+        <v>101.5</v>
       </c>
     </row>
     <row r="69">
@@ -3859,29 +3871,29 @@
         </is>
       </c>
       <c r="B69" t="n">
+        <v>2</v>
+      </c>
+      <c r="C69" t="n">
         <v>5</v>
       </c>
-      <c r="C69" t="n">
-        <v>9</v>
-      </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>180%</t>
+          <t>250%</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Lider Paola Andrea Clavijo</t>
+          <t>Elizabeth  Quintero Mejia</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>ENVIGADO</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3899,7 +3911,7 @@
         <v>100</v>
       </c>
       <c r="L69" t="n">
-        <v>50.1</v>
+        <v>101.5</v>
       </c>
     </row>
     <row r="70">
@@ -3909,29 +3921,29 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C70" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Lider Paola Andrea Clavijo</t>
+          <t>Elizabeth  Quintero Mejia</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>ENVIGADO</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3949,7 +3961,7 @@
         <v>100</v>
       </c>
       <c r="L70" t="n">
-        <v>50.1</v>
+        <v>101.5</v>
       </c>
     </row>
     <row r="71">
@@ -3959,10 +3971,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="C71" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -3971,17 +3983,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Lider Paola Andrea Clavijo</t>
+          <t>Elizabeth  Quintero Mejia</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>ENVIGADO</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3999,7 +4011,7 @@
         <v>100</v>
       </c>
       <c r="L71" t="n">
-        <v>50.1</v>
+        <v>101.5</v>
       </c>
     </row>
     <row r="72">
@@ -4009,7 +4021,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>392</v>
+        <v>216</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
@@ -4021,17 +4033,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Lider Paola Andrea Clavijo</t>
+          <t>Elizabeth  Quintero Mejia</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>ENVIGADO</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4049,7 +4061,7 @@
         <v>100</v>
       </c>
       <c r="L72" t="n">
-        <v>50.1</v>
+        <v>101.5</v>
       </c>
     </row>
     <row r="73">
@@ -4059,29 +4071,29 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1177071</v>
+        <v>576842</v>
       </c>
       <c r="C73" t="n">
-        <v>100000</v>
+        <v>720000</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>125%</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Lider Paola Andrea Clavijo</t>
+          <t>Elizabeth  Quintero Mejia</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>ENVIGADO</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4099,7 +4111,7 @@
         <v>100</v>
       </c>
       <c r="L73" t="n">
-        <v>50.1</v>
+        <v>101.5</v>
       </c>
     </row>
     <row r="74">
@@ -4109,29 +4121,29 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C74" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Luz Enith Sanchez Galeano</t>
+          <t>LÃ­der Sandra Arbelaez</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>ENVIGADO</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4144,16 +4156,12 @@
           <t>Sin pago (0%)</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>Cubrio 2 días a la asesora Andrea Arenas en el CVS de Sabaneta por ende se promedia la meta</t>
-        </is>
-      </c>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="n">
         <v>100</v>
       </c>
       <c r="L74" t="n">
-        <v>36.8</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="75">
@@ -4163,29 +4171,29 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C75" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Luz Enith Sanchez Galeano</t>
+          <t>LÃ­der Sandra Arbelaez</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>ENVIGADO</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -4203,7 +4211,7 @@
         <v>100</v>
       </c>
       <c r="L75" t="n">
-        <v>36.8</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="76">
@@ -4213,29 +4221,29 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C76" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Luz Enith Sanchez Galeano</t>
+          <t>LÃ­der Sandra Arbelaez</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>ENVIGADO</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4253,7 +4261,7 @@
         <v>100</v>
       </c>
       <c r="L76" t="n">
-        <v>36.8</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="77">
@@ -4263,10 +4271,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="C77" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -4275,17 +4283,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Luz Enith Sanchez Galeano</t>
+          <t>LÃ­der Sandra Arbelaez</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>ENVIGADO</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4303,7 +4311,7 @@
         <v>100</v>
       </c>
       <c r="L77" t="n">
-        <v>36.8</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="78">
@@ -4313,7 +4321,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>519</v>
+        <v>600</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
@@ -4325,17 +4333,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Luz Enith Sanchez Galeano</t>
+          <t>LÃ­der Sandra Arbelaez</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>ENVIGADO</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4353,7 +4361,7 @@
         <v>100</v>
       </c>
       <c r="L78" t="n">
-        <v>36.8</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="79">
@@ -4363,29 +4371,29 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1557643</v>
+        <v>1600000</v>
       </c>
       <c r="C79" t="n">
-        <v>250000</v>
+        <v>110000</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Luz Enith Sanchez Galeano</t>
+          <t>LÃ­der Sandra Arbelaez</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>ENVIGADO</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4403,7 +4411,7 @@
         <v>100</v>
       </c>
       <c r="L79" t="n">
-        <v>36.8</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="80">
@@ -4413,19 +4421,19 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C80" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>118%</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Yessica  Restrepo Caicedo</t>
+          <t>Andrea  Arenas Hurtado</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4435,7 +4443,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>ENVIGADO</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4448,12 +4456,16 @@
           <t>Sin pago (0%)</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Vacaciones hasta el 2 de septiembre - inicia labores el 3 - pasa el 12 a Itagui</t>
+        </is>
+      </c>
       <c r="K80" t="n">
         <v>100</v>
       </c>
       <c r="L80" t="n">
-        <v>34.3</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="81">
@@ -4463,19 +4475,19 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C81" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Yessica  Restrepo Caicedo</t>
+          <t>Andrea  Arenas Hurtado</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4485,7 +4497,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>ENVIGADO</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4503,7 +4515,7 @@
         <v>100</v>
       </c>
       <c r="L81" t="n">
-        <v>34.3</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="82">
@@ -4513,19 +4525,19 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="C82" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>118%</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Yessica  Restrepo Caicedo</t>
+          <t>Andrea  Arenas Hurtado</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4535,7 +4547,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>ENVIGADO</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4553,7 +4565,7 @@
         <v>100</v>
       </c>
       <c r="L82" t="n">
-        <v>34.3</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="83">
@@ -4563,10 +4575,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="C83" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -4575,7 +4587,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Yessica  Restrepo Caicedo</t>
+          <t>Andrea  Arenas Hurtado</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4585,7 +4597,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>ENVIGADO</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4603,7 +4615,7 @@
         <v>100</v>
       </c>
       <c r="L83" t="n">
-        <v>34.3</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="84">
@@ -4613,7 +4625,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>588</v>
+        <v>277</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
@@ -4625,7 +4637,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Yessica  Restrepo Caicedo</t>
+          <t>Andrea  Arenas Hurtado</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4635,7 +4647,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>ENVIGADO</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4653,7 +4665,7 @@
         <v>100</v>
       </c>
       <c r="L84" t="n">
-        <v>34.3</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="85">
@@ -4663,10 +4675,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1765286</v>
+        <v>738462</v>
       </c>
       <c r="C85" t="n">
-        <v>424000</v>
+        <v>175000</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -4675,7 +4687,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Yessica  Restrepo Caicedo</t>
+          <t>Andrea  Arenas Hurtado</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4685,7 +4697,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>ENVIGADO</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4703,7 +4715,7 @@
         <v>100</v>
       </c>
       <c r="L85" t="n">
-        <v>34.3</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="86">
@@ -4713,29 +4725,29 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Lider Sara Julieth Acevedo Gutierrez</t>
+          <t>Elizabeth  Quintero Mejia</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4748,12 +4760,16 @@
           <t>Sin pago (0%)</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr"/>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Reemplaza Andrea</t>
+        </is>
+      </c>
       <c r="K86" t="n">
         <v>100</v>
       </c>
       <c r="L86" t="n">
-        <v>17.7</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="87">
@@ -4763,7 +4779,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -4775,17 +4791,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Lider Sara Julieth Acevedo Gutierrez</t>
+          <t>Elizabeth  Quintero Mejia</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4803,7 +4819,7 @@
         <v>100</v>
       </c>
       <c r="L87" t="n">
-        <v>17.7</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="88">
@@ -4813,29 +4829,29 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C88" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Lider Sara Julieth Acevedo Gutierrez</t>
+          <t>Elizabeth  Quintero Mejia</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4853,7 +4869,7 @@
         <v>100</v>
       </c>
       <c r="L88" t="n">
-        <v>17.7</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="89">
@@ -4863,10 +4879,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="C89" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -4875,17 +4891,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Lider Sara Julieth Acevedo Gutierrez</t>
+          <t>Elizabeth  Quintero Mejia</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4903,7 +4919,7 @@
         <v>100</v>
       </c>
       <c r="L89" t="n">
-        <v>17.7</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="90">
@@ -4913,7 +4929,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0</v>
+        <v>554</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
@@ -4925,17 +4941,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Lider Sara Julieth Acevedo Gutierrez</t>
+          <t>Elizabeth  Quintero Mejia</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4953,7 +4969,7 @@
         <v>100</v>
       </c>
       <c r="L90" t="n">
-        <v>17.7</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="91">
@@ -4963,29 +4979,29 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1540000</v>
+        <v>1476923</v>
       </c>
       <c r="C91" t="n">
-        <v>160000</v>
+        <v>0</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Lider Sara Julieth Acevedo Gutierrez</t>
+          <t>Elizabeth  Quintero Mejia</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5003,7 +5019,7 @@
         <v>100</v>
       </c>
       <c r="L91" t="n">
-        <v>17.7</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="92">
@@ -5013,19 +5029,19 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C92" t="n">
         <v>3</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>300%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Daniel Alberto Orozco Orozco</t>
+          <t>Luz Enith Sanchez Galeano</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -5035,7 +5051,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -5050,14 +5066,14 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>El 8 inician capacitación de CVS PLUS</t>
+          <t>Cubre 2 días Andrea</t>
         </is>
       </c>
       <c r="K92" t="n">
         <v>100</v>
       </c>
       <c r="L92" t="n">
-        <v>114.2</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="93">
@@ -5067,7 +5083,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
@@ -5079,7 +5095,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Daniel Alberto Orozco Orozco</t>
+          <t>Luz Enith Sanchez Galeano</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -5089,7 +5105,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -5107,7 +5123,7 @@
         <v>100</v>
       </c>
       <c r="L93" t="n">
-        <v>114.2</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="94">
@@ -5120,16 +5136,16 @@
         <v>3</v>
       </c>
       <c r="C94" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Daniel Alberto Orozco Orozco</t>
+          <t>Luz Enith Sanchez Galeano</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -5139,7 +5155,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -5157,7 +5173,7 @@
         <v>100</v>
       </c>
       <c r="L94" t="n">
-        <v>114.2</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="95">
@@ -5167,10 +5183,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C95" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -5179,7 +5195,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Daniel Alberto Orozco Orozco</t>
+          <t>Luz Enith Sanchez Galeano</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -5189,7 +5205,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -5207,7 +5223,7 @@
         <v>100</v>
       </c>
       <c r="L95" t="n">
-        <v>114.2</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="96">
@@ -5217,7 +5233,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
@@ -5229,7 +5245,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Daniel Alberto Orozco Orozco</t>
+          <t>Luz Enith Sanchez Galeano</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5239,7 +5255,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -5257,7 +5273,7 @@
         <v>100</v>
       </c>
       <c r="L96" t="n">
-        <v>114.2</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="97">
@@ -5267,7 +5283,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>184000</v>
+        <v>184615</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
@@ -5279,7 +5295,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Daniel Alberto Orozco Orozco</t>
+          <t>Luz Enith Sanchez Galeano</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -5289,7 +5305,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>SABANETA</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -5307,7 +5323,7 @@
         <v>100</v>
       </c>
       <c r="L97" t="n">
-        <v>114.2</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="98">
@@ -5317,29 +5333,29 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C98" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Luz Aida Quirama Corrales</t>
+          <t>Lider Marcela Valencia Tabares</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>ITAGUI</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -5352,16 +5368,12 @@
           <t>Sin pago (0%)</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>El 8 inician capacitación de CVS PLUS</t>
-        </is>
-      </c>
+      <c r="J98" t="inlineStr"/>
       <c r="K98" t="n">
         <v>100</v>
       </c>
       <c r="L98" t="n">
-        <v>37</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="99">
@@ -5371,29 +5383,29 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C99" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Luz Aida Quirama Corrales</t>
+          <t>Lider Marcela Valencia Tabares</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>ITAGUI</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -5411,7 +5423,7 @@
         <v>100</v>
       </c>
       <c r="L99" t="n">
-        <v>37</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="100">
@@ -5421,29 +5433,29 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Luz Aida Quirama Corrales</t>
+          <t>Lider Marcela Valencia Tabares</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>ITAGUI</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -5461,7 +5473,7 @@
         <v>100</v>
       </c>
       <c r="L100" t="n">
-        <v>37</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="101">
@@ -5471,10 +5483,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="C101" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -5483,17 +5495,17 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Luz Aida Quirama Corrales</t>
+          <t>Lider Marcela Valencia Tabares</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>ITAGUI</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -5511,7 +5523,7 @@
         <v>100</v>
       </c>
       <c r="L101" t="n">
-        <v>37</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="102">
@@ -5521,7 +5533,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0</v>
+        <v>375</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
@@ -5533,17 +5545,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Luz Aida Quirama Corrales</t>
+          <t>Lider Marcela Valencia Tabares</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>ITAGUI</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -5561,7 +5573,7 @@
         <v>100</v>
       </c>
       <c r="L102" t="n">
-        <v>37</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="103">
@@ -5571,29 +5583,29 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>750000</v>
+        <v>0</v>
       </c>
       <c r="C103" t="n">
-        <v>135000</v>
+        <v>0</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Luz Aida Quirama Corrales</t>
+          <t>Lider Marcela Valencia Tabares</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>ITAGUI</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -5611,7 +5623,7 @@
         <v>100</v>
       </c>
       <c r="L103" t="n">
-        <v>37</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="104">
@@ -5621,29 +5633,29 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Lider Maribel Cortes Pineda</t>
+          <t>Andrea  Arenas Hurtado</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>BELLO</t>
+          <t>ITAGUI</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -5656,12 +5668,16 @@
           <t>Sin pago (0%)</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr"/>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Inicia el 12 como remplazó de Diana</t>
+        </is>
+      </c>
       <c r="K104" t="n">
         <v>100</v>
       </c>
       <c r="L104" t="n">
-        <v>26.5</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="105">
@@ -5671,7 +5687,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
@@ -5683,17 +5699,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Lider Maribel Cortes Pineda</t>
+          <t>Andrea  Arenas Hurtado</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>BELLO</t>
+          <t>ITAGUI</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -5711,7 +5727,7 @@
         <v>100</v>
       </c>
       <c r="L105" t="n">
-        <v>26.5</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="106">
@@ -5721,29 +5737,29 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C106" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Lider Maribel Cortes Pineda</t>
+          <t>Andrea  Arenas Hurtado</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>BELLO</t>
+          <t>ITAGUI</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -5761,7 +5777,7 @@
         <v>100</v>
       </c>
       <c r="L106" t="n">
-        <v>26.5</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="107">
@@ -5771,10 +5787,10 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C107" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -5783,17 +5799,17 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Lider Maribel Cortes Pineda</t>
+          <t>Andrea  Arenas Hurtado</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>BELLO</t>
+          <t>ITAGUI</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -5811,7 +5827,7 @@
         <v>100</v>
       </c>
       <c r="L107" t="n">
-        <v>26.5</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="108">
@@ -5821,7 +5837,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>375</v>
+        <v>346</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -5833,17 +5849,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Lider Maribel Cortes Pineda</t>
+          <t>Andrea  Arenas Hurtado</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>BELLO</t>
+          <t>ITAGUI</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -5861,7 +5877,7 @@
         <v>100</v>
       </c>
       <c r="L108" t="n">
-        <v>26.5</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="109">
@@ -5871,29 +5887,29 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>1000702</v>
+        <v>0</v>
       </c>
       <c r="C109" t="n">
-        <v>105000</v>
+        <v>0</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Lider Maribel Cortes Pineda</t>
+          <t>Andrea  Arenas Hurtado</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>BELLO</t>
+          <t>ITAGUI</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -5911,7 +5927,7 @@
         <v>100</v>
       </c>
       <c r="L109" t="n">
-        <v>26.5</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="110">
@@ -5921,19 +5937,19 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C110" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>37%</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cristian Camilo Torres Toro</t>
+          <t>Dailyn Del Valle Alvarez Rueda</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5943,7 +5959,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>BELLO</t>
+          <t>ITAGUI</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5961,7 +5977,7 @@
         <v>100</v>
       </c>
       <c r="L110" t="n">
-        <v>38.6</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="111">
@@ -5983,7 +5999,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Cristian Camilo Torres Toro</t>
+          <t>Dailyn Del Valle Alvarez Rueda</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5993,7 +6009,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>BELLO</t>
+          <t>ITAGUI</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -6011,7 +6027,7 @@
         <v>100</v>
       </c>
       <c r="L111" t="n">
-        <v>38.6</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="112">
@@ -6021,19 +6037,19 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C112" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Cristian Camilo Torres Toro</t>
+          <t>Dailyn Del Valle Alvarez Rueda</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -6043,7 +6059,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>BELLO</t>
+          <t>ITAGUI</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -6061,7 +6077,7 @@
         <v>100</v>
       </c>
       <c r="L112" t="n">
-        <v>38.6</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="113">
@@ -6071,19 +6087,19 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C113" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>Pendiente 4 porta pre</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Cristian Camilo Torres Toro</t>
+          <t>Dailyn Del Valle Alvarez Rueda</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -6093,7 +6109,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>BELLO</t>
+          <t>ITAGUI</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -6111,7 +6127,7 @@
         <v>100</v>
       </c>
       <c r="L113" t="n">
-        <v>38.6</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="114">
@@ -6133,7 +6149,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Cristian Camilo Torres Toro</t>
+          <t>Dailyn Del Valle Alvarez Rueda</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -6143,7 +6159,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>BELLO</t>
+          <t>ITAGUI</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -6161,7 +6177,7 @@
         <v>100</v>
       </c>
       <c r="L114" t="n">
-        <v>38.6</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="115">
@@ -6171,19 +6187,19 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>1500351</v>
+        <v>0</v>
       </c>
       <c r="C115" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Cristian Camilo Torres Toro</t>
+          <t>Dailyn Del Valle Alvarez Rueda</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -6193,7 +6209,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>BELLO</t>
+          <t>ITAGUI</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -6211,7 +6227,7 @@
         <v>100</v>
       </c>
       <c r="L115" t="n">
-        <v>38.6</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="116">
@@ -6221,14 +6237,14 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C116" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>200%</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -6243,7 +6259,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>BELLO</t>
+          <t>ITAGUI</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -6258,14 +6274,14 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Inicia el 12 como reemplazó de Elizabeth</t>
+          <t xml:space="preserve">El 12 pasa a Bello </t>
         </is>
       </c>
       <c r="K116" t="n">
         <v>100</v>
       </c>
       <c r="L116" t="n">
-        <v>0.2</v>
+        <v>114.1</v>
       </c>
     </row>
     <row r="117">
@@ -6275,14 +6291,14 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C117" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>200%</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -6297,7 +6313,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>BELLO</t>
+          <t>ITAGUI</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -6315,7 +6331,7 @@
         <v>100</v>
       </c>
       <c r="L117" t="n">
-        <v>0.2</v>
+        <v>114.1</v>
       </c>
     </row>
     <row r="118">
@@ -6325,14 +6341,14 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C118" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -6347,7 +6363,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>BELLO</t>
+          <t>ITAGUI</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -6365,7 +6381,7 @@
         <v>100</v>
       </c>
       <c r="L118" t="n">
-        <v>0.2</v>
+        <v>114.1</v>
       </c>
     </row>
     <row r="119">
@@ -6375,10 +6391,10 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C119" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -6397,7 +6413,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>BELLO</t>
+          <t>ITAGUI</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -6415,7 +6431,7 @@
         <v>100</v>
       </c>
       <c r="L119" t="n">
-        <v>0.2</v>
+        <v>114.1</v>
       </c>
     </row>
     <row r="120">
@@ -6425,7 +6441,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>346</v>
+        <v>217</v>
       </c>
       <c r="C120" t="n">
         <v>0</v>
@@ -6447,7 +6463,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>BELLO</t>
+          <t>ITAGUI</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -6465,7 +6481,7 @@
         <v>100</v>
       </c>
       <c r="L120" t="n">
-        <v>0.2</v>
+        <v>114.1</v>
       </c>
     </row>
     <row r="121">
@@ -6475,7 +6491,7 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>923509</v>
+        <v>0</v>
       </c>
       <c r="C121" t="n">
         <v>0</v>
@@ -6497,7 +6513,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>BELLO</t>
+          <t>ITAGUI</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -6515,7 +6531,7 @@
         <v>100</v>
       </c>
       <c r="L121" t="n">
-        <v>0.2</v>
+        <v>114.1</v>
       </c>
     </row>
     <row r="122">
@@ -6525,29 +6541,29 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C122" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>112%</t>
+          <t>92%</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Elizabeth  Quintero Mejia</t>
+          <t>Dayanis  Celsa Gamarra</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>BELLO</t>
+          <t>EL BAGRE</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -6560,16 +6576,12 @@
           <t>Sin pago (0%)</t>
         </is>
       </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>Pasa a Sabaneta como reemplazó de Andrea</t>
-        </is>
-      </c>
+      <c r="J122" t="inlineStr"/>
       <c r="K122" t="n">
         <v>100</v>
       </c>
       <c r="L122" t="n">
-        <v>101.5</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="123">
@@ -6579,29 +6591,29 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C123" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>250%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Elizabeth  Quintero Mejia</t>
+          <t>Dayanis  Celsa Gamarra</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>BELLO</t>
+          <t>EL BAGRE</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -6619,7 +6631,7 @@
         <v>100</v>
       </c>
       <c r="L123" t="n">
-        <v>101.5</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="124">
@@ -6629,29 +6641,29 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="C124" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Elizabeth  Quintero Mejia</t>
+          <t>Dayanis  Celsa Gamarra</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>BELLO</t>
+          <t>EL BAGRE</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -6669,7 +6681,7 @@
         <v>100</v>
       </c>
       <c r="L124" t="n">
-        <v>101.5</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="125">
@@ -6679,10 +6691,10 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="C125" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -6691,17 +6703,17 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Elizabeth  Quintero Mejia</t>
+          <t>Dayanis  Celsa Gamarra</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>BELLO</t>
+          <t>EL BAGRE</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -6719,7 +6731,7 @@
         <v>100</v>
       </c>
       <c r="L125" t="n">
-        <v>101.5</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="126">
@@ -6729,7 +6741,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>216</v>
+        <v>401</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
@@ -6741,17 +6753,17 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Elizabeth  Quintero Mejia</t>
+          <t>Dayanis  Celsa Gamarra</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>BELLO</t>
+          <t>EL BAGRE</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -6769,7 +6781,7 @@
         <v>100</v>
       </c>
       <c r="L126" t="n">
-        <v>101.5</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="127">
@@ -6779,29 +6791,29 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>576842</v>
+        <v>2005714</v>
       </c>
       <c r="C127" t="n">
-        <v>720000</v>
+        <v>1177000</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>125%</t>
+          <t>59%</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Elizabeth  Quintero Mejia</t>
+          <t>Dayanis  Celsa Gamarra</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>BELLO</t>
+          <t>EL BAGRE</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -6819,7 +6831,7 @@
         <v>100</v>
       </c>
       <c r="L127" t="n">
-        <v>101.5</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="128">
@@ -6829,29 +6841,29 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C128" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>LÃ­der Sandra Arbelaez</t>
+          <t>Darly Esther Sola Tarriba</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>EL BAGRE</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -6864,12 +6876,16 @@
           <t>Sin pago (0%)</t>
         </is>
       </c>
-      <c r="J128" t="inlineStr"/>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Vacaciones hasta el 3 de septiembre e incapacidad 3 días</t>
+        </is>
+      </c>
       <c r="K128" t="n">
         <v>100</v>
       </c>
       <c r="L128" t="n">
-        <v>23.9</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="129">
@@ -6879,29 +6895,29 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C129" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>LÃ­der Sandra Arbelaez</t>
+          <t>Darly Esther Sola Tarriba</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>EL BAGRE</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -6919,7 +6935,7 @@
         <v>100</v>
       </c>
       <c r="L129" t="n">
-        <v>23.9</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="130">
@@ -6929,29 +6945,29 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="C130" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>LÃ­der Sandra Arbelaez</t>
+          <t>Darly Esther Sola Tarriba</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>EL BAGRE</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -6969,7 +6985,7 @@
         <v>100</v>
       </c>
       <c r="L130" t="n">
-        <v>23.9</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="131">
@@ -6979,10 +6995,10 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="C131" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -6991,17 +7007,17 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>LÃ­der Sandra Arbelaez</t>
+          <t>Darly Esther Sola Tarriba</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>EL BAGRE</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -7019,7 +7035,7 @@
         <v>100</v>
       </c>
       <c r="L131" t="n">
-        <v>23.9</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="132">
@@ -7029,7 +7045,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>600</v>
+        <v>435</v>
       </c>
       <c r="C132" t="n">
         <v>0</v>
@@ -7041,17 +7057,17 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>LÃ­der Sandra Arbelaez</t>
+          <t>Darly Esther Sola Tarriba</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>EL BAGRE</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -7069,7 +7085,7 @@
         <v>100</v>
       </c>
       <c r="L132" t="n">
-        <v>23.9</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="133">
@@ -7079,29 +7095,29 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>1600000</v>
+        <v>2177143</v>
       </c>
       <c r="C133" t="n">
-        <v>110000</v>
+        <v>1733900</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>LÃ­der Sandra Arbelaez</t>
+          <t>Darly Esther Sola Tarriba</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>EL BAGRE</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -7119,7 +7135,7 @@
         <v>100</v>
       </c>
       <c r="L133" t="n">
-        <v>23.9</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="134">
@@ -7129,19 +7145,19 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C134" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>118%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Andrea  Arenas Hurtado</t>
+          <t>Jeider Alberto Moreno Solano</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -7151,7 +7167,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>EL BAGRE</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -7164,16 +7180,12 @@
           <t>Sin pago (0%)</t>
         </is>
       </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>Vacaciones hasta el 2 de septiembre - inicia labores el 3 - pasa el 12 a Itagui</t>
-        </is>
-      </c>
+      <c r="J134" t="inlineStr"/>
       <c r="K134" t="n">
         <v>100</v>
       </c>
       <c r="L134" t="n">
-        <v>96.59999999999999</v>
+        <v>57.4</v>
       </c>
     </row>
     <row r="135">
@@ -7183,19 +7195,19 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C135" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Andrea  Arenas Hurtado</t>
+          <t>Jeider Alberto Moreno Solano</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -7205,7 +7217,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>EL BAGRE</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -7223,7 +7235,7 @@
         <v>100</v>
       </c>
       <c r="L135" t="n">
-        <v>96.59999999999999</v>
+        <v>57.4</v>
       </c>
     </row>
     <row r="136">
@@ -7233,19 +7245,19 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="C136" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>118%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Andrea  Arenas Hurtado</t>
+          <t>Jeider Alberto Moreno Solano</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -7255,7 +7267,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>EL BAGRE</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -7273,7 +7285,7 @@
         <v>100</v>
       </c>
       <c r="L136" t="n">
-        <v>96.59999999999999</v>
+        <v>57.4</v>
       </c>
     </row>
     <row r="137">
@@ -7283,10 +7295,10 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="C137" t="n">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -7295,7 +7307,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Andrea  Arenas Hurtado</t>
+          <t>Jeider Alberto Moreno Solano</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -7305,7 +7317,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>EL BAGRE</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -7323,7 +7335,7 @@
         <v>100</v>
       </c>
       <c r="L137" t="n">
-        <v>96.59999999999999</v>
+        <v>57.4</v>
       </c>
     </row>
     <row r="138">
@@ -7333,7 +7345,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>277</v>
+        <v>601</v>
       </c>
       <c r="C138" t="n">
         <v>0</v>
@@ -7345,7 +7357,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Andrea  Arenas Hurtado</t>
+          <t>Jeider Alberto Moreno Solano</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -7355,7 +7367,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>EL BAGRE</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -7373,7 +7385,7 @@
         <v>100</v>
       </c>
       <c r="L138" t="n">
-        <v>96.59999999999999</v>
+        <v>57.4</v>
       </c>
     </row>
     <row r="139">
@@ -7383,19 +7395,19 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>738462</v>
+        <v>3006429</v>
       </c>
       <c r="C139" t="n">
-        <v>175000</v>
+        <v>1834000</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Andrea  Arenas Hurtado</t>
+          <t>Jeider Alberto Moreno Solano</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -7405,7 +7417,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>EL BAGRE</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -7423,7 +7435,7 @@
         <v>100</v>
       </c>
       <c r="L139" t="n">
-        <v>96.59999999999999</v>
+        <v>57.4</v>
       </c>
     </row>
     <row r="140">
@@ -7433,19 +7445,19 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="C140" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>150%</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Elizabeth  Quintero Mejia</t>
+          <t>Marvin Santiago Duran Arroyo</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -7455,7 +7467,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>EL BAGRE</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -7470,14 +7482,14 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Reemplaza Andrea</t>
+          <t>Nuevo y cubre la incapacidad de Darly</t>
         </is>
       </c>
       <c r="K140" t="n">
         <v>100</v>
       </c>
       <c r="L140" t="n">
-        <v>0.3</v>
+        <v>74.40000000000001</v>
       </c>
     </row>
     <row r="141">
@@ -7487,7 +7499,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
@@ -7499,7 +7511,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Elizabeth  Quintero Mejia</t>
+          <t>Marvin Santiago Duran Arroyo</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -7509,7 +7521,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>EL BAGRE</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -7527,7 +7539,7 @@
         <v>100</v>
       </c>
       <c r="L141" t="n">
-        <v>0.3</v>
+        <v>74.40000000000001</v>
       </c>
     </row>
     <row r="142">
@@ -7537,19 +7549,19 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="C142" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Elizabeth  Quintero Mejia</t>
+          <t>Marvin Santiago Duran Arroyo</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -7559,7 +7571,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>EL BAGRE</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -7577,7 +7589,7 @@
         <v>100</v>
       </c>
       <c r="L142" t="n">
-        <v>0.3</v>
+        <v>74.40000000000001</v>
       </c>
     </row>
     <row r="143">
@@ -7587,10 +7599,10 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>78</v>
+        <v>7</v>
       </c>
       <c r="C143" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -7599,7 +7611,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Elizabeth  Quintero Mejia</t>
+          <t>Marvin Santiago Duran Arroyo</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -7609,7 +7621,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>EL BAGRE</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -7627,7 +7639,7 @@
         <v>100</v>
       </c>
       <c r="L143" t="n">
-        <v>0.3</v>
+        <v>74.40000000000001</v>
       </c>
     </row>
     <row r="144">
@@ -7637,7 +7649,7 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>554</v>
+        <v>62</v>
       </c>
       <c r="C144" t="n">
         <v>0</v>
@@ -7649,7 +7661,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Elizabeth  Quintero Mejia</t>
+          <t>Marvin Santiago Duran Arroyo</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -7659,7 +7671,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>EL BAGRE</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -7677,7 +7689,7 @@
         <v>100</v>
       </c>
       <c r="L144" t="n">
-        <v>0.3</v>
+        <v>74.40000000000001</v>
       </c>
     </row>
     <row r="145">
@@ -7687,7 +7699,7 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>1476923</v>
+        <v>310714</v>
       </c>
       <c r="C145" t="n">
         <v>0</v>
@@ -7699,7 +7711,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Elizabeth  Quintero Mejia</t>
+          <t>Marvin Santiago Duran Arroyo</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -7709,7 +7721,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>EL BAGRE</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -7727,7 +7739,7 @@
         <v>100</v>
       </c>
       <c r="L145" t="n">
-        <v>0.3</v>
+        <v>74.40000000000001</v>
       </c>
     </row>
     <row r="146">
@@ -7737,29 +7749,29 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C146" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Luz Enith Sanchez Galeano</t>
+          <t>Lider Don Matias Diana Ruiz</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>DON MATIAS</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -7774,14 +7786,14 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Cubre 2 días Andrea</t>
+          <t>Vacaciones del 7 al 16 de septiembre</t>
         </is>
       </c>
       <c r="K146" t="n">
         <v>100</v>
       </c>
       <c r="L146" t="n">
-        <v>43.1</v>
+        <v>70.7</v>
       </c>
     </row>
     <row r="147">
@@ -7791,7 +7803,7 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C147" t="n">
         <v>0</v>
@@ -7803,17 +7815,17 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Luz Enith Sanchez Galeano</t>
+          <t>Lider Don Matias Diana Ruiz</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>DON MATIAS</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -7831,7 +7843,7 @@
         <v>100</v>
       </c>
       <c r="L147" t="n">
-        <v>43.1</v>
+        <v>70.7</v>
       </c>
     </row>
     <row r="148">
@@ -7841,29 +7853,29 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C148" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Luz Enith Sanchez Galeano</t>
+          <t>Lider Don Matias Diana Ruiz</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>DON MATIAS</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -7881,7 +7893,7 @@
         <v>100</v>
       </c>
       <c r="L148" t="n">
-        <v>43.1</v>
+        <v>70.7</v>
       </c>
     </row>
     <row r="149">
@@ -7891,10 +7903,10 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C149" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -7903,17 +7915,17 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Luz Enith Sanchez Galeano</t>
+          <t>Lider Don Matias Diana Ruiz</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>DON MATIAS</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -7931,7 +7943,7 @@
         <v>100</v>
       </c>
       <c r="L149" t="n">
-        <v>43.1</v>
+        <v>70.7</v>
       </c>
     </row>
     <row r="150">
@@ -7941,7 +7953,7 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>69</v>
+        <v>314</v>
       </c>
       <c r="C150" t="n">
         <v>0</v>
@@ -7953,17 +7965,17 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Luz Enith Sanchez Galeano</t>
+          <t>Lider Don Matias Diana Ruiz</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>DON MATIAS</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -7981,7 +7993,7 @@
         <v>100</v>
       </c>
       <c r="L150" t="n">
-        <v>43.1</v>
+        <v>70.7</v>
       </c>
     </row>
     <row r="151">
@@ -7991,29 +8003,29 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>184615</v>
+        <v>1306667</v>
       </c>
       <c r="C151" t="n">
-        <v>0</v>
+        <v>1228000</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Luz Enith Sanchez Galeano</t>
+          <t>Lider Don Matias Diana Ruiz</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>SABANETA</t>
+          <t>DON MATIAS</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -8031,7 +8043,7 @@
         <v>100</v>
       </c>
       <c r="L151" t="n">
-        <v>43.1</v>
+        <v>70.7</v>
       </c>
     </row>
     <row r="152">
@@ -8041,29 +8053,29 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C152" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Lider Marcela Valencia Tabares</t>
+          <t>Evelyn Daniela Lopera Lopera</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>ITAGUI</t>
+          <t>DON MATIAS</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -8081,7 +8093,7 @@
         <v>100</v>
       </c>
       <c r="L152" t="n">
-        <v>39.8</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="153">
@@ -8091,29 +8103,29 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C153" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Lider Marcela Valencia Tabares</t>
+          <t>Evelyn Daniela Lopera Lopera</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>ITAGUI</t>
+          <t>DON MATIAS</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -8131,7 +8143,7 @@
         <v>100</v>
       </c>
       <c r="L153" t="n">
-        <v>39.8</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="154">
@@ -8141,29 +8153,29 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C154" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Lider Marcela Valencia Tabares</t>
+          <t>Evelyn Daniela Lopera Lopera</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>ITAGUI</t>
+          <t>DON MATIAS</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -8181,7 +8193,7 @@
         <v>100</v>
       </c>
       <c r="L154" t="n">
-        <v>39.8</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="155">
@@ -8191,10 +8203,10 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="C155" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -8203,17 +8215,17 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Lider Marcela Valencia Tabares</t>
+          <t>Evelyn Daniela Lopera Lopera</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>ITAGUI</t>
+          <t>DON MATIAS</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -8231,7 +8243,7 @@
         <v>100</v>
       </c>
       <c r="L155" t="n">
-        <v>39.8</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="156">
@@ -8241,7 +8253,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>375</v>
+        <v>886</v>
       </c>
       <c r="C156" t="n">
         <v>0</v>
@@ -8253,17 +8265,17 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Lider Marcela Valencia Tabares</t>
+          <t>Evelyn Daniela Lopera Lopera</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>ITAGUI</t>
+          <t>DON MATIAS</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -8281,7 +8293,7 @@
         <v>100</v>
       </c>
       <c r="L156" t="n">
-        <v>39.8</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="157">
@@ -8291,29 +8303,29 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0</v>
+        <v>3693333</v>
       </c>
       <c r="C157" t="n">
-        <v>0</v>
+        <v>1933000</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>52%</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Lider Marcela Valencia Tabares</t>
+          <t>Evelyn Daniela Lopera Lopera</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>ITAGUI</t>
+          <t>DON MATIAS</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -8331,7 +8343,7 @@
         <v>100</v>
       </c>
       <c r="L157" t="n">
-        <v>39.8</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="158">
@@ -8341,29 +8353,29 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C158" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Andrea  Arenas Hurtado</t>
+          <t>Lider Paulina Andrea Zapata Jimenez</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>ITAGUI</t>
+          <t>BARBOSA</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -8376,16 +8388,12 @@
           <t>Sin pago (0%)</t>
         </is>
       </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>Inicia el 12 como remplazó de Diana</t>
-        </is>
-      </c>
+      <c r="J158" t="inlineStr"/>
       <c r="K158" t="n">
         <v>100</v>
       </c>
       <c r="L158" t="n">
-        <v>7.7</v>
+        <v>78</v>
       </c>
     </row>
     <row r="159">
@@ -8398,26 +8406,26 @@
         <v>3</v>
       </c>
       <c r="C159" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Andrea  Arenas Hurtado</t>
+          <t>Lider Paulina Andrea Zapata Jimenez</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>ITAGUI</t>
+          <t>BARBOSA</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -8435,7 +8443,7 @@
         <v>100</v>
       </c>
       <c r="L159" t="n">
-        <v>7.7</v>
+        <v>78</v>
       </c>
     </row>
     <row r="160">
@@ -8445,29 +8453,29 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C160" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Andrea  Arenas Hurtado</t>
+          <t>Lider Paulina Andrea Zapata Jimenez</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>ITAGUI</t>
+          <t>BARBOSA</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -8485,7 +8493,7 @@
         <v>100</v>
       </c>
       <c r="L160" t="n">
-        <v>7.7</v>
+        <v>78</v>
       </c>
     </row>
     <row r="161">
@@ -8495,10 +8503,10 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="C161" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -8507,17 +8515,17 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Andrea  Arenas Hurtado</t>
+          <t>Lider Paulina Andrea Zapata Jimenez</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>ITAGUI</t>
+          <t>BARBOSA</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -8535,7 +8543,7 @@
         <v>100</v>
       </c>
       <c r="L161" t="n">
-        <v>7.7</v>
+        <v>78</v>
       </c>
     </row>
     <row r="162">
@@ -8545,7 +8553,7 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>346</v>
+        <v>401</v>
       </c>
       <c r="C162" t="n">
         <v>0</v>
@@ -8557,17 +8565,17 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Andrea  Arenas Hurtado</t>
+          <t>Lider Paulina Andrea Zapata Jimenez</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>ITAGUI</t>
+          <t>BARBOSA</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -8585,7 +8593,7 @@
         <v>100</v>
       </c>
       <c r="L162" t="n">
-        <v>7.7</v>
+        <v>78</v>
       </c>
     </row>
     <row r="163">
@@ -8595,29 +8603,29 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0</v>
+        <v>2273750</v>
       </c>
       <c r="C163" t="n">
-        <v>0</v>
+        <v>2230000</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Andrea  Arenas Hurtado</t>
+          <t>Lider Paulina Andrea Zapata Jimenez</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>ITAGUI</t>
+          <t>BARBOSA</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -8635,7 +8643,7 @@
         <v>100</v>
       </c>
       <c r="L163" t="n">
-        <v>7.7</v>
+        <v>78</v>
       </c>
     </row>
     <row r="164">
@@ -8645,19 +8653,19 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C164" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Dailyn Del Valle Alvarez Rueda</t>
+          <t>Evelis Mary Ojeda Baldovino</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -8667,7 +8675,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>ITAGUI</t>
+          <t>BARBOSA</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -8685,7 +8693,7 @@
         <v>100</v>
       </c>
       <c r="L164" t="n">
-        <v>44.4</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="165">
@@ -8695,19 +8703,19 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C165" t="n">
         <v>3</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Dailyn Del Valle Alvarez Rueda</t>
+          <t>Evelis Mary Ojeda Baldovino</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -8717,7 +8725,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>ITAGUI</t>
+          <t>BARBOSA</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -8735,7 +8743,7 @@
         <v>100</v>
       </c>
       <c r="L165" t="n">
-        <v>44.4</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="166">
@@ -8745,19 +8753,19 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C166" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>59%</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Dailyn Del Valle Alvarez Rueda</t>
+          <t>Evelis Mary Ojeda Baldovino</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -8767,7 +8775,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>ITAGUI</t>
+          <t>BARBOSA</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -8785,7 +8793,7 @@
         <v>100</v>
       </c>
       <c r="L166" t="n">
-        <v>44.4</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="167">
@@ -8795,19 +8803,19 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="C167" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Pendiente 4 porta pre</t>
+          <t>92%</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Dailyn Del Valle Alvarez Rueda</t>
+          <t>Evelis Mary Ojeda Baldovino</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -8817,7 +8825,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>ITAGUI</t>
+          <t>BARBOSA</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -8835,7 +8843,7 @@
         <v>100</v>
       </c>
       <c r="L167" t="n">
-        <v>44.4</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="168">
@@ -8845,7 +8853,7 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>563</v>
+        <v>601</v>
       </c>
       <c r="C168" t="n">
         <v>0</v>
@@ -8857,7 +8865,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Dailyn Del Valle Alvarez Rueda</t>
+          <t>Evelis Mary Ojeda Baldovino</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -8867,7 +8875,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>ITAGUI</t>
+          <t>BARBOSA</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -8885,7 +8893,7 @@
         <v>100</v>
       </c>
       <c r="L168" t="n">
-        <v>44.4</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="169">
@@ -8895,19 +8903,19 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0</v>
+        <v>3407083</v>
       </c>
       <c r="C169" t="n">
-        <v>0</v>
+        <v>1274000</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>37%</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Dailyn Del Valle Alvarez Rueda</t>
+          <t>Evelis Mary Ojeda Baldovino</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -8917,7 +8925,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>ITAGUI</t>
+          <t>BARBOSA</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -8935,7 +8943,7 @@
         <v>100</v>
       </c>
       <c r="L169" t="n">
-        <v>44.4</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="170">
@@ -8945,19 +8953,19 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C170" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>200%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Diana Marcela Taborda Ruiz</t>
+          <t>Sene Del Socorro Suarez Torres</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -8967,7 +8975,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>ITAGUI</t>
+          <t>BARBOSA</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -8982,14 +8990,14 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t xml:space="preserve">El 12 pasa a Bello </t>
+          <t>Incapacidad de 3 días</t>
         </is>
       </c>
       <c r="K170" t="n">
         <v>100</v>
       </c>
       <c r="L170" t="n">
-        <v>114.1</v>
+        <v>68.40000000000001</v>
       </c>
     </row>
     <row r="171">
@@ -8999,19 +9007,19 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C171" t="n">
         <v>4</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>200%</t>
+          <t>133%</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Diana Marcela Taborda Ruiz</t>
+          <t>Sene Del Socorro Suarez Torres</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -9021,7 +9029,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>ITAGUI</t>
+          <t>BARBOSA</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -9039,7 +9047,7 @@
         <v>100</v>
       </c>
       <c r="L171" t="n">
-        <v>114.1</v>
+        <v>68.40000000000001</v>
       </c>
     </row>
     <row r="172">
@@ -9049,19 +9057,19 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C172" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Diana Marcela Taborda Ruiz</t>
+          <t>Sene Del Socorro Suarez Torres</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -9071,7 +9079,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>ITAGUI</t>
+          <t>BARBOSA</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -9089,7 +9097,7 @@
         <v>100</v>
       </c>
       <c r="L172" t="n">
-        <v>114.1</v>
+        <v>68.40000000000001</v>
       </c>
     </row>
     <row r="173">
@@ -9099,10 +9107,10 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C173" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -9111,7 +9119,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Diana Marcela Taborda Ruiz</t>
+          <t>Sene Del Socorro Suarez Torres</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -9121,7 +9129,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>ITAGUI</t>
+          <t>BARBOSA</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -9139,7 +9147,7 @@
         <v>100</v>
       </c>
       <c r="L173" t="n">
-        <v>114.1</v>
+        <v>68.40000000000001</v>
       </c>
     </row>
     <row r="174">
@@ -9149,7 +9157,7 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>217</v>
+        <v>498</v>
       </c>
       <c r="C174" t="n">
         <v>0</v>
@@ -9161,7 +9169,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Diana Marcela Taborda Ruiz</t>
+          <t>Sene Del Socorro Suarez Torres</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -9171,7 +9179,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>ITAGUI</t>
+          <t>BARBOSA</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -9189,7 +9197,7 @@
         <v>100</v>
       </c>
       <c r="L174" t="n">
-        <v>114.1</v>
+        <v>68.40000000000001</v>
       </c>
     </row>
     <row r="175">
@@ -9199,19 +9207,19 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0</v>
+        <v>2819167</v>
       </c>
       <c r="C175" t="n">
-        <v>0</v>
+        <v>2890000</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>103%</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Diana Marcela Taborda Ruiz</t>
+          <t>Sene Del Socorro Suarez Torres</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -9221,7 +9229,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>ITAGUI</t>
+          <t>BARBOSA</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -9239,7 +9247,2415 @@
         <v>100</v>
       </c>
       <c r="L175" t="n">
-        <v>114.1</v>
+        <v>68.40000000000001</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>POSTPAGO</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>12</v>
+      </c>
+      <c r="C176" t="n">
+        <v>8</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Lider Leider  Alexander Calderon</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>Vacaciones del 1 al  17  de septiembre</t>
+        </is>
+      </c>
+      <c r="K176" t="n">
+        <v>100</v>
+      </c>
+      <c r="L176" t="n">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>HOGAR</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>1</v>
+      </c>
+      <c r="C177" t="n">
+        <v>0</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Lider Leider  Alexander Calderon</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="n">
+        <v>100</v>
+      </c>
+      <c r="L177" t="n">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>TERMINALES</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>19</v>
+      </c>
+      <c r="C178" t="n">
+        <v>4</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Lider Leider  Alexander Calderon</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="n">
+        <v>100</v>
+      </c>
+      <c r="L178" t="n">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>42</v>
+      </c>
+      <c r="C179" t="n">
+        <v>22</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Pendiente 4 porta pre</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Lider Leider  Alexander Calderon</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="n">
+        <v>100</v>
+      </c>
+      <c r="L179" t="n">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>CVS PLUS</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>127</v>
+      </c>
+      <c r="C180" t="n">
+        <v>0</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Lider Leider  Alexander Calderon</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="n">
+        <v>100</v>
+      </c>
+      <c r="L180" t="n">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>ACCESORIOS</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>592015</v>
+      </c>
+      <c r="C181" t="n">
+        <v>530000</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Lider Leider  Alexander Calderon</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="n">
+        <v>100</v>
+      </c>
+      <c r="L181" t="n">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>POSTPAGO</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>37</v>
+      </c>
+      <c r="C182" t="n">
+        <v>37</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Jessica Catherine Gutierrez Garcia</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="n">
+        <v>100</v>
+      </c>
+      <c r="L182" t="n">
+        <v>86.40000000000001</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>HOGAR</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>4</v>
+      </c>
+      <c r="C183" t="n">
+        <v>5</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>125%</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Jessica Catherine Gutierrez Garcia</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="n">
+        <v>100</v>
+      </c>
+      <c r="L183" t="n">
+        <v>86.40000000000001</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>TERMINALES</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>59</v>
+      </c>
+      <c r="C184" t="n">
+        <v>45</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Jessica Catherine Gutierrez Garcia</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="n">
+        <v>100</v>
+      </c>
+      <c r="L184" t="n">
+        <v>86.40000000000001</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>133</v>
+      </c>
+      <c r="C185" t="n">
+        <v>76</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Jessica Catherine Gutierrez Garcia</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="n">
+        <v>100</v>
+      </c>
+      <c r="L185" t="n">
+        <v>86.40000000000001</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>CVS PLUS</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>400</v>
+      </c>
+      <c r="C186" t="n">
+        <v>0</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Jessica Catherine Gutierrez Garcia</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="n">
+        <v>100</v>
+      </c>
+      <c r="L186" t="n">
+        <v>86.40000000000001</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>ACCESORIOS</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>1866632</v>
+      </c>
+      <c r="C187" t="n">
+        <v>739000</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Jessica Catherine Gutierrez Garcia</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="n">
+        <v>100</v>
+      </c>
+      <c r="L187" t="n">
+        <v>86.40000000000001</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>POSTPAGO</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>37</v>
+      </c>
+      <c r="C188" t="n">
+        <v>48</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>130%</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Nasly Johanna Martinez Ocampo</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="n">
+        <v>100</v>
+      </c>
+      <c r="L188" t="n">
+        <v>102.8</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>HOGAR</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>4</v>
+      </c>
+      <c r="C189" t="n">
+        <v>2</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Nasly Johanna Martinez Ocampo</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="n">
+        <v>100</v>
+      </c>
+      <c r="L189" t="n">
+        <v>102.8</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>TERMINALES</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>59</v>
+      </c>
+      <c r="C190" t="n">
+        <v>64</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>108%</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Nasly Johanna Martinez Ocampo</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="n">
+        <v>100</v>
+      </c>
+      <c r="L190" t="n">
+        <v>102.8</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>133</v>
+      </c>
+      <c r="C191" t="n">
+        <v>112</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>84%</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Nasly Johanna Martinez Ocampo</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="n">
+        <v>100</v>
+      </c>
+      <c r="L191" t="n">
+        <v>102.8</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>CVS PLUS</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>400</v>
+      </c>
+      <c r="C192" t="n">
+        <v>0</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Nasly Johanna Martinez Ocampo</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="n">
+        <v>100</v>
+      </c>
+      <c r="L192" t="n">
+        <v>102.8</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>ACCESORIOS</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>1866632</v>
+      </c>
+      <c r="C193" t="n">
+        <v>1534400</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>82%</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Nasly Johanna Martinez Ocampo</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="n">
+        <v>100</v>
+      </c>
+      <c r="L193" t="n">
+        <v>102.8</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>POSTPAGO</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>37</v>
+      </c>
+      <c r="C194" t="n">
+        <v>27</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Sandra Milena Carmona Galeano</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="n">
+        <v>100</v>
+      </c>
+      <c r="L194" t="n">
+        <v>70.2</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>HOGAR</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>4</v>
+      </c>
+      <c r="C195" t="n">
+        <v>3</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Sandra Milena Carmona Galeano</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="n">
+        <v>100</v>
+      </c>
+      <c r="L195" t="n">
+        <v>70.2</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>TERMINALES</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>59</v>
+      </c>
+      <c r="C196" t="n">
+        <v>36</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Sandra Milena Carmona Galeano</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="n">
+        <v>100</v>
+      </c>
+      <c r="L196" t="n">
+        <v>70.2</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>133</v>
+      </c>
+      <c r="C197" t="n">
+        <v>79</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Sandra Milena Carmona Galeano</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="n">
+        <v>100</v>
+      </c>
+      <c r="L197" t="n">
+        <v>70.2</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>CVS PLUS</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>400</v>
+      </c>
+      <c r="C198" t="n">
+        <v>0</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Sandra Milena Carmona Galeano</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="n">
+        <v>100</v>
+      </c>
+      <c r="L198" t="n">
+        <v>70.2</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>ACCESORIOS</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>1866632</v>
+      </c>
+      <c r="C199" t="n">
+        <v>1314000</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Sandra Milena Carmona Galeano</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="n">
+        <v>100</v>
+      </c>
+      <c r="L199" t="n">
+        <v>70.2</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>POSTPAGO</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>16</v>
+      </c>
+      <c r="C200" t="n">
+        <v>10</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Yuliana Ospina Saldarriaga</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="n">
+        <v>100</v>
+      </c>
+      <c r="L200" t="n">
+        <v>63.6</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>HOGAR</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>2</v>
+      </c>
+      <c r="C201" t="n">
+        <v>0</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Yuliana Ospina Saldarriaga</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="n">
+        <v>100</v>
+      </c>
+      <c r="L201" t="n">
+        <v>63.6</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>TERMINALES</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>25</v>
+      </c>
+      <c r="C202" t="n">
+        <v>16</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Yuliana Ospina Saldarriaga</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="n">
+        <v>100</v>
+      </c>
+      <c r="L202" t="n">
+        <v>63.6</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>58</v>
+      </c>
+      <c r="C203" t="n">
+        <v>24</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Pendiente 4 porta pre</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Yuliana Ospina Saldarriaga</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="n">
+        <v>100</v>
+      </c>
+      <c r="L203" t="n">
+        <v>63.6</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>CVS PLUS</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>173</v>
+      </c>
+      <c r="C204" t="n">
+        <v>0</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Yuliana Ospina Saldarriaga</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="n">
+        <v>100</v>
+      </c>
+      <c r="L204" t="n">
+        <v>63.6</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>ACCESORIOS</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>808088</v>
+      </c>
+      <c r="C205" t="n">
+        <v>385000</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Yuliana Ospina Saldarriaga</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="n">
+        <v>100</v>
+      </c>
+      <c r="L205" t="n">
+        <v>63.6</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>POSTPAGO</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>37</v>
+      </c>
+      <c r="C206" t="n">
+        <v>6</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Sara Julieth Acevedo Gutierrez</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>SUPERNUMERARIO</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="n">
+        <v>100</v>
+      </c>
+      <c r="L206" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>HOGAR</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>4</v>
+      </c>
+      <c r="C207" t="n">
+        <v>0</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Sara Julieth Acevedo Gutierrez</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>SUPERNUMERARIO</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" t="n">
+        <v>100</v>
+      </c>
+      <c r="L207" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>TERMINALES</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>59</v>
+      </c>
+      <c r="C208" t="n">
+        <v>1</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Sara Julieth Acevedo Gutierrez</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>SUPERNUMERARIO</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" t="n">
+        <v>100</v>
+      </c>
+      <c r="L208" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>133</v>
+      </c>
+      <c r="C209" t="n">
+        <v>10</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Pendiente 4 porta pre</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Sara Julieth Acevedo Gutierrez</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>SUPERNUMERARIO</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr"/>
+      <c r="K209" t="n">
+        <v>100</v>
+      </c>
+      <c r="L209" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>CVS PLUS</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>399</v>
+      </c>
+      <c r="C210" t="n">
+        <v>0</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Sara Julieth Acevedo Gutierrez</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>SUPERNUMERARIO</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr"/>
+      <c r="K210" t="n">
+        <v>100</v>
+      </c>
+      <c r="L210" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>ACCESORIOS</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>1862000</v>
+      </c>
+      <c r="C211" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Sara Julieth Acevedo Gutierrez</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>SUPERNUMERARIO</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="n">
+        <v>100</v>
+      </c>
+      <c r="L211" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>POSTPAGO</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>2</v>
+      </c>
+      <c r="C212" t="n">
+        <v>1</v>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Lider Zargoza Kelly Celsa</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>ZARAGOZA</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Termina licencia de maternidad al 21, elabora 8 días </t>
+        </is>
+      </c>
+      <c r="K212" t="n">
+        <v>100</v>
+      </c>
+      <c r="L212" t="n">
+        <v>36.3</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>HOGAR</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>0</v>
+      </c>
+      <c r="C213" t="n">
+        <v>0</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Lider Zargoza Kelly Celsa</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>ZARAGOZA</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="n">
+        <v>100</v>
+      </c>
+      <c r="L213" t="n">
+        <v>36.3</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>TERMINALES</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>5</v>
+      </c>
+      <c r="C214" t="n">
+        <v>1</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Lider Zargoza Kelly Celsa</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>ZARAGOZA</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="n">
+        <v>100</v>
+      </c>
+      <c r="L214" t="n">
+        <v>36.3</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>7</v>
+      </c>
+      <c r="C215" t="n">
+        <v>2</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Pendiente 4 porta pre</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Lider Zargoza Kelly Celsa</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>ZARAGOZA</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr"/>
+      <c r="K215" t="n">
+        <v>100</v>
+      </c>
+      <c r="L215" t="n">
+        <v>36.3</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>CVS PLUS</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>92</v>
+      </c>
+      <c r="C216" t="n">
+        <v>0</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Lider Zargoza Kelly Celsa</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>ZARAGOZA</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr"/>
+      <c r="K216" t="n">
+        <v>100</v>
+      </c>
+      <c r="L216" t="n">
+        <v>36.3</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>ACCESORIOS</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>460000</v>
+      </c>
+      <c r="C217" t="n">
+        <v>2584001</v>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>562%</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Lider Zargoza Kelly Celsa</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>ZARAGOZA</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr"/>
+      <c r="K217" t="n">
+        <v>100</v>
+      </c>
+      <c r="L217" t="n">
+        <v>36.3</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>POSTPAGO</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>14</v>
+      </c>
+      <c r="C218" t="n">
+        <v>12</v>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Paola Andrea Castillo Perez</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>ZARAGOZA</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="n">
+        <v>100</v>
+      </c>
+      <c r="L218" t="n">
+        <v>110.5</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>HOGAR</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>0</v>
+      </c>
+      <c r="C219" t="n">
+        <v>0</v>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Paola Andrea Castillo Perez</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>ZARAGOZA</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr"/>
+      <c r="K219" t="n">
+        <v>100</v>
+      </c>
+      <c r="L219" t="n">
+        <v>110.5</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>TERMINALES</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>42</v>
+      </c>
+      <c r="C220" t="n">
+        <v>41</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Paola Andrea Castillo Perez</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>ZARAGOZA</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr"/>
+      <c r="K220" t="n">
+        <v>100</v>
+      </c>
+      <c r="L220" t="n">
+        <v>110.5</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>54</v>
+      </c>
+      <c r="C221" t="n">
+        <v>41</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Pendiente 4 porta pre</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Paola Andrea Castillo Perez</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>ZARAGOZA</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr"/>
+      <c r="K221" t="n">
+        <v>100</v>
+      </c>
+      <c r="L221" t="n">
+        <v>110.5</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>CVS PLUS</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>720</v>
+      </c>
+      <c r="C222" t="n">
+        <v>0</v>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Paola Andrea Castillo Perez</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>ZARAGOZA</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr"/>
+      <c r="K222" t="n">
+        <v>100</v>
+      </c>
+      <c r="L222" t="n">
+        <v>110.5</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>ACCESORIOS</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="C223" t="n">
+        <v>0</v>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Paola Andrea Castillo Perez</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>ZARAGOZA</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr"/>
+      <c r="K223" t="n">
+        <v>100</v>
+      </c>
+      <c r="L223" t="n">
+        <v>110.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/historico_comisiones.xlsx
+++ b/data/historico_comisiones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L361"/>
+  <dimension ref="A1:L391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11977,19 +11977,19 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C230" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>142%</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Lider Don Matias Diana Ruiz</t>
+          <t>Dayanis  Celsa Gamarra</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -11999,7 +11999,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>DON MATIAS</t>
+          <t>EL BAGRE</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -12017,7 +12017,7 @@
         <v>100</v>
       </c>
       <c r="L230" t="n">
-        <v>90.3</v>
+        <v>113.2</v>
       </c>
     </row>
     <row r="231">
@@ -12030,7 +12030,7 @@
         <v>0</v>
       </c>
       <c r="C231" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Lider Don Matias Diana Ruiz</t>
+          <t>Dayanis  Celsa Gamarra</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -12049,7 +12049,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>DON MATIAS</t>
+          <t>EL BAGRE</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -12067,7 +12067,7 @@
         <v>100</v>
       </c>
       <c r="L231" t="n">
-        <v>90.3</v>
+        <v>113.2</v>
       </c>
     </row>
     <row r="232">
@@ -12077,19 +12077,19 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="C232" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>128%</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Lider Don Matias Diana Ruiz</t>
+          <t>Dayanis  Celsa Gamarra</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -12099,7 +12099,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>DON MATIAS</t>
+          <t>EL BAGRE</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -12117,7 +12117,7 @@
         <v>100</v>
       </c>
       <c r="L232" t="n">
-        <v>90.3</v>
+        <v>113.2</v>
       </c>
     </row>
     <row r="233">
@@ -12127,10 +12127,10 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="C233" t="n">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Lider Don Matias Diana Ruiz</t>
+          <t>Dayanis  Celsa Gamarra</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>DON MATIAS</t>
+          <t>EL BAGRE</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -12167,7 +12167,7 @@
         <v>100</v>
       </c>
       <c r="L233" t="n">
-        <v>90.3</v>
+        <v>113.2</v>
       </c>
     </row>
     <row r="234">
@@ -12177,7 +12177,7 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>314</v>
+        <v>369</v>
       </c>
       <c r="C234" t="n">
         <v>0</v>
@@ -12189,7 +12189,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Lider Don Matias Diana Ruiz</t>
+          <t>Dayanis  Celsa Gamarra</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -12199,7 +12199,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>DON MATIAS</t>
+          <t>EL BAGRE</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -12217,7 +12217,7 @@
         <v>100</v>
       </c>
       <c r="L234" t="n">
-        <v>90.3</v>
+        <v>113.2</v>
       </c>
     </row>
     <row r="235">
@@ -12227,19 +12227,19 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>1306667</v>
+        <v>1845000</v>
       </c>
       <c r="C235" t="n">
-        <v>2127900</v>
+        <v>1658000</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>163%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Lider Don Matias Diana Ruiz</t>
+          <t>Dayanis  Celsa Gamarra</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -12249,7 +12249,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>DON MATIAS</t>
+          <t>EL BAGRE</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -12267,7 +12267,7 @@
         <v>100</v>
       </c>
       <c r="L235" t="n">
-        <v>90.3</v>
+        <v>113.2</v>
       </c>
     </row>
     <row r="236">
@@ -12277,19 +12277,19 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C236" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>115%</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Evelyn Daniela Lopera Lopera</t>
+          <t>Darly Esther Sola Tarriba</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -12299,7 +12299,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>DON MATIAS</t>
+          <t>EL BAGRE</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -12312,12 +12312,16 @@
           <t>Sin pago (0%)</t>
         </is>
       </c>
-      <c r="J236" t="inlineStr"/>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>Vacaciones hasta el 3 de septiembre e incapacidad 3 días</t>
+        </is>
+      </c>
       <c r="K236" t="n">
         <v>100</v>
       </c>
       <c r="L236" t="n">
-        <v>68.59999999999999</v>
+        <v>68.90000000000001</v>
       </c>
     </row>
     <row r="237">
@@ -12339,7 +12343,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Evelyn Daniela Lopera Lopera</t>
+          <t>Darly Esther Sola Tarriba</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -12349,7 +12353,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>DON MATIAS</t>
+          <t>EL BAGRE</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -12367,7 +12371,7 @@
         <v>100</v>
       </c>
       <c r="L237" t="n">
-        <v>68.59999999999999</v>
+        <v>68.90000000000001</v>
       </c>
     </row>
     <row r="238">
@@ -12377,19 +12381,19 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C238" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Evelyn Daniela Lopera Lopera</t>
+          <t>Darly Esther Sola Tarriba</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -12399,7 +12403,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>DON MATIAS</t>
+          <t>EL BAGRE</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -12417,7 +12421,7 @@
         <v>100</v>
       </c>
       <c r="L238" t="n">
-        <v>68.59999999999999</v>
+        <v>68.90000000000001</v>
       </c>
     </row>
     <row r="239">
@@ -12427,10 +12431,10 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C239" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -12439,7 +12443,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Evelyn Daniela Lopera Lopera</t>
+          <t>Darly Esther Sola Tarriba</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -12449,7 +12453,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>DON MATIAS</t>
+          <t>EL BAGRE</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -12467,7 +12471,7 @@
         <v>100</v>
       </c>
       <c r="L239" t="n">
-        <v>68.59999999999999</v>
+        <v>68.90000000000001</v>
       </c>
     </row>
     <row r="240">
@@ -12477,7 +12481,7 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>886</v>
+        <v>405</v>
       </c>
       <c r="C240" t="n">
         <v>0</v>
@@ -12489,7 +12493,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Evelyn Daniela Lopera Lopera</t>
+          <t>Darly Esther Sola Tarriba</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -12499,7 +12503,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>DON MATIAS</t>
+          <t>EL BAGRE</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -12517,7 +12521,7 @@
         <v>100</v>
       </c>
       <c r="L240" t="n">
-        <v>68.59999999999999</v>
+        <v>68.90000000000001</v>
       </c>
     </row>
     <row r="241">
@@ -12527,19 +12531,19 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>3693333</v>
+        <v>2022857</v>
       </c>
       <c r="C241" t="n">
-        <v>2409000</v>
+        <v>1993900</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Evelyn Daniela Lopera Lopera</t>
+          <t>Darly Esther Sola Tarriba</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -12549,7 +12553,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>DON MATIAS</t>
+          <t>EL BAGRE</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -12567,7 +12571,7 @@
         <v>100</v>
       </c>
       <c r="L241" t="n">
-        <v>68.59999999999999</v>
+        <v>68.90000000000001</v>
       </c>
     </row>
     <row r="242">
@@ -12577,24 +12581,24 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C242" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>142%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Dayanis  Celsa Gamarra</t>
+          <t>Jeider Alberto Moreno Solano</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -12617,7 +12621,7 @@
         <v>100</v>
       </c>
       <c r="L242" t="n">
-        <v>113.2</v>
+        <v>76.09999999999999</v>
       </c>
     </row>
     <row r="243">
@@ -12630,7 +12634,7 @@
         <v>0</v>
       </c>
       <c r="C243" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -12639,12 +12643,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Dayanis  Celsa Gamarra</t>
+          <t>Jeider Alberto Moreno Solano</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -12667,7 +12671,7 @@
         <v>100</v>
       </c>
       <c r="L243" t="n">
-        <v>113.2</v>
+        <v>76.09999999999999</v>
       </c>
     </row>
     <row r="244">
@@ -12677,24 +12681,24 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="C244" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>128%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Dayanis  Celsa Gamarra</t>
+          <t>Jeider Alberto Moreno Solano</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -12717,7 +12721,7 @@
         <v>100</v>
       </c>
       <c r="L244" t="n">
-        <v>113.2</v>
+        <v>76.09999999999999</v>
       </c>
     </row>
     <row r="245">
@@ -12727,10 +12731,10 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="C245" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -12739,12 +12743,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Dayanis  Celsa Gamarra</t>
+          <t>Jeider Alberto Moreno Solano</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -12767,7 +12771,7 @@
         <v>100</v>
       </c>
       <c r="L245" t="n">
-        <v>113.2</v>
+        <v>76.09999999999999</v>
       </c>
     </row>
     <row r="246">
@@ -12777,7 +12781,7 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>369</v>
+        <v>538</v>
       </c>
       <c r="C246" t="n">
         <v>0</v>
@@ -12789,12 +12793,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Dayanis  Celsa Gamarra</t>
+          <t>Jeider Alberto Moreno Solano</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -12817,7 +12821,7 @@
         <v>100</v>
       </c>
       <c r="L246" t="n">
-        <v>113.2</v>
+        <v>76.09999999999999</v>
       </c>
     </row>
     <row r="247">
@@ -12827,24 +12831,24 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>1845000</v>
+        <v>2691429</v>
       </c>
       <c r="C247" t="n">
-        <v>1658000</v>
+        <v>2496000</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Dayanis  Celsa Gamarra</t>
+          <t>Jeider Alberto Moreno Solano</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -12867,7 +12871,7 @@
         <v>100</v>
       </c>
       <c r="L247" t="n">
-        <v>113.2</v>
+        <v>76.09999999999999</v>
       </c>
     </row>
     <row r="248">
@@ -12877,19 +12881,19 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C248" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>115%</t>
+          <t>117%</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Darly Esther Sola Tarriba</t>
+          <t>Marvin Santiago Duran Arroyo</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -12914,14 +12918,14 @@
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>Vacaciones hasta el 3 de septiembre e incapacidad 3 días</t>
+          <t>Inicia el 18 con facturación</t>
         </is>
       </c>
       <c r="K248" t="n">
         <v>100</v>
       </c>
       <c r="L248" t="n">
-        <v>68.90000000000001</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="249">
@@ -12943,7 +12947,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Darly Esther Sola Tarriba</t>
+          <t>Marvin Santiago Duran Arroyo</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -12971,7 +12975,7 @@
         <v>100</v>
       </c>
       <c r="L249" t="n">
-        <v>68.90000000000001</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="250">
@@ -12981,19 +12985,19 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="C250" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Darly Esther Sola Tarriba</t>
+          <t>Marvin Santiago Duran Arroyo</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -13021,7 +13025,7 @@
         <v>100</v>
       </c>
       <c r="L250" t="n">
-        <v>68.90000000000001</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="251">
@@ -13031,10 +13035,10 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="C251" t="n">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -13043,7 +13047,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Darly Esther Sola Tarriba</t>
+          <t>Marvin Santiago Duran Arroyo</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -13071,7 +13075,7 @@
         <v>100</v>
       </c>
       <c r="L251" t="n">
-        <v>68.90000000000001</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="252">
@@ -13081,7 +13085,7 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>405</v>
+        <v>188</v>
       </c>
       <c r="C252" t="n">
         <v>0</v>
@@ -13093,7 +13097,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Darly Esther Sola Tarriba</t>
+          <t>Marvin Santiago Duran Arroyo</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -13121,7 +13125,7 @@
         <v>100</v>
       </c>
       <c r="L252" t="n">
-        <v>68.90000000000001</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="253">
@@ -13131,19 +13135,19 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>2022857</v>
+        <v>940714</v>
       </c>
       <c r="C253" t="n">
-        <v>1993900</v>
+        <v>0</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Darly Esther Sola Tarriba</t>
+          <t>Marvin Santiago Duran Arroyo</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -13171,7 +13175,7 @@
         <v>100</v>
       </c>
       <c r="L253" t="n">
-        <v>68.90000000000001</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="254">
@@ -13181,29 +13185,29 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C254" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>138%</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Jeider Alberto Moreno Solano</t>
+          <t>Lider Sara Julieth Acevedo Gutierrez</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>EL BAGRE</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -13216,12 +13220,16 @@
           <t>Sin pago (0%)</t>
         </is>
       </c>
-      <c r="J254" t="inlineStr"/>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>Inicia desde el 8 en el punto</t>
+        </is>
+      </c>
       <c r="K254" t="n">
         <v>100</v>
       </c>
       <c r="L254" t="n">
-        <v>76.09999999999999</v>
+        <v>96</v>
       </c>
     </row>
     <row r="255">
@@ -13231,29 +13239,29 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C255" t="n">
         <v>1</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Jeider Alberto Moreno Solano</t>
+          <t>Lider Sara Julieth Acevedo Gutierrez</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>EL BAGRE</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -13271,7 +13279,7 @@
         <v>100</v>
       </c>
       <c r="L255" t="n">
-        <v>76.09999999999999</v>
+        <v>96</v>
       </c>
     </row>
     <row r="256">
@@ -13281,29 +13289,29 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="C256" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Jeider Alberto Moreno Solano</t>
+          <t>Lider Sara Julieth Acevedo Gutierrez</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>EL BAGRE</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -13321,7 +13329,7 @@
         <v>100</v>
       </c>
       <c r="L256" t="n">
-        <v>76.09999999999999</v>
+        <v>96</v>
       </c>
     </row>
     <row r="257">
@@ -13331,10 +13339,10 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="C257" t="n">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -13343,17 +13351,17 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Jeider Alberto Moreno Solano</t>
+          <t>Lider Sara Julieth Acevedo Gutierrez</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>EL BAGRE</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -13371,7 +13379,7 @@
         <v>100</v>
       </c>
       <c r="L257" t="n">
-        <v>76.09999999999999</v>
+        <v>96</v>
       </c>
     </row>
     <row r="258">
@@ -13381,7 +13389,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>538</v>
+        <v>0</v>
       </c>
       <c r="C258" t="n">
         <v>0</v>
@@ -13393,17 +13401,17 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Jeider Alberto Moreno Solano</t>
+          <t>Lider Sara Julieth Acevedo Gutierrez</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>EL BAGRE</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -13421,7 +13429,7 @@
         <v>100</v>
       </c>
       <c r="L258" t="n">
-        <v>76.09999999999999</v>
+        <v>96</v>
       </c>
     </row>
     <row r="259">
@@ -13431,29 +13439,29 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>2691429</v>
+        <v>1076000</v>
       </c>
       <c r="C259" t="n">
-        <v>2496000</v>
+        <v>0</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Jeider Alberto Moreno Solano</t>
+          <t>Lider Sara Julieth Acevedo Gutierrez</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>EL BAGRE</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -13471,7 +13479,7 @@
         <v>100</v>
       </c>
       <c r="L259" t="n">
-        <v>76.09999999999999</v>
+        <v>96</v>
       </c>
     </row>
     <row r="260">
@@ -13481,19 +13489,19 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C260" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>117%</t>
+          <t>133%</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Marvin Santiago Duran Arroyo</t>
+          <t>Daniel Alberto Orozco Orozco</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -13503,7 +13511,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>EL BAGRE</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -13518,14 +13526,14 @@
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>Inicia el 18 con facturación</t>
+          <t>El 8 inician capacitación de CVS PLUS - elabora 12 días en el punto</t>
         </is>
       </c>
       <c r="K260" t="n">
         <v>100</v>
       </c>
       <c r="L260" t="n">
-        <v>66.7</v>
+        <v>77.59999999999999</v>
       </c>
     </row>
     <row r="261">
@@ -13535,7 +13543,7 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C261" t="n">
         <v>0</v>
@@ -13547,7 +13555,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Marvin Santiago Duran Arroyo</t>
+          <t>Daniel Alberto Orozco Orozco</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -13557,7 +13565,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>EL BAGRE</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -13575,7 +13583,7 @@
         <v>100</v>
       </c>
       <c r="L261" t="n">
-        <v>66.7</v>
+        <v>77.59999999999999</v>
       </c>
     </row>
     <row r="262">
@@ -13585,19 +13593,19 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C262" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Marvin Santiago Duran Arroyo</t>
+          <t>Daniel Alberto Orozco Orozco</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -13607,7 +13615,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>EL BAGRE</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -13625,7 +13633,7 @@
         <v>100</v>
       </c>
       <c r="L262" t="n">
-        <v>66.7</v>
+        <v>77.59999999999999</v>
       </c>
     </row>
     <row r="263">
@@ -13635,10 +13643,10 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C263" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -13647,7 +13655,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Marvin Santiago Duran Arroyo</t>
+          <t>Daniel Alberto Orozco Orozco</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -13657,7 +13665,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>EL BAGRE</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -13675,7 +13683,7 @@
         <v>100</v>
       </c>
       <c r="L263" t="n">
-        <v>66.7</v>
+        <v>77.59999999999999</v>
       </c>
     </row>
     <row r="264">
@@ -13685,7 +13693,7 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="C264" t="n">
         <v>0</v>
@@ -13697,7 +13705,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Marvin Santiago Duran Arroyo</t>
+          <t>Daniel Alberto Orozco Orozco</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -13707,7 +13715,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>EL BAGRE</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -13725,7 +13733,7 @@
         <v>100</v>
       </c>
       <c r="L264" t="n">
-        <v>66.7</v>
+        <v>77.59999999999999</v>
       </c>
     </row>
     <row r="265">
@@ -13735,19 +13743,19 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>940714</v>
+        <v>370000</v>
       </c>
       <c r="C265" t="n">
-        <v>0</v>
+        <v>160000</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Marvin Santiago Duran Arroyo</t>
+          <t>Daniel Alberto Orozco Orozco</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -13757,7 +13765,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>EL BAGRE</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -13775,7 +13783,7 @@
         <v>100</v>
       </c>
       <c r="L265" t="n">
-        <v>66.7</v>
+        <v>77.59999999999999</v>
       </c>
     </row>
     <row r="266">
@@ -13785,29 +13793,29 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C266" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>125%</t>
+          <t>150%</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Lider Leider  Alexander Calderon</t>
+          <t>Luz Aida Quirama Corrales</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -13822,14 +13830,14 @@
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>Vacaciones del 1 al  17  de septiembre</t>
+          <t>El 8 inician capacitación de CVS PLUS - elabora 12 días en el punto</t>
         </is>
       </c>
       <c r="K266" t="n">
         <v>100</v>
       </c>
       <c r="L266" t="n">
-        <v>80.8</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="267">
@@ -13842,26 +13850,26 @@
         <v>1</v>
       </c>
       <c r="C267" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Lider Leider  Alexander Calderon</t>
+          <t>Luz Aida Quirama Corrales</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -13879,7 +13887,7 @@
         <v>100</v>
       </c>
       <c r="L267" t="n">
-        <v>80.8</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="268">
@@ -13889,29 +13897,29 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C268" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Lider Leider  Alexander Calderon</t>
+          <t>Luz Aida Quirama Corrales</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -13929,7 +13937,7 @@
         <v>100</v>
       </c>
       <c r="L268" t="n">
-        <v>80.8</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="269">
@@ -13939,29 +13947,29 @@
         </is>
       </c>
       <c r="B269" t="n">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="C269" t="n">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>150%</t>
+          <t>Pendiente 4 porta pre</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Lider Leider  Alexander Calderon</t>
+          <t>Luz Aida Quirama Corrales</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -13979,7 +13987,7 @@
         <v>100</v>
       </c>
       <c r="L269" t="n">
-        <v>80.8</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="270">
@@ -13989,7 +13997,7 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="C270" t="n">
         <v>0</v>
@@ -14001,17 +14009,17 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Lider Leider  Alexander Calderon</t>
+          <t>Luz Aida Quirama Corrales</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -14029,7 +14037,7 @@
         <v>100</v>
       </c>
       <c r="L270" t="n">
-        <v>80.8</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="271">
@@ -14039,29 +14047,29 @@
         </is>
       </c>
       <c r="B271" t="n">
-        <v>592015</v>
+        <v>554000</v>
       </c>
       <c r="C271" t="n">
-        <v>865000</v>
+        <v>390000</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>146%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Lider Leider  Alexander Calderon</t>
+          <t>Luz Aida Quirama Corrales</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>METRO EST. SAN ANTONIO</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -14079,7 +14087,7 @@
         <v>100</v>
       </c>
       <c r="L271" t="n">
-        <v>80.8</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="272">
@@ -14089,29 +14097,29 @@
         </is>
       </c>
       <c r="B272" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="C272" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>250%</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Jessica Catherine Gutierrez Garcia</t>
+          <t>Lider Zargoza Kelly Celsa</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>ZARAGOZA</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -14124,12 +14132,16 @@
           <t>Sin pago (0%)</t>
         </is>
       </c>
-      <c r="J272" t="inlineStr"/>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>Termina licencia de maternidad el 21 - inicia labor el 22</t>
+        </is>
+      </c>
       <c r="K272" t="n">
         <v>100</v>
       </c>
       <c r="L272" t="n">
-        <v>94.59999999999999</v>
+        <v>189.4</v>
       </c>
     </row>
     <row r="273">
@@ -14139,29 +14151,29 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C273" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>125%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Jessica Catherine Gutierrez Garcia</t>
+          <t>Lider Zargoza Kelly Celsa</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>ZARAGOZA</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -14179,7 +14191,7 @@
         <v>100</v>
       </c>
       <c r="L273" t="n">
-        <v>94.59999999999999</v>
+        <v>189.4</v>
       </c>
     </row>
     <row r="274">
@@ -14189,29 +14201,29 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="C274" t="n">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>140%</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Jessica Catherine Gutierrez Garcia</t>
+          <t>Lider Zargoza Kelly Celsa</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>ZARAGOZA</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -14229,7 +14241,7 @@
         <v>100</v>
       </c>
       <c r="L274" t="n">
-        <v>94.59999999999999</v>
+        <v>189.4</v>
       </c>
     </row>
     <row r="275">
@@ -14239,29 +14251,29 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>133</v>
+        <v>7</v>
       </c>
       <c r="C275" t="n">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>Pendiente 4 porta pre</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Jessica Catherine Gutierrez Garcia</t>
+          <t>Lider Zargoza Kelly Celsa</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>ZARAGOZA</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -14279,7 +14291,7 @@
         <v>100</v>
       </c>
       <c r="L275" t="n">
-        <v>94.59999999999999</v>
+        <v>189.4</v>
       </c>
     </row>
     <row r="276">
@@ -14289,7 +14301,7 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>400</v>
+        <v>92</v>
       </c>
       <c r="C276" t="n">
         <v>0</v>
@@ -14301,17 +14313,17 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Jessica Catherine Gutierrez Garcia</t>
+          <t>Lider Zargoza Kelly Celsa</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>ZARAGOZA</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -14329,7 +14341,7 @@
         <v>100</v>
       </c>
       <c r="L276" t="n">
-        <v>94.59999999999999</v>
+        <v>189.4</v>
       </c>
     </row>
     <row r="277">
@@ -14339,29 +14351,29 @@
         </is>
       </c>
       <c r="B277" t="n">
-        <v>1866632</v>
+        <v>460000</v>
       </c>
       <c r="C277" t="n">
-        <v>899000</v>
+        <v>0</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Jessica Catherine Gutierrez Garcia</t>
+          <t>Lider Zargoza Kelly Celsa</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>ZARAGOZA</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -14379,7 +14391,7 @@
         <v>100</v>
       </c>
       <c r="L277" t="n">
-        <v>94.59999999999999</v>
+        <v>189.4</v>
       </c>
     </row>
     <row r="278">
@@ -14389,19 +14401,19 @@
         </is>
       </c>
       <c r="B278" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="C278" t="n">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>149%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Nasly Johanna Martinez Ocampo</t>
+          <t>Paola Andrea Castillo Perez</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -14411,7 +14423,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>ZARAGOZA</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -14429,7 +14441,7 @@
         <v>100</v>
       </c>
       <c r="L278" t="n">
-        <v>133.1</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="279">
@@ -14439,19 +14451,19 @@
         </is>
       </c>
       <c r="B279" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C279" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>150%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Nasly Johanna Martinez Ocampo</t>
+          <t>Paola Andrea Castillo Perez</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -14461,7 +14473,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>ZARAGOZA</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -14479,7 +14491,7 @@
         <v>100</v>
       </c>
       <c r="L279" t="n">
-        <v>133.1</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="280">
@@ -14489,19 +14501,19 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C280" t="n">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>129%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Nasly Johanna Martinez Ocampo</t>
+          <t>Paola Andrea Castillo Perez</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -14511,7 +14523,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>ZARAGOZA</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -14529,7 +14541,7 @@
         <v>100</v>
       </c>
       <c r="L280" t="n">
-        <v>133.1</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="281">
@@ -14539,19 +14551,19 @@
         </is>
       </c>
       <c r="B281" t="n">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="C281" t="n">
-        <v>140</v>
+        <v>56</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>105%</t>
+          <t>Pendiente 4 porta pre</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Nasly Johanna Martinez Ocampo</t>
+          <t>Paola Andrea Castillo Perez</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -14561,7 +14573,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>ZARAGOZA</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -14579,7 +14591,7 @@
         <v>100</v>
       </c>
       <c r="L281" t="n">
-        <v>133.1</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="282">
@@ -14589,7 +14601,7 @@
         </is>
       </c>
       <c r="B282" t="n">
-        <v>400</v>
+        <v>1108</v>
       </c>
       <c r="C282" t="n">
         <v>0</v>
@@ -14601,7 +14613,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Nasly Johanna Martinez Ocampo</t>
+          <t>Paola Andrea Castillo Perez</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -14611,7 +14623,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>ZARAGOZA</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -14629,7 +14641,7 @@
         <v>100</v>
       </c>
       <c r="L282" t="n">
-        <v>133.1</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="283">
@@ -14639,19 +14651,19 @@
         </is>
       </c>
       <c r="B283" t="n">
-        <v>1866632</v>
+        <v>5540000</v>
       </c>
       <c r="C283" t="n">
-        <v>2891400</v>
+        <v>3700001</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>155%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Nasly Johanna Martinez Ocampo</t>
+          <t>Paola Andrea Castillo Perez</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -14661,7 +14673,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>ZARAGOZA</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -14679,7 +14691,7 @@
         <v>100</v>
       </c>
       <c r="L283" t="n">
-        <v>133.1</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="284">
@@ -14689,29 +14701,29 @@
         </is>
       </c>
       <c r="B284" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="C284" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>108%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Sandra Milena Carmona Galeano</t>
+          <t>Kelly Yuliana Ospina Saldarriaga</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>SUPERNUMERARIO</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>ZARAGOZA</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -14729,7 +14741,7 @@
         <v>100</v>
       </c>
       <c r="L284" t="n">
-        <v>101.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="285">
@@ -14739,29 +14751,29 @@
         </is>
       </c>
       <c r="B285" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C285" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>150%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Sandra Milena Carmona Galeano</t>
+          <t>Kelly Yuliana Ospina Saldarriaga</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>SUPERNUMERARIO</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>ZARAGOZA</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -14779,7 +14791,7 @@
         <v>100</v>
       </c>
       <c r="L285" t="n">
-        <v>101.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="286">
@@ -14789,29 +14801,29 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C286" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Sandra Milena Carmona Galeano</t>
+          <t>Kelly Yuliana Ospina Saldarriaga</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>SUPERNUMERARIO</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>ZARAGOZA</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -14829,7 +14841,7 @@
         <v>100</v>
       </c>
       <c r="L286" t="n">
-        <v>101.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="287">
@@ -14839,29 +14851,29 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>133</v>
+        <v>54</v>
       </c>
       <c r="C287" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>Pendiente 4 porta pre</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Sandra Milena Carmona Galeano</t>
+          <t>Kelly Yuliana Ospina Saldarriaga</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>SUPERNUMERARIO</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>ZARAGOZA</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -14879,7 +14891,7 @@
         <v>100</v>
       </c>
       <c r="L287" t="n">
-        <v>101.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="288">
@@ -14889,7 +14901,7 @@
         </is>
       </c>
       <c r="B288" t="n">
-        <v>400</v>
+        <v>720</v>
       </c>
       <c r="C288" t="n">
         <v>0</v>
@@ -14901,17 +14913,17 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Sandra Milena Carmona Galeano</t>
+          <t>Kelly Yuliana Ospina Saldarriaga</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>SUPERNUMERARIO</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>ZARAGOZA</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -14929,7 +14941,7 @@
         <v>100</v>
       </c>
       <c r="L288" t="n">
-        <v>101.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="289">
@@ -14939,29 +14951,29 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>1866632</v>
+        <v>3600000</v>
       </c>
       <c r="C289" t="n">
-        <v>1374000</v>
+        <v>462000</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Sandra Milena Carmona Galeano</t>
+          <t>Kelly Yuliana Ospina Saldarriaga</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>SUPERNUMERARIO</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>ZARAGOZA</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -14979,7 +14991,7 @@
         <v>100</v>
       </c>
       <c r="L289" t="n">
-        <v>101.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="290">
@@ -14989,29 +15001,29 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C290" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Kelly Yuliana Ospina Saldarriaga</t>
+          <t>Lider Eduar Alonso Olaya Estrada</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>SUPERNUMERARIO</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>GIRARDOTA</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -15024,12 +15036,16 @@
           <t>Sin pago (0%)</t>
         </is>
       </c>
-      <c r="J290" t="inlineStr"/>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>Elabora en el punto 14 días por capacitación de CVS PLUS</t>
+        </is>
+      </c>
       <c r="K290" t="n">
         <v>100</v>
       </c>
       <c r="L290" t="n">
-        <v>63.6</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="291">
@@ -15051,17 +15067,17 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Kelly Yuliana Ospina Saldarriaga</t>
+          <t>Lider Eduar Alonso Olaya Estrada</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>SUPERNUMERARIO</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>GIRARDOTA</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -15079,7 +15095,7 @@
         <v>100</v>
       </c>
       <c r="L291" t="n">
-        <v>63.6</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="292">
@@ -15089,29 +15105,29 @@
         </is>
       </c>
       <c r="B292" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C292" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Kelly Yuliana Ospina Saldarriaga</t>
+          <t>Lider Eduar Alonso Olaya Estrada</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>SUPERNUMERARIO</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>GIRARDOTA</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -15129,7 +15145,7 @@
         <v>100</v>
       </c>
       <c r="L292" t="n">
-        <v>63.6</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="293">
@@ -15139,10 +15155,10 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="C293" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -15151,17 +15167,17 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Kelly Yuliana Ospina Saldarriaga</t>
+          <t>Lider Eduar Alonso Olaya Estrada</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>SUPERNUMERARIO</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>GIRARDOTA</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -15179,7 +15195,7 @@
         <v>100</v>
       </c>
       <c r="L293" t="n">
-        <v>63.6</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="294">
@@ -15189,7 +15205,7 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>173</v>
+        <v>259</v>
       </c>
       <c r="C294" t="n">
         <v>0</v>
@@ -15201,17 +15217,17 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Kelly Yuliana Ospina Saldarriaga</t>
+          <t>Lider Eduar Alonso Olaya Estrada</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>SUPERNUMERARIO</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>GIRARDOTA</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -15229,7 +15245,7 @@
         <v>100</v>
       </c>
       <c r="L294" t="n">
-        <v>63.6</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="295">
@@ -15239,29 +15255,29 @@
         </is>
       </c>
       <c r="B295" t="n">
-        <v>808088</v>
+        <v>1185250</v>
       </c>
       <c r="C295" t="n">
-        <v>0</v>
+        <v>349000</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Kelly Yuliana Ospina Saldarriaga</t>
+          <t>Lider Eduar Alonso Olaya Estrada</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>SUPERNUMERARIO</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>GIRARDOTA</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -15279,7 +15295,7 @@
         <v>100</v>
       </c>
       <c r="L295" t="n">
-        <v>63.6</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="296">
@@ -15289,29 +15305,29 @@
         </is>
       </c>
       <c r="B296" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C296" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>115%</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Sara Julieth Acevedo Gutierrez</t>
+          <t>Narelig Alejandra GarcÃ­a Ramirez</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>SUPERNUMERARIO</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>GIRARDOTA</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -15329,7 +15345,7 @@
         <v>100</v>
       </c>
       <c r="L296" t="n">
-        <v>5</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="297">
@@ -15339,29 +15355,29 @@
         </is>
       </c>
       <c r="B297" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C297" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Sara Julieth Acevedo Gutierrez</t>
+          <t>Narelig Alejandra GarcÃ­a Ramirez</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>SUPERNUMERARIO</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>GIRARDOTA</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -15379,7 +15395,7 @@
         <v>100</v>
       </c>
       <c r="L297" t="n">
-        <v>5</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="298">
@@ -15389,29 +15405,29 @@
         </is>
       </c>
       <c r="B298" t="n">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="C298" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Sara Julieth Acevedo Gutierrez</t>
+          <t>Narelig Alejandra GarcÃ­a Ramirez</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>SUPERNUMERARIO</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>GIRARDOTA</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -15429,7 +15445,7 @@
         <v>100</v>
       </c>
       <c r="L298" t="n">
-        <v>5</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="299">
@@ -15439,10 +15455,10 @@
         </is>
       </c>
       <c r="B299" t="n">
-        <v>133</v>
+        <v>102</v>
       </c>
       <c r="C299" t="n">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -15451,17 +15467,17 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Sara Julieth Acevedo Gutierrez</t>
+          <t>Narelig Alejandra GarcÃ­a Ramirez</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>SUPERNUMERARIO</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>GIRARDOTA</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -15479,7 +15495,7 @@
         <v>100</v>
       </c>
       <c r="L299" t="n">
-        <v>5</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="300">
@@ -15489,7 +15505,7 @@
         </is>
       </c>
       <c r="B300" t="n">
-        <v>399</v>
+        <v>941</v>
       </c>
       <c r="C300" t="n">
         <v>0</v>
@@ -15501,17 +15517,17 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Sara Julieth Acevedo Gutierrez</t>
+          <t>Narelig Alejandra GarcÃ­a Ramirez</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>SUPERNUMERARIO</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>GIRARDOTA</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -15529,7 +15545,7 @@
         <v>100</v>
       </c>
       <c r="L300" t="n">
-        <v>5</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="301">
@@ -15539,29 +15555,29 @@
         </is>
       </c>
       <c r="B301" t="n">
-        <v>1862000</v>
+        <v>4314750</v>
       </c>
       <c r="C301" t="n">
-        <v>20000</v>
+        <v>3027900</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Sara Julieth Acevedo Gutierrez</t>
+          <t>Narelig Alejandra GarcÃ­a Ramirez</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>SUPERNUMERARIO</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>GIRARDOTA</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -15579,7 +15595,7 @@
         <v>100</v>
       </c>
       <c r="L301" t="n">
-        <v>5</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="302">
@@ -15589,19 +15605,19 @@
         </is>
       </c>
       <c r="B302" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C302" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>138%</t>
+          <t>180%</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Lider Sara Julieth Acevedo Gutierrez</t>
+          <t>Luisa Fernanda Miranda Rodriguez</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
@@ -15611,7 +15627,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>SEGOVIA</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -15624,16 +15640,12 @@
           <t>Sin pago (0%)</t>
         </is>
       </c>
-      <c r="J302" t="inlineStr">
-        <is>
-          <t>Inicia desde el 8 en el punto</t>
-        </is>
-      </c>
+      <c r="J302" t="inlineStr"/>
       <c r="K302" t="n">
         <v>100</v>
       </c>
       <c r="L302" t="n">
-        <v>96</v>
+        <v>109.5</v>
       </c>
     </row>
     <row r="303">
@@ -15643,19 +15655,19 @@
         </is>
       </c>
       <c r="B303" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Lider Sara Julieth Acevedo Gutierrez</t>
+          <t>Luisa Fernanda Miranda Rodriguez</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
@@ -15665,7 +15677,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>SEGOVIA</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -15683,7 +15695,7 @@
         <v>100</v>
       </c>
       <c r="L303" t="n">
-        <v>96</v>
+        <v>109.5</v>
       </c>
     </row>
     <row r="304">
@@ -15693,19 +15705,19 @@
         </is>
       </c>
       <c r="B304" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C304" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Lider Sara Julieth Acevedo Gutierrez</t>
+          <t>Luisa Fernanda Miranda Rodriguez</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
@@ -15715,7 +15727,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>SEGOVIA</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -15733,7 +15745,7 @@
         <v>100</v>
       </c>
       <c r="L304" t="n">
-        <v>96</v>
+        <v>109.5</v>
       </c>
     </row>
     <row r="305">
@@ -15743,10 +15755,10 @@
         </is>
       </c>
       <c r="B305" t="n">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="C305" t="n">
-        <v>25</v>
+        <v>112</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -15755,7 +15767,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Lider Sara Julieth Acevedo Gutierrez</t>
+          <t>Luisa Fernanda Miranda Rodriguez</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
@@ -15765,7 +15777,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>SEGOVIA</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -15783,7 +15795,7 @@
         <v>100</v>
       </c>
       <c r="L305" t="n">
-        <v>96</v>
+        <v>109.5</v>
       </c>
     </row>
     <row r="306">
@@ -15793,7 +15805,7 @@
         </is>
       </c>
       <c r="B306" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="C306" t="n">
         <v>0</v>
@@ -15805,7 +15817,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Lider Sara Julieth Acevedo Gutierrez</t>
+          <t>Luisa Fernanda Miranda Rodriguez</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
@@ -15815,7 +15827,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>SEGOVIA</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -15833,7 +15845,7 @@
         <v>100</v>
       </c>
       <c r="L306" t="n">
-        <v>96</v>
+        <v>109.5</v>
       </c>
     </row>
     <row r="307">
@@ -15843,19 +15855,19 @@
         </is>
       </c>
       <c r="B307" t="n">
-        <v>1076000</v>
+        <v>2500000</v>
       </c>
       <c r="C307" t="n">
-        <v>0</v>
+        <v>2260900</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Lider Sara Julieth Acevedo Gutierrez</t>
+          <t>Luisa Fernanda Miranda Rodriguez</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
@@ -15865,7 +15877,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>SEGOVIA</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -15883,7 +15895,7 @@
         <v>100</v>
       </c>
       <c r="L307" t="n">
-        <v>96</v>
+        <v>109.5</v>
       </c>
     </row>
     <row r="308">
@@ -15893,19 +15905,19 @@
         </is>
       </c>
       <c r="B308" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C308" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>133%</t>
+          <t>170%</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Daniel Alberto Orozco Orozco</t>
+          <t>Sandra Milena Ortiz Solorzano</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
@@ -15915,7 +15927,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>SEGOVIA</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -15930,14 +15942,14 @@
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>El 8 inician capacitación de CVS PLUS - elabora 12 días en el punto</t>
+          <t>Inicia el 7 a elaborar en el punto</t>
         </is>
       </c>
       <c r="K308" t="n">
         <v>100</v>
       </c>
       <c r="L308" t="n">
-        <v>77.59999999999999</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="309">
@@ -15947,7 +15959,7 @@
         </is>
       </c>
       <c r="B309" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C309" t="n">
         <v>0</v>
@@ -15959,7 +15971,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Daniel Alberto Orozco Orozco</t>
+          <t>Sandra Milena Ortiz Solorzano</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
@@ -15969,7 +15981,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>SEGOVIA</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -15987,7 +15999,7 @@
         <v>100</v>
       </c>
       <c r="L309" t="n">
-        <v>77.59999999999999</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="310">
@@ -15997,10 +16009,10 @@
         </is>
       </c>
       <c r="B310" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C310" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -16009,7 +16021,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Daniel Alberto Orozco Orozco</t>
+          <t>Sandra Milena Ortiz Solorzano</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -16019,7 +16031,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>SEGOVIA</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -16037,7 +16049,7 @@
         <v>100</v>
       </c>
       <c r="L310" t="n">
-        <v>77.59999999999999</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="311">
@@ -16047,10 +16059,10 @@
         </is>
       </c>
       <c r="B311" t="n">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="C311" t="n">
-        <v>12</v>
+        <v>99</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -16059,7 +16071,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Daniel Alberto Orozco Orozco</t>
+          <t>Sandra Milena Ortiz Solorzano</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
@@ -16069,7 +16081,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>SEGOVIA</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -16087,7 +16099,7 @@
         <v>100</v>
       </c>
       <c r="L311" t="n">
-        <v>77.59999999999999</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="312">
@@ -16097,7 +16109,7 @@
         </is>
       </c>
       <c r="B312" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="C312" t="n">
         <v>0</v>
@@ -16109,7 +16121,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Daniel Alberto Orozco Orozco</t>
+          <t>Sandra Milena Ortiz Solorzano</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
@@ -16119,7 +16131,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>SEGOVIA</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -16137,7 +16149,7 @@
         <v>100</v>
       </c>
       <c r="L312" t="n">
-        <v>77.59999999999999</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="313">
@@ -16147,19 +16159,19 @@
         </is>
       </c>
       <c r="B313" t="n">
-        <v>370000</v>
+        <v>2500000</v>
       </c>
       <c r="C313" t="n">
-        <v>160000</v>
+        <v>1339000</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Daniel Alberto Orozco Orozco</t>
+          <t>Sandra Milena Ortiz Solorzano</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
@@ -16169,7 +16181,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>SEGOVIA</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -16187,7 +16199,7 @@
         <v>100</v>
       </c>
       <c r="L313" t="n">
-        <v>77.59999999999999</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="314">
@@ -16197,29 +16209,29 @@
         </is>
       </c>
       <c r="B314" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C314" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>150%</t>
+          <t>115%</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Luz Aida Quirama Corrales</t>
+          <t>Lider Leider  Alexander Calderon</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -16234,14 +16246,14 @@
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>El 8 inician capacitación de CVS PLUS - elabora 12 días en el punto</t>
+          <t>Vacaciones del 1 al  17  de septiembre</t>
         </is>
       </c>
       <c r="K314" t="n">
         <v>100</v>
       </c>
       <c r="L314" t="n">
-        <v>85.90000000000001</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="315">
@@ -16254,26 +16266,26 @@
         <v>1</v>
       </c>
       <c r="C315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Luz Aida Quirama Corrales</t>
+          <t>Lider Leider  Alexander Calderon</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -16291,7 +16303,7 @@
         <v>100</v>
       </c>
       <c r="L315" t="n">
-        <v>85.90000000000001</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="316">
@@ -16301,29 +16313,29 @@
         </is>
       </c>
       <c r="B316" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C316" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Luz Aida Quirama Corrales</t>
+          <t>Lider Leider  Alexander Calderon</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -16341,7 +16353,7 @@
         <v>100</v>
       </c>
       <c r="L316" t="n">
-        <v>85.90000000000001</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="317">
@@ -16351,29 +16363,29 @@
         </is>
       </c>
       <c r="B317" t="n">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="C317" t="n">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Pendiente 4 porta pre</t>
+          <t>133%</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Luz Aida Quirama Corrales</t>
+          <t>Lider Leider  Alexander Calderon</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -16391,7 +16403,7 @@
         <v>100</v>
       </c>
       <c r="L317" t="n">
-        <v>85.90000000000001</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="318">
@@ -16401,29 +16413,29 @@
         </is>
       </c>
       <c r="B318" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="C318" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>185%</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Luz Aida Quirama Corrales</t>
+          <t>Lider Leider  Alexander Calderon</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -16441,7 +16453,7 @@
         <v>100</v>
       </c>
       <c r="L318" t="n">
-        <v>85.90000000000001</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="319">
@@ -16451,29 +16463,29 @@
         </is>
       </c>
       <c r="B319" t="n">
-        <v>554000</v>
+        <v>633088</v>
       </c>
       <c r="C319" t="n">
-        <v>390000</v>
+        <v>1035000</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>163%</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Luz Aida Quirama Corrales</t>
+          <t>Lider Leider  Alexander Calderon</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>METRO EST. SAN ANTONIO</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -16491,7 +16503,7 @@
         <v>100</v>
       </c>
       <c r="L319" t="n">
-        <v>85.90000000000001</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="320">
@@ -16501,29 +16513,29 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="C320" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>250%</t>
+          <t>109%</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Lider Zargoza Kelly Celsa</t>
+          <t>Jessica Catherine Gutierrez Garcia</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>ZARAGOZA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -16538,14 +16550,14 @@
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>Termina licencia de maternidad el 21 - inicia labor el 22</t>
+          <t>Vacaciones del 28 de sept al 15 de octubre</t>
         </is>
       </c>
       <c r="K320" t="n">
         <v>100</v>
       </c>
       <c r="L320" t="n">
-        <v>189.4</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="321">
@@ -16555,29 +16567,29 @@
         </is>
       </c>
       <c r="B321" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C321" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>167%</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Lider Zargoza Kelly Celsa</t>
+          <t>Jessica Catherine Gutierrez Garcia</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>ZARAGOZA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -16595,7 +16607,7 @@
         <v>100</v>
       </c>
       <c r="L321" t="n">
-        <v>189.4</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="322">
@@ -16605,29 +16617,29 @@
         </is>
       </c>
       <c r="B322" t="n">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="C322" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>140%</t>
+          <t>96%</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Lider Zargoza Kelly Celsa</t>
+          <t>Jessica Catherine Gutierrez Garcia</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>ZARAGOZA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -16645,7 +16657,7 @@
         <v>100</v>
       </c>
       <c r="L322" t="n">
-        <v>189.4</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="323">
@@ -16655,10 +16667,10 @@
         </is>
       </c>
       <c r="B323" t="n">
-        <v>7</v>
+        <v>118</v>
       </c>
       <c r="C323" t="n">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -16667,17 +16679,17 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Lider Zargoza Kelly Celsa</t>
+          <t>Jessica Catherine Gutierrez Garcia</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>ZARAGOZA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -16695,7 +16707,7 @@
         <v>100</v>
       </c>
       <c r="L323" t="n">
-        <v>189.4</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="324">
@@ -16705,29 +16717,29 @@
         </is>
       </c>
       <c r="B324" t="n">
-        <v>92</v>
+        <v>354</v>
       </c>
       <c r="C324" t="n">
-        <v>0</v>
+        <v>505</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>143%</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Lider Zargoza Kelly Celsa</t>
+          <t>Jessica Catherine Gutierrez Garcia</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>ZARAGOZA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -16745,7 +16757,7 @@
         <v>100</v>
       </c>
       <c r="L324" t="n">
-        <v>189.4</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="325">
@@ -16755,29 +16767,29 @@
         </is>
       </c>
       <c r="B325" t="n">
-        <v>460000</v>
+        <v>1651176</v>
       </c>
       <c r="C325" t="n">
-        <v>0</v>
+        <v>899000</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Lider Zargoza Kelly Celsa</t>
+          <t>Jessica Catherine Gutierrez Garcia</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>ZARAGOZA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -16795,7 +16807,7 @@
         <v>100</v>
       </c>
       <c r="L325" t="n">
-        <v>189.4</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="326">
@@ -16805,19 +16817,19 @@
         </is>
       </c>
       <c r="B326" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="C326" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>141%</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Paola Andrea Castillo Perez</t>
+          <t>Nasly Johanna Martinez Ocampo</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
@@ -16827,7 +16839,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>ZARAGOZA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -16845,7 +16857,7 @@
         <v>100</v>
       </c>
       <c r="L326" t="n">
-        <v>91.5</v>
+        <v>127.1</v>
       </c>
     </row>
     <row r="327">
@@ -16855,19 +16867,19 @@
         </is>
       </c>
       <c r="B327" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C327" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>150%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Paola Andrea Castillo Perez</t>
+          <t>Nasly Johanna Martinez Ocampo</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
@@ -16877,7 +16889,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>ZARAGOZA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -16895,7 +16907,7 @@
         <v>100</v>
       </c>
       <c r="L327" t="n">
-        <v>91.5</v>
+        <v>127.1</v>
       </c>
     </row>
     <row r="328">
@@ -16905,19 +16917,19 @@
         </is>
       </c>
       <c r="B328" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C328" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>125%</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Paola Andrea Castillo Perez</t>
+          <t>Nasly Johanna Martinez Ocampo</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
@@ -16927,7 +16939,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>ZARAGOZA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -16945,7 +16957,7 @@
         <v>100</v>
       </c>
       <c r="L328" t="n">
-        <v>91.5</v>
+        <v>127.1</v>
       </c>
     </row>
     <row r="329">
@@ -16955,19 +16967,19 @@
         </is>
       </c>
       <c r="B329" t="n">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="C329" t="n">
-        <v>56</v>
+        <v>139</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Pendiente 4 porta pre</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Paola Andrea Castillo Perez</t>
+          <t>Nasly Johanna Martinez Ocampo</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
@@ -16977,7 +16989,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>ZARAGOZA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -16995,7 +17007,7 @@
         <v>100</v>
       </c>
       <c r="L329" t="n">
-        <v>91.5</v>
+        <v>127.1</v>
       </c>
     </row>
     <row r="330">
@@ -17005,19 +17017,19 @@
         </is>
       </c>
       <c r="B330" t="n">
-        <v>1108</v>
+        <v>419</v>
       </c>
       <c r="C330" t="n">
-        <v>0</v>
+        <v>505</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>121%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Paola Andrea Castillo Perez</t>
+          <t>Nasly Johanna Martinez Ocampo</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
@@ -17027,7 +17039,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>ZARAGOZA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -17045,7 +17057,7 @@
         <v>100</v>
       </c>
       <c r="L330" t="n">
-        <v>91.5</v>
+        <v>127.1</v>
       </c>
     </row>
     <row r="331">
@@ -17055,19 +17067,19 @@
         </is>
       </c>
       <c r="B331" t="n">
-        <v>5540000</v>
+        <v>1953824</v>
       </c>
       <c r="C331" t="n">
-        <v>3700001</v>
+        <v>2986400</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>153%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Paola Andrea Castillo Perez</t>
+          <t>Nasly Johanna Martinez Ocampo</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
@@ -17077,7 +17089,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>ZARAGOZA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -17095,7 +17107,7 @@
         <v>100</v>
       </c>
       <c r="L331" t="n">
-        <v>91.5</v>
+        <v>127.1</v>
       </c>
     </row>
     <row r="332">
@@ -17105,29 +17117,29 @@
         </is>
       </c>
       <c r="B332" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="C332" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>103%</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Kelly Yuliana Ospina Saldarriaga</t>
+          <t>Sandra Milena Carmona Galeano</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>SUPERNUMERARIO</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>ZARAGOZA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -17145,7 +17157,7 @@
         <v>100</v>
       </c>
       <c r="L332" t="n">
-        <v>0</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="333">
@@ -17155,29 +17167,29 @@
         </is>
       </c>
       <c r="B333" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C333" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>150%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Kelly Yuliana Ospina Saldarriaga</t>
+          <t>Sandra Milena Carmona Galeano</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>SUPERNUMERARIO</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>ZARAGOZA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -17195,7 +17207,7 @@
         <v>100</v>
       </c>
       <c r="L333" t="n">
-        <v>0</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="334">
@@ -17205,29 +17217,29 @@
         </is>
       </c>
       <c r="B334" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C334" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Kelly Yuliana Ospina Saldarriaga</t>
+          <t>Sandra Milena Carmona Galeano</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>SUPERNUMERARIO</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>ZARAGOZA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -17245,7 +17257,7 @@
         <v>100</v>
       </c>
       <c r="L334" t="n">
-        <v>0</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="335">
@@ -17255,10 +17267,10 @@
         </is>
       </c>
       <c r="B335" t="n">
-        <v>54</v>
+        <v>140</v>
       </c>
       <c r="C335" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -17267,17 +17279,17 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Kelly Yuliana Ospina Saldarriaga</t>
+          <t>Sandra Milena Carmona Galeano</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>SUPERNUMERARIO</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>ZARAGOZA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -17295,7 +17307,7 @@
         <v>100</v>
       </c>
       <c r="L335" t="n">
-        <v>0</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="336">
@@ -17305,29 +17317,29 @@
         </is>
       </c>
       <c r="B336" t="n">
-        <v>720</v>
+        <v>419</v>
       </c>
       <c r="C336" t="n">
-        <v>0</v>
+        <v>505</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>121%</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Kelly Yuliana Ospina Saldarriaga</t>
+          <t>Sandra Milena Carmona Galeano</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>SUPERNUMERARIO</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>ZARAGOZA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -17345,7 +17357,7 @@
         <v>100</v>
       </c>
       <c r="L336" t="n">
-        <v>0</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="337">
@@ -17355,29 +17367,29 @@
         </is>
       </c>
       <c r="B337" t="n">
-        <v>3600000</v>
+        <v>1953824</v>
       </c>
       <c r="C337" t="n">
-        <v>462000</v>
+        <v>1493500</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Kelly Yuliana Ospina Saldarriaga</t>
+          <t>Sandra Milena Carmona Galeano</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>SUPERNUMERARIO</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>ZARAGOZA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -17395,7 +17407,7 @@
         <v>100</v>
       </c>
       <c r="L337" t="n">
-        <v>0</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="338">
@@ -17405,29 +17417,29 @@
         </is>
       </c>
       <c r="B338" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C338" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Lider Eduar Alonso Olaya Estrada</t>
+          <t>Yuliana Ospina Saldarriaga</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>GIRARDOTA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -17442,14 +17454,14 @@
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>Elabora en el punto 14 días por capacitación de CVS PLUS</t>
+          <t>Cubre vacaciones de Leider 12 días</t>
         </is>
       </c>
       <c r="K338" t="n">
         <v>100</v>
       </c>
       <c r="L338" t="n">
-        <v>9.6</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="339">
@@ -17471,17 +17483,17 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Lider Eduar Alonso Olaya Estrada</t>
+          <t>Yuliana Ospina Saldarriaga</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>GIRARDOTA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -17499,7 +17511,7 @@
         <v>100</v>
       </c>
       <c r="L339" t="n">
-        <v>9.6</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="340">
@@ -17509,29 +17521,29 @@
         </is>
       </c>
       <c r="B340" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C340" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Lider Eduar Alonso Olaya Estrada</t>
+          <t>Yuliana Ospina Saldarriaga</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>GIRARDOTA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -17549,7 +17561,7 @@
         <v>100</v>
       </c>
       <c r="L340" t="n">
-        <v>9.6</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="341">
@@ -17559,10 +17571,10 @@
         </is>
       </c>
       <c r="B341" t="n">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="C341" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -17571,17 +17583,17 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Lider Eduar Alonso Olaya Estrada</t>
+          <t>Yuliana Ospina Saldarriaga</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>GIRARDOTA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -17599,7 +17611,7 @@
         <v>100</v>
       </c>
       <c r="L341" t="n">
-        <v>9.6</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="342">
@@ -17609,29 +17621,29 @@
         </is>
       </c>
       <c r="B342" t="n">
-        <v>259</v>
+        <v>173</v>
       </c>
       <c r="C342" t="n">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>146%</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Lider Eduar Alonso Olaya Estrada</t>
+          <t>Yuliana Ospina Saldarriaga</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>GIRARDOTA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -17649,7 +17661,7 @@
         <v>100</v>
       </c>
       <c r="L342" t="n">
-        <v>9.6</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="343">
@@ -17659,29 +17671,29 @@
         </is>
       </c>
       <c r="B343" t="n">
-        <v>1185250</v>
+        <v>808088</v>
       </c>
       <c r="C343" t="n">
-        <v>349000</v>
+        <v>385000</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>48%</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Lider Eduar Alonso Olaya Estrada</t>
+          <t>Yuliana Ospina Saldarriaga</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>ASESOR</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>GIRARDOTA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -17699,7 +17711,7 @@
         <v>100</v>
       </c>
       <c r="L343" t="n">
-        <v>9.6</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="344">
@@ -17709,29 +17721,29 @@
         </is>
       </c>
       <c r="B344" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="C344" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>115%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Narelig Alejandra GarcÃ­a Ramirez</t>
+          <t>Sara Julieth Acevedo Gutierrez</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>SUPERNUMERARIO</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>GIRARDOTA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -17744,12 +17756,16 @@
           <t>Sin pago (0%)</t>
         </is>
       </c>
-      <c r="J344" t="inlineStr"/>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>Cubre vacaciones de Leider 4 días</t>
+        </is>
+      </c>
       <c r="K344" t="n">
         <v>100</v>
       </c>
       <c r="L344" t="n">
-        <v>79.59999999999999</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="345">
@@ -17759,29 +17775,29 @@
         </is>
       </c>
       <c r="B345" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C345" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Narelig Alejandra GarcÃ­a Ramirez</t>
+          <t>Sara Julieth Acevedo Gutierrez</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>SUPERNUMERARIO</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>GIRARDOTA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -17799,7 +17815,7 @@
         <v>100</v>
       </c>
       <c r="L345" t="n">
-        <v>79.59999999999999</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="346">
@@ -17809,29 +17825,29 @@
         </is>
       </c>
       <c r="B346" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="C346" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Narelig Alejandra GarcÃ­a Ramirez</t>
+          <t>Sara Julieth Acevedo Gutierrez</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>SUPERNUMERARIO</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>GIRARDOTA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -17849,7 +17865,7 @@
         <v>100</v>
       </c>
       <c r="L346" t="n">
-        <v>79.59999999999999</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="347">
@@ -17859,10 +17875,10 @@
         </is>
       </c>
       <c r="B347" t="n">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="C347" t="n">
-        <v>95</v>
+        <v>11</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -17871,17 +17887,17 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Narelig Alejandra GarcÃ­a Ramirez</t>
+          <t>Sara Julieth Acevedo Gutierrez</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>SUPERNUMERARIO</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>GIRARDOTA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -17899,7 +17915,7 @@
         <v>100</v>
       </c>
       <c r="L347" t="n">
-        <v>79.59999999999999</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="348">
@@ -17909,7 +17925,7 @@
         </is>
       </c>
       <c r="B348" t="n">
-        <v>941</v>
+        <v>399</v>
       </c>
       <c r="C348" t="n">
         <v>0</v>
@@ -17921,17 +17937,17 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Narelig Alejandra GarcÃ­a Ramirez</t>
+          <t>Sara Julieth Acevedo Gutierrez</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>SUPERNUMERARIO</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>GIRARDOTA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -17949,7 +17965,7 @@
         <v>100</v>
       </c>
       <c r="L348" t="n">
-        <v>79.59999999999999</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="349">
@@ -17959,29 +17975,29 @@
         </is>
       </c>
       <c r="B349" t="n">
-        <v>4314750</v>
+        <v>1862000</v>
       </c>
       <c r="C349" t="n">
-        <v>3027900</v>
+        <v>20000</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Narelig Alejandra GarcÃ­a Ramirez</t>
+          <t>Sara Julieth Acevedo Gutierrez</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>ASESOR</t>
+          <t>SUPERNUMERARIO</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>GIRARDOTA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -17999,7 +18015,7 @@
         <v>100</v>
       </c>
       <c r="L349" t="n">
-        <v>79.59999999999999</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="350">
@@ -18009,19 +18025,19 @@
         </is>
       </c>
       <c r="B350" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C350" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>180%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Luisa Fernanda Miranda Rodriguez</t>
+          <t>Lider Don Matias Diana Ruiz</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
@@ -18031,7 +18047,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>SEGOVIA</t>
+          <t>DON MATIAS</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -18044,12 +18060,16 @@
           <t>Sin pago (0%)</t>
         </is>
       </c>
-      <c r="J350" t="inlineStr"/>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>Vacaciones del 7 al 16 de septiembre</t>
+        </is>
+      </c>
       <c r="K350" t="n">
         <v>100</v>
       </c>
       <c r="L350" t="n">
-        <v>109.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="351">
@@ -18071,7 +18091,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Luisa Fernanda Miranda Rodriguez</t>
+          <t>Lider Don Matias Diana Ruiz</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
@@ -18081,7 +18101,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>SEGOVIA</t>
+          <t>DON MATIAS</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -18099,7 +18119,7 @@
         <v>100</v>
       </c>
       <c r="L351" t="n">
-        <v>109.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="352">
@@ -18109,19 +18129,19 @@
         </is>
       </c>
       <c r="B352" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C352" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>92%</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Luisa Fernanda Miranda Rodriguez</t>
+          <t>Lider Don Matias Diana Ruiz</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
@@ -18131,7 +18151,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>SEGOVIA</t>
+          <t>DON MATIAS</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -18149,7 +18169,7 @@
         <v>100</v>
       </c>
       <c r="L352" t="n">
-        <v>109.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="353">
@@ -18159,10 +18179,10 @@
         </is>
       </c>
       <c r="B353" t="n">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="C353" t="n">
-        <v>112</v>
+        <v>31</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -18171,7 +18191,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Luisa Fernanda Miranda Rodriguez</t>
+          <t>Lider Don Matias Diana Ruiz</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
@@ -18181,7 +18201,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>SEGOVIA</t>
+          <t>DON MATIAS</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -18199,7 +18219,7 @@
         <v>100</v>
       </c>
       <c r="L353" t="n">
-        <v>109.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="354">
@@ -18209,19 +18229,19 @@
         </is>
       </c>
       <c r="B354" t="n">
-        <v>600</v>
+        <v>314</v>
       </c>
       <c r="C354" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>153%</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Luisa Fernanda Miranda Rodriguez</t>
+          <t>Lider Don Matias Diana Ruiz</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
@@ -18231,7 +18251,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>SEGOVIA</t>
+          <t>DON MATIAS</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -18249,7 +18269,7 @@
         <v>100</v>
       </c>
       <c r="L354" t="n">
-        <v>109.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="355">
@@ -18259,19 +18279,19 @@
         </is>
       </c>
       <c r="B355" t="n">
-        <v>2500000</v>
+        <v>1306667</v>
       </c>
       <c r="C355" t="n">
-        <v>2260900</v>
+        <v>2135900</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>163%</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Luisa Fernanda Miranda Rodriguez</t>
+          <t>Lider Don Matias Diana Ruiz</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
@@ -18281,7 +18301,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>SEGOVIA</t>
+          <t>DON MATIAS</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -18299,7 +18319,7 @@
         <v>100</v>
       </c>
       <c r="L355" t="n">
-        <v>109.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="356">
@@ -18309,19 +18329,19 @@
         </is>
       </c>
       <c r="B356" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C356" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>170%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Sandra Milena Ortiz Solorzano</t>
+          <t>Evelyn Daniela Lopera Lopera</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
@@ -18331,7 +18351,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>SEGOVIA</t>
+          <t>DON MATIAS</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -18344,16 +18364,12 @@
           <t>Sin pago (0%)</t>
         </is>
       </c>
-      <c r="J356" t="inlineStr">
-        <is>
-          <t>Inicia el 7 a elaborar en el punto</t>
-        </is>
-      </c>
+      <c r="J356" t="inlineStr"/>
       <c r="K356" t="n">
         <v>100</v>
       </c>
       <c r="L356" t="n">
-        <v>85.2</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="357">
@@ -18375,7 +18391,7 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Sandra Milena Ortiz Solorzano</t>
+          <t>Evelyn Daniela Lopera Lopera</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
@@ -18385,7 +18401,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>SEGOVIA</t>
+          <t>DON MATIAS</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -18403,7 +18419,7 @@
         <v>100</v>
       </c>
       <c r="L357" t="n">
-        <v>85.2</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="358">
@@ -18413,19 +18429,19 @@
         </is>
       </c>
       <c r="B358" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C358" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Sandra Milena Ortiz Solorzano</t>
+          <t>Evelyn Daniela Lopera Lopera</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
@@ -18435,7 +18451,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>SEGOVIA</t>
+          <t>DON MATIAS</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -18453,7 +18469,7 @@
         <v>100</v>
       </c>
       <c r="L358" t="n">
-        <v>85.2</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="359">
@@ -18463,10 +18479,10 @@
         </is>
       </c>
       <c r="B359" t="n">
-        <v>110</v>
+        <v>59</v>
       </c>
       <c r="C359" t="n">
-        <v>99</v>
+        <v>54</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -18475,7 +18491,7 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Sandra Milena Ortiz Solorzano</t>
+          <t>Evelyn Daniela Lopera Lopera</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
@@ -18485,7 +18501,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>SEGOVIA</t>
+          <t>DON MATIAS</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -18503,7 +18519,7 @@
         <v>100</v>
       </c>
       <c r="L359" t="n">
-        <v>85.2</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="360">
@@ -18513,19 +18529,19 @@
         </is>
       </c>
       <c r="B360" t="n">
-        <v>600</v>
+        <v>886</v>
       </c>
       <c r="C360" t="n">
-        <v>0</v>
+        <v>738</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Sandra Milena Ortiz Solorzano</t>
+          <t>Evelyn Daniela Lopera Lopera</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
@@ -18535,7 +18551,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>SEGOVIA</t>
+          <t>DON MATIAS</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -18553,7 +18569,7 @@
         <v>100</v>
       </c>
       <c r="L360" t="n">
-        <v>85.2</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="361">
@@ -18563,19 +18579,19 @@
         </is>
       </c>
       <c r="B361" t="n">
-        <v>2500000</v>
+        <v>3693333</v>
       </c>
       <c r="C361" t="n">
-        <v>1339000</v>
+        <v>2739000</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Sandra Milena Ortiz Solorzano</t>
+          <t>Evelyn Daniela Lopera Lopera</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
@@ -18585,7 +18601,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>SEGOVIA</t>
+          <t>DON MATIAS</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -18603,7 +18619,1515 @@
         <v>100</v>
       </c>
       <c r="L361" t="n">
-        <v>85.2</v>
+        <v>88.59999999999999</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>POSTPAGO</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>15</v>
+      </c>
+      <c r="C362" t="n">
+        <v>14</v>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>93%</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>Lider Copacabana Vanessa Carolina Castillo Duran</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>COPACABANA</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr"/>
+      <c r="K362" t="n">
+        <v>100</v>
+      </c>
+      <c r="L362" t="n">
+        <v>81.90000000000001</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>HOGAR</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>4</v>
+      </c>
+      <c r="C363" t="n">
+        <v>6</v>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>150%</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>Lider Copacabana Vanessa Carolina Castillo Duran</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>COPACABANA</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr"/>
+      <c r="K363" t="n">
+        <v>100</v>
+      </c>
+      <c r="L363" t="n">
+        <v>81.90000000000001</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>TERMINALES</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>26</v>
+      </c>
+      <c r="C364" t="n">
+        <v>17</v>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>Lider Copacabana Vanessa Carolina Castillo Duran</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>COPACABANA</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr"/>
+      <c r="K364" t="n">
+        <v>100</v>
+      </c>
+      <c r="L364" t="n">
+        <v>81.90000000000001</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>50</v>
+      </c>
+      <c r="C365" t="n">
+        <v>30</v>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>Lider Copacabana Vanessa Carolina Castillo Duran</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>COPACABANA</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr"/>
+      <c r="K365" t="n">
+        <v>100</v>
+      </c>
+      <c r="L365" t="n">
+        <v>81.90000000000001</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>CVS PLUS</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>418</v>
+      </c>
+      <c r="C366" t="n">
+        <v>386</v>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Lider Copacabana Vanessa Carolina Castillo Duran</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>COPACABANA</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr"/>
+      <c r="K366" t="n">
+        <v>100</v>
+      </c>
+      <c r="L366" t="n">
+        <v>81.90000000000001</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>ACCESORIOS</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>0</v>
+      </c>
+      <c r="C367" t="n">
+        <v>0</v>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>Lider Copacabana Vanessa Carolina Castillo Duran</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>COPACABANA</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr"/>
+      <c r="K367" t="n">
+        <v>100</v>
+      </c>
+      <c r="L367" t="n">
+        <v>81.90000000000001</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>POSTPAGO</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>17</v>
+      </c>
+      <c r="C368" t="n">
+        <v>18</v>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>106%</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>Alexandra Patricia Duque</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>COPACABANA</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>Calamidad de  5 días</t>
+        </is>
+      </c>
+      <c r="K368" t="n">
+        <v>100</v>
+      </c>
+      <c r="L368" t="n">
+        <v>107.9</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>HOGAR</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>4</v>
+      </c>
+      <c r="C369" t="n">
+        <v>10</v>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>250%</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>Alexandra Patricia Duque</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>COPACABANA</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr"/>
+      <c r="K369" t="n">
+        <v>100</v>
+      </c>
+      <c r="L369" t="n">
+        <v>107.9</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>TERMINALES</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>29</v>
+      </c>
+      <c r="C370" t="n">
+        <v>27</v>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>93%</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>Alexandra Patricia Duque</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>COPACABANA</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr"/>
+      <c r="K370" t="n">
+        <v>100</v>
+      </c>
+      <c r="L370" t="n">
+        <v>107.9</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>55</v>
+      </c>
+      <c r="C371" t="n">
+        <v>37</v>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Pendiente 4 porta pre</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>Alexandra Patricia Duque</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>COPACABANA</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr"/>
+      <c r="K371" t="n">
+        <v>100</v>
+      </c>
+      <c r="L371" t="n">
+        <v>107.9</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>CVS PLUS</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>455</v>
+      </c>
+      <c r="C372" t="n">
+        <v>573</v>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>126%</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>Alexandra Patricia Duque</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>COPACABANA</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr"/>
+      <c r="K372" t="n">
+        <v>100</v>
+      </c>
+      <c r="L372" t="n">
+        <v>107.9</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>ACCESORIOS</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>0</v>
+      </c>
+      <c r="C373" t="n">
+        <v>0</v>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>Alexandra Patricia Duque</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>COPACABANA</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr"/>
+      <c r="K373" t="n">
+        <v>100</v>
+      </c>
+      <c r="L373" t="n">
+        <v>107.9</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>POSTPAGO</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>23</v>
+      </c>
+      <c r="C374" t="n">
+        <v>22</v>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>Bibiana Farley Rios Agudelo</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>COPACABANA</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr"/>
+      <c r="K374" t="n">
+        <v>100</v>
+      </c>
+      <c r="L374" t="n">
+        <v>97.3</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>HOGAR</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>6</v>
+      </c>
+      <c r="C375" t="n">
+        <v>8</v>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>133%</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>Bibiana Farley Rios Agudelo</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>COPACABANA</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr"/>
+      <c r="K375" t="n">
+        <v>100</v>
+      </c>
+      <c r="L375" t="n">
+        <v>97.3</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>TERMINALES</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>40</v>
+      </c>
+      <c r="C376" t="n">
+        <v>33</v>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>82%</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Bibiana Farley Rios Agudelo</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>COPACABANA</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr"/>
+      <c r="K376" t="n">
+        <v>100</v>
+      </c>
+      <c r="L376" t="n">
+        <v>97.3</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>75</v>
+      </c>
+      <c r="C377" t="n">
+        <v>61</v>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>Bibiana Farley Rios Agudelo</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>COPACABANA</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr"/>
+      <c r="K377" t="n">
+        <v>100</v>
+      </c>
+      <c r="L377" t="n">
+        <v>97.3</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>CVS PLUS</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>628</v>
+      </c>
+      <c r="C378" t="n">
+        <v>573</v>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>Bibiana Farley Rios Agudelo</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>COPACABANA</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr"/>
+      <c r="K378" t="n">
+        <v>100</v>
+      </c>
+      <c r="L378" t="n">
+        <v>97.3</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>ACCESORIOS</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>0</v>
+      </c>
+      <c r="C379" t="n">
+        <v>0</v>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>Bibiana Farley Rios Agudelo</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>COPACABANA</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr"/>
+      <c r="K379" t="n">
+        <v>100</v>
+      </c>
+      <c r="L379" t="n">
+        <v>97.3</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>POSTPAGO</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>4</v>
+      </c>
+      <c r="C380" t="n">
+        <v>6</v>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>150%</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>Lider Nechi Maricela Ravelo Hernandez</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>NECHI</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>9 días en caja</t>
+        </is>
+      </c>
+      <c r="K380" t="n">
+        <v>100</v>
+      </c>
+      <c r="L380" t="n">
+        <v>81.09999999999999</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>HOGAR</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>0</v>
+      </c>
+      <c r="C381" t="n">
+        <v>0</v>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>Lider Nechi Maricela Ravelo Hernandez</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>NECHI</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr"/>
+      <c r="K381" t="n">
+        <v>100</v>
+      </c>
+      <c r="L381" t="n">
+        <v>81.09999999999999</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>TERMINALES</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>20</v>
+      </c>
+      <c r="C382" t="n">
+        <v>15</v>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>Lider Nechi Maricela Ravelo Hernandez</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>NECHI</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr"/>
+      <c r="K382" t="n">
+        <v>100</v>
+      </c>
+      <c r="L382" t="n">
+        <v>81.09999999999999</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>18</v>
+      </c>
+      <c r="C383" t="n">
+        <v>33</v>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Pendiente 4 porta pre</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>Lider Nechi Maricela Ravelo Hernandez</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>NECHI</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr"/>
+      <c r="K383" t="n">
+        <v>100</v>
+      </c>
+      <c r="L383" t="n">
+        <v>81.09999999999999</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>CVS PLUS</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>209</v>
+      </c>
+      <c r="C384" t="n">
+        <v>340</v>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>163%</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>Lider Nechi Maricela Ravelo Hernandez</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>NECHI</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr"/>
+      <c r="K384" t="n">
+        <v>100</v>
+      </c>
+      <c r="L384" t="n">
+        <v>81.09999999999999</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>ACCESORIOS</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>1046000</v>
+      </c>
+      <c r="C385" t="n">
+        <v>2364000</v>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>226%</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>Lider Nechi Maricela Ravelo Hernandez</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>NECHI</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr"/>
+      <c r="K385" t="n">
+        <v>100</v>
+      </c>
+      <c r="L385" t="n">
+        <v>81.09999999999999</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>POSTPAGO</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>9</v>
+      </c>
+      <c r="C386" t="n">
+        <v>12</v>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>133%</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>LeidisÂ  Rosa Luna Serpa</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>NECHI</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr"/>
+      <c r="K386" t="n">
+        <v>100</v>
+      </c>
+      <c r="L386" t="n">
+        <v>81.3</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>HOGAR</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>0</v>
+      </c>
+      <c r="C387" t="n">
+        <v>0</v>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>LeidisÂ  Rosa Luna Serpa</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>NECHI</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J387" t="inlineStr"/>
+      <c r="K387" t="n">
+        <v>100</v>
+      </c>
+      <c r="L387" t="n">
+        <v>81.3</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>TERMINALES</t>
+        </is>
+      </c>
+      <c r="B388" t="n">
+        <v>45</v>
+      </c>
+      <c r="C388" t="n">
+        <v>38</v>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>84%</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>LeidisÂ  Rosa Luna Serpa</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>NECHI</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr"/>
+      <c r="K388" t="n">
+        <v>100</v>
+      </c>
+      <c r="L388" t="n">
+        <v>81.3</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+      <c r="B389" t="n">
+        <v>42</v>
+      </c>
+      <c r="C389" t="n">
+        <v>51</v>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Pendiente 4 porta pre</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>LeidisÂ  Rosa Luna Serpa</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>NECHI</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J389" t="inlineStr"/>
+      <c r="K389" t="n">
+        <v>100</v>
+      </c>
+      <c r="L389" t="n">
+        <v>81.3</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>CVS PLUS</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>480</v>
+      </c>
+      <c r="C390" t="n">
+        <v>499</v>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>104%</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>LeidisÂ  Rosa Luna Serpa</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>NECHI</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr"/>
+      <c r="K390" t="n">
+        <v>100</v>
+      </c>
+      <c r="L390" t="n">
+        <v>81.3</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>ACCESORIOS</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="C391" t="n">
+        <v>1414900</v>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>LeidisÂ  Rosa Luna Serpa</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>NECHI</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>Sin pago (0%)</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr"/>
+      <c r="K391" t="n">
+        <v>100</v>
+      </c>
+      <c r="L391" t="n">
+        <v>81.3</v>
       </c>
     </row>
   </sheetData>
